--- a/outputs/Table1_scc193_main.xlsx
+++ b/outputs/Table1_scc193_main.xlsx
@@ -912,7 +912,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K92"/>
-  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.6640625" style="1" bestFit="true" customWidth="true"/>
     <col min="2" max="2" width="57.88671875" style="1" bestFit="true" customWidth="true"/>
@@ -971,10 +971,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="1">
-        <v>4.2477803230285645</v>
+        <v>4.247780323028564</v>
       </c>
       <c r="D2" s="1">
-        <v>1.9003175552994895</v>
+        <v>1.90031755529949</v>
       </c>
       <c r="E2" s="1">
         <v>0.6449316181257877</v>
@@ -983,19 +983,19 @@
         <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>7.7930296273764865</v>
+        <v>7.793029627376487</v>
       </c>
       <c r="H2" s="1">
-        <v>0.32764032483100891</v>
+        <v>0.3276403248310089</v>
       </c>
       <c r="I2" s="1">
-        <v>1.3276402897315467</v>
+        <v>1.327640289731547</v>
       </c>
       <c r="J2" s="1">
         <v>5.869835376739502</v>
       </c>
       <c r="K2" s="1">
-        <v>0.99999999037529597</v>
+        <v>0.999999990375296</v>
       </c>
     </row>
     <row r="3">
@@ -1006,28 +1006,28 @@
         <v>1</v>
       </c>
       <c r="C3" s="1">
-        <v>5.3255972862243652</v>
+        <v>5.325597286224365</v>
       </c>
       <c r="D3" s="1">
         <v>3.276528843806986</v>
       </c>
       <c r="E3" s="1">
-        <v>0.91962104150673818</v>
+        <v>0.9196210415067382</v>
       </c>
       <c r="F3" s="1">
         <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>10.521747042780412</v>
+        <v>10.52174704278041</v>
       </c>
       <c r="H3" s="1">
-        <v>0.39422008395195007</v>
+        <v>0.3942200839519501</v>
       </c>
       <c r="I3" s="1">
-        <v>1.3942200638426809</v>
+        <v>1.394220063842681</v>
       </c>
       <c r="J3" s="1">
-        <v>7.5466903078276531</v>
+        <v>7.546690307827653</v>
       </c>
       <c r="K3" s="1"/>
     </row>
@@ -1039,13 +1039,13 @@
         <v>1</v>
       </c>
       <c r="C4" s="1">
-        <v>3.9663248062133789</v>
+        <v>3.966324806213379</v>
       </c>
       <c r="D4" s="1">
-        <v>1.4268290128130754</v>
+        <v>1.426829012813075</v>
       </c>
       <c r="E4" s="1">
-        <v>0.55988090691523651</v>
+        <v>0.5598809069152365</v>
       </c>
       <c r="F4" s="1">
         <v>0</v>
@@ -1054,13 +1054,13 @@
         <v>6.95303471610241</v>
       </c>
       <c r="H4" s="1">
-        <v>0.31237339973449707</v>
+        <v>0.3123733997344971</v>
       </c>
       <c r="I4" s="1">
-        <v>1.3123733759099934</v>
+        <v>1.312373375909993</v>
       </c>
       <c r="J4" s="1">
-        <v>5.2980613929943594</v>
+        <v>5.298061392994359</v>
       </c>
       <c r="K4" s="1"/>
     </row>
@@ -1072,19 +1072,19 @@
         <v>1</v>
       </c>
       <c r="C5" s="1">
-        <v>3.4514193534851074</v>
+        <v>3.451419353485107</v>
       </c>
       <c r="D5" s="1">
-        <v>0.99759480927840705</v>
+        <v>0.997594809278407</v>
       </c>
       <c r="E5" s="1">
-        <v>0.45529290595538857</v>
+        <v>0.4552929059553886</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>5.9043071232466371</v>
+        <v>5.904307123246637</v>
       </c>
       <c r="H5" s="1">
         <v>0.2763274610042572</v>
@@ -1093,7 +1093,7 @@
         <v>1.276327429441966</v>
       </c>
       <c r="J5" s="1">
-        <v>4.6260128765140687</v>
+        <v>4.626012876514069</v>
       </c>
       <c r="K5" s="1"/>
     </row>
@@ -1102,31 +1102,31 @@
         <v>19</v>
       </c>
       <c r="B6" s="1">
-        <v>1.1055999994277954</v>
+        <v>1.105599999427795</v>
       </c>
       <c r="C6" s="1">
-        <v>1.5485392808914185</v>
+        <v>1.548539280891418</v>
       </c>
       <c r="D6" s="1">
-        <v>2.2798671552230556</v>
+        <v>2.279867155223056</v>
       </c>
       <c r="E6" s="1">
-        <v>1.6356427467497199</v>
+        <v>1.63564274674972</v>
       </c>
       <c r="F6" s="1">
-        <v>-0.21376650035381317</v>
+        <v>-0.2137665003538132</v>
       </c>
       <c r="G6" s="1">
-        <v>6.3558827133164444</v>
+        <v>6.355882713316444</v>
       </c>
       <c r="H6" s="1">
-        <v>0.64589637517929077</v>
+        <v>0.6458963751792908</v>
       </c>
       <c r="I6" s="1">
-        <v>1.6458963407490212</v>
+        <v>1.645896340749021</v>
       </c>
       <c r="J6" s="1">
-        <v>3.8616542816162109</v>
+        <v>3.861654281616211</v>
       </c>
       <c r="K6" s="1">
         <v>1</v>
@@ -1140,28 +1140,28 @@
         <v>1</v>
       </c>
       <c r="C7" s="1">
-        <v>3.8758747577667236</v>
+        <v>3.875874757766724</v>
       </c>
       <c r="D7" s="1">
-        <v>4.9876325384792626</v>
+        <v>4.987632538479263</v>
       </c>
       <c r="E7" s="1">
-        <v>3.9873895827094756</v>
+        <v>3.987389582709476</v>
       </c>
       <c r="F7" s="1">
-        <v>-0.53504109382629395</v>
+        <v>-0.5350410938262939</v>
       </c>
       <c r="G7" s="1">
-        <v>13.315855810094593</v>
+        <v>13.31585581009459</v>
       </c>
       <c r="H7" s="1">
-        <v>1.6298918724060059</v>
+        <v>1.629891872406006</v>
       </c>
       <c r="I7" s="1">
-        <v>2.6298918836667342</v>
+        <v>2.629891883666734</v>
       </c>
       <c r="J7" s="1">
-        <v>5.0632711910304558</v>
+        <v>5.063271191030456</v>
       </c>
       <c r="K7" s="1"/>
     </row>
@@ -1173,28 +1173,28 @@
         <v>1</v>
       </c>
       <c r="C8" s="1">
-        <v>1.0996706485748291</v>
+        <v>1.099670648574829</v>
       </c>
       <c r="D8" s="1">
-        <v>3.1323282110512265</v>
+        <v>3.132328211051226</v>
       </c>
       <c r="E8" s="1">
-        <v>1.6098784208297734</v>
+        <v>1.609878420829773</v>
       </c>
       <c r="F8" s="1">
-        <v>-0.15180288255214691</v>
+        <v>-0.1518028825521469</v>
       </c>
       <c r="G8" s="1">
-        <v>6.6900743664630671</v>
+        <v>6.690074366463067</v>
       </c>
       <c r="H8" s="1">
         <v>0.4307093620300293</v>
       </c>
       <c r="I8" s="1">
-        <v>1.4307093677889202</v>
+        <v>1.43070936778892</v>
       </c>
       <c r="J8" s="1">
-        <v>4.6760540729541704</v>
+        <v>4.67605407295417</v>
       </c>
       <c r="K8" s="1"/>
     </row>
@@ -1203,28 +1203,28 @@
         <v>22</v>
       </c>
       <c r="B9" s="1">
-        <v>1.5279999971389771</v>
+        <v>1.527999997138977</v>
       </c>
       <c r="C9" s="1">
-        <v>1.4464571475982666</v>
+        <v>1.446457147598267</v>
       </c>
       <c r="D9" s="1">
-        <v>1.9822511014968154</v>
+        <v>1.982251101496815</v>
       </c>
       <c r="E9" s="1">
-        <v>1.3710674047470091</v>
+        <v>1.371067404747009</v>
       </c>
       <c r="F9" s="1">
-        <v>-0.19967468082904816</v>
+        <v>-0.1996746808290482</v>
       </c>
       <c r="G9" s="1">
-        <v>6.1281009961228596</v>
+        <v>6.12810099612286</v>
       </c>
       <c r="H9" s="1">
         <v>0.6061214804649353</v>
       </c>
       <c r="I9" s="1">
-        <v>1.6061214347280783</v>
+        <v>1.606121434728078</v>
       </c>
       <c r="J9" s="1">
         <v>3.815465545517962</v>
@@ -1239,28 +1239,28 @@
         <v>1</v>
       </c>
       <c r="C10" s="1">
-        <v>0.84013050794601441</v>
+        <v>0.8401305079460144</v>
       </c>
       <c r="D10" s="1">
-        <v>1.0811142380392549</v>
+        <v>1.081114238039255</v>
       </c>
       <c r="E10" s="1">
-        <v>0.86430245637893677</v>
+        <v>0.8643024563789368</v>
       </c>
       <c r="F10" s="1">
-        <v>-0.11597494035959244</v>
+        <v>-0.1159749403595924</v>
       </c>
       <c r="G10" s="1">
-        <v>3.6695722794360197</v>
+        <v>3.66957227943602</v>
       </c>
       <c r="H10" s="1">
-        <v>0.35329365730285645</v>
+        <v>0.3532936573028564</v>
       </c>
       <c r="I10" s="1">
-        <v>1.3532936397657145</v>
+        <v>1.353293639765714</v>
       </c>
       <c r="J10" s="1">
-        <v>2.7115861418452432</v>
+        <v>2.711586141845243</v>
       </c>
       <c r="K10" s="1"/>
     </row>
@@ -1272,22 +1272,22 @@
         <v>1</v>
       </c>
       <c r="C11" s="1">
-        <v>0.48056343197822571</v>
+        <v>0.4805634319782257</v>
       </c>
       <c r="D11" s="1">
-        <v>0.21600968704871831</v>
+        <v>0.2160096870487183</v>
       </c>
       <c r="E11" s="1">
-        <v>0.34557586908340449</v>
+        <v>0.3455758690834045</v>
       </c>
       <c r="F11" s="1">
-        <v>-0.066338881850242615</v>
+        <v>-0.06633888185024261</v>
       </c>
       <c r="G11" s="1">
-        <v>1.9758101144656826</v>
+        <v>1.975810114465683</v>
       </c>
       <c r="H11" s="1">
-        <v>0.20946536958217621</v>
+        <v>0.2094653695821762</v>
       </c>
       <c r="I11" s="1">
         <v>1.209465377795659</v>
@@ -1305,28 +1305,28 @@
         <v>1</v>
       </c>
       <c r="C12" s="1">
-        <v>0.088997833430767059</v>
+        <v>0.08899783343076706</v>
       </c>
       <c r="D12" s="1">
-        <v>0.073379440318946734</v>
+        <v>0.07337944031894673</v>
       </c>
       <c r="E12" s="1">
-        <v>0.45123902658621473</v>
+        <v>0.4512390265862147</v>
       </c>
       <c r="F12" s="1">
-        <v>-0.042789928615093231</v>
+        <v>-0.04278992861509323</v>
       </c>
       <c r="G12" s="1">
-        <v>1.5708263679494401</v>
+        <v>1.57082636794944</v>
       </c>
       <c r="H12" s="1">
-        <v>0.087150976061820984</v>
+        <v>0.08715097606182098</v>
       </c>
       <c r="I12" s="1">
-        <v>1.0871509725852866</v>
+        <v>1.087150972585287</v>
       </c>
       <c r="J12" s="1">
-        <v>1.4449018239974976</v>
+        <v>1.444901823997498</v>
       </c>
       <c r="K12" s="1">
         <v>1</v>
@@ -1340,22 +1340,22 @@
         <v>1</v>
       </c>
       <c r="C13" s="1">
-        <v>0.10679655522108078</v>
+        <v>0.1067965552210808</v>
       </c>
       <c r="D13" s="1">
-        <v>0.10275288153424859</v>
+        <v>0.1027528815342486</v>
       </c>
       <c r="E13" s="1">
-        <v>0.56318658590316773</v>
+        <v>0.5631865859031677</v>
       </c>
       <c r="F13" s="1">
-        <v>-0.051347509026527405</v>
+        <v>-0.0513475090265274</v>
       </c>
       <c r="G13" s="1">
-        <v>1.7213885109027161</v>
+        <v>1.721388510902716</v>
       </c>
       <c r="H13" s="1">
-        <v>0.10289375483989716</v>
+        <v>0.1028937548398972</v>
       </c>
       <c r="I13" s="1">
         <v>1.102893754428349</v>
@@ -1376,25 +1376,25 @@
         <v>0.09515073150396347</v>
       </c>
       <c r="D14" s="1">
-        <v>0.077734426990598501</v>
+        <v>0.0777344269905985</v>
       </c>
       <c r="E14" s="1">
-        <v>0.48161107301712042</v>
+        <v>0.4816110730171204</v>
       </c>
       <c r="F14" s="1">
-        <v>-0.045748230069875717</v>
+        <v>-0.04574823006987572</v>
       </c>
       <c r="G14" s="1">
         <v>1.608748003206723</v>
       </c>
       <c r="H14" s="1">
-        <v>0.091918006539344788</v>
+        <v>0.09191800653934479</v>
       </c>
       <c r="I14" s="1">
         <v>1.091918002728935</v>
       </c>
       <c r="J14" s="1">
-        <v>1.4733230876184109</v>
+        <v>1.473323087618411</v>
       </c>
       <c r="K14" s="1"/>
     </row>
@@ -1406,7 +1406,7 @@
         <v>1</v>
       </c>
       <c r="C15" s="1">
-        <v>0.065046206116676331</v>
+        <v>0.06504620611667633</v>
       </c>
       <c r="D15" s="1">
         <v>0.0396510124319931</v>
@@ -1421,13 +1421,13 @@
         <v>1.382342589738881</v>
       </c>
       <c r="H15" s="1">
-        <v>0.066641159355640411</v>
+        <v>0.06664115935564041</v>
       </c>
       <c r="I15" s="1">
         <v>1.066641160598576</v>
       </c>
       <c r="J15" s="1">
-        <v>1.2959771672069551</v>
+        <v>1.295977167206955</v>
       </c>
       <c r="K15" s="1"/>
     </row>
@@ -1436,10 +1436,10 @@
         <v>29</v>
       </c>
       <c r="B16" s="1">
-        <v>0.86747825145721436</v>
+        <v>0.8674782514572144</v>
       </c>
       <c r="C16" s="1">
-        <v>0.45064985752105713</v>
+        <v>0.4506498575210571</v>
       </c>
       <c r="D16" s="1">
         <v>0</v>
@@ -1448,19 +1448,19 @@
         <v>0</v>
       </c>
       <c r="F16" s="1">
-        <v>-0.10313244163990021</v>
+        <v>-0.1031324416399002</v>
       </c>
       <c r="G16" s="1">
-        <v>1.2149956659266381</v>
+        <v>1.214995665926638</v>
       </c>
       <c r="H16" s="1">
-        <v>0.043586790561676025</v>
+        <v>0.04358679056167603</v>
       </c>
       <c r="I16" s="1">
-        <v>1.0435867926298426</v>
+        <v>1.043586792629843</v>
       </c>
       <c r="J16" s="1">
-        <v>1.1642497777938843</v>
+        <v>1.164249777793884</v>
       </c>
       <c r="K16" s="1">
         <v>1.000000001580061</v>
@@ -1471,10 +1471,10 @@
         <v>30</v>
       </c>
       <c r="B17" s="1">
-        <v>0.95249998569488525</v>
+        <v>0.9524999856948853</v>
       </c>
       <c r="C17" s="1">
-        <v>0.50880336761474609</v>
+        <v>0.5088033676147461</v>
       </c>
       <c r="D17" s="1">
         <v>0</v>
@@ -1483,19 +1483,19 @@
         <v>0</v>
       </c>
       <c r="F17" s="1">
-        <v>-0.038752090185880661</v>
+        <v>-0.03875209018588066</v>
       </c>
       <c r="G17" s="1">
-        <v>1.4225512457028553</v>
+        <v>1.422551245702855</v>
       </c>
       <c r="H17" s="1">
-        <v>0.012415665201842785</v>
+        <v>0.01241566520184278</v>
       </c>
       <c r="I17" s="1">
-        <v>1.0124156586626045</v>
+        <v>1.012415658662605</v>
       </c>
       <c r="J17" s="1">
-        <v>1.4051059300900559</v>
+        <v>1.405105930090056</v>
       </c>
       <c r="K17" s="1"/>
     </row>
@@ -1504,10 +1504,10 @@
         <v>32</v>
       </c>
       <c r="B18" s="1">
-        <v>0.59782606363296509</v>
+        <v>0.5978260636329651</v>
       </c>
       <c r="C18" s="1">
-        <v>1.5059171915054321</v>
+        <v>1.505917191505432</v>
       </c>
       <c r="D18" s="1">
         <v>0</v>
@@ -1516,16 +1516,16 @@
         <v>0</v>
       </c>
       <c r="F18" s="1">
-        <v>-0.65867865085601807</v>
+        <v>-0.6586786508560181</v>
       </c>
       <c r="G18" s="1">
         <v>1.445064617251252</v>
       </c>
       <c r="H18" s="1">
-        <v>0.078375332057476044</v>
+        <v>0.07837533205747604</v>
       </c>
       <c r="I18" s="1">
-        <v>1.0783753039467419</v>
+        <v>1.078375303946742</v>
       </c>
       <c r="J18" s="1">
         <v>1.340038678521722</v>
@@ -1540,7 +1540,7 @@
         <v>1</v>
       </c>
       <c r="C19" s="1">
-        <v>0.79383164644241333</v>
+        <v>0.7938316464424133</v>
       </c>
       <c r="D19" s="1">
         <v>0</v>
@@ -1549,19 +1549,19 @@
         <v>0</v>
       </c>
       <c r="F19" s="1">
-        <v>-0.071863658726215363</v>
+        <v>-0.07186365872621536</v>
       </c>
       <c r="G19" s="1">
-        <v>1.7219679644381421</v>
+        <v>1.721967964438142</v>
       </c>
       <c r="H19" s="1">
-        <v>0.31483599543571472</v>
+        <v>0.3148359954357147</v>
       </c>
       <c r="I19" s="1">
         <v>1.314835995386064</v>
       </c>
       <c r="J19" s="1">
-        <v>1.3096446784851941</v>
+        <v>1.309644678485194</v>
       </c>
       <c r="K19" s="1"/>
     </row>
@@ -1570,10 +1570,10 @@
         <v>33</v>
       </c>
       <c r="B20" s="1">
-        <v>0.92949998378753662</v>
+        <v>0.9294999837875366</v>
       </c>
       <c r="C20" s="1">
-        <v>0.22539462149143219</v>
+        <v>0.2253946214914322</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
@@ -1582,16 +1582,16 @@
         <v>0</v>
       </c>
       <c r="F20" s="1">
-        <v>-0.016616303473711014</v>
+        <v>-0.01661630347371101</v>
       </c>
       <c r="G20" s="1">
-        <v>1.1382783503795941</v>
+        <v>1.138278350379594</v>
       </c>
       <c r="H20" s="1">
-        <v>0.0052036396227777004</v>
+        <v>0.0052036396227777</v>
       </c>
       <c r="I20" s="1">
-        <v>1.0052036704661302</v>
+        <v>1.00520367046613</v>
       </c>
       <c r="J20" s="1">
         <v>1.132385787898839</v>
@@ -1606,7 +1606,7 @@
         <v>1</v>
       </c>
       <c r="C21" s="1">
-        <v>-0.20532937347888947</v>
+        <v>-0.2053293734788895</v>
       </c>
       <c r="D21" s="1">
         <v>0</v>
@@ -1615,19 +1615,19 @@
         <v>0</v>
       </c>
       <c r="F21" s="1">
-        <v>0.018587972968816757</v>
+        <v>0.01858797296881676</v>
       </c>
       <c r="G21" s="1">
-        <v>0.81325859162791414</v>
+        <v>0.8132585916279141</v>
       </c>
       <c r="H21" s="1">
-        <v>-0.22795268893241882</v>
+        <v>-0.2279526889324188</v>
       </c>
       <c r="I21" s="1">
-        <v>0.77204729985662424</v>
+        <v>0.7720472998566242</v>
       </c>
       <c r="J21" s="1">
-        <v>1.0533792317892221</v>
+        <v>1.053379231789222</v>
       </c>
       <c r="K21" s="1"/>
     </row>
@@ -1636,7 +1636,7 @@
         <v>34</v>
       </c>
       <c r="B22" s="1">
-        <v>0.95999991893768311</v>
+        <v>0.9599999189376831</v>
       </c>
       <c r="C22" s="1">
         <v>0.09147227555513382</v>
@@ -1648,19 +1648,19 @@
         <v>0</v>
       </c>
       <c r="F22" s="1">
-        <v>-0.0071807135827839375</v>
+        <v>-0.007180713582783937</v>
       </c>
       <c r="G22" s="1">
         <v>1.044291550132193</v>
       </c>
       <c r="H22" s="1">
-        <v>0.0023472367320209742</v>
+        <v>0.002347236732020974</v>
       </c>
       <c r="I22" s="1">
-        <v>1.0023472245997365</v>
+        <v>1.002347224599736</v>
       </c>
       <c r="J22" s="1">
-        <v>1.0418461033293189</v>
+        <v>1.041846103329319</v>
       </c>
       <c r="K22" s="1"/>
     </row>
@@ -1672,7 +1672,7 @@
         <v>1</v>
       </c>
       <c r="C23" s="1">
-        <v>0.18327267467975616</v>
+        <v>0.1832726746797562</v>
       </c>
       <c r="D23" s="1">
         <v>0</v>
@@ -1681,19 +1681,19 @@
         <v>0</v>
       </c>
       <c r="F23" s="1">
-        <v>-0.016591232270002365</v>
+        <v>-0.01659123227000237</v>
       </c>
       <c r="G23" s="1">
         <v>1.166681438228496</v>
       </c>
       <c r="H23" s="1">
-        <v>0.15350914001464844</v>
+        <v>0.1535091400146484</v>
       </c>
       <c r="I23" s="1">
-        <v>1.1535091456387501</v>
+        <v>1.15350914563875</v>
       </c>
       <c r="J23" s="1">
-        <v>1.0114193221957091</v>
+        <v>1.011419322195709</v>
       </c>
       <c r="K23" s="1"/>
     </row>
@@ -1705,7 +1705,7 @@
         <v>0.5</v>
       </c>
       <c r="C24" s="1">
-        <v>0.50183641910552979</v>
+        <v>0.5018364191055298</v>
       </c>
       <c r="D24" s="1">
         <v>0</v>
@@ -1714,19 +1714,19 @@
         <v>0</v>
       </c>
       <c r="F24" s="1">
-        <v>-0.033964861184358597</v>
+        <v>-0.0339648611843586</v>
       </c>
       <c r="G24" s="1">
-        <v>0.96787156965265742</v>
+        <v>0.9678715696526574</v>
       </c>
       <c r="H24" s="1">
-        <v>0.0099600190296769142</v>
+        <v>0.009960019029676914</v>
       </c>
       <c r="I24" s="1">
-        <v>1.0099600424820896</v>
+        <v>1.00996004248209</v>
       </c>
       <c r="J24" s="1">
-        <v>0.95832659604433956</v>
+        <v>0.9583265960443396</v>
       </c>
       <c r="K24" s="1"/>
     </row>
@@ -1735,10 +1735,10 @@
         <v>38</v>
       </c>
       <c r="B25" s="1">
-        <v>0.91011238098144531</v>
+        <v>0.9101123809814453</v>
       </c>
       <c r="C25" s="1">
-        <v>0.24524000287055969</v>
+        <v>0.2452400028705597</v>
       </c>
       <c r="D25" s="1">
         <v>0</v>
@@ -1750,19 +1750,19 @@
         <v>-0.04927363246679306</v>
       </c>
       <c r="G25" s="1">
-        <v>1.1060787106407883</v>
+        <v>1.106078710640788</v>
       </c>
       <c r="H25" s="1">
-        <v>0.055976692587137222</v>
+        <v>0.05597669258713722</v>
       </c>
       <c r="I25" s="1">
-        <v>1.0559766608412027</v>
+        <v>1.055976660841203</v>
       </c>
       <c r="J25" s="1">
-        <v>1.0474461317062378</v>
+        <v>1.047446131706238</v>
       </c>
       <c r="K25" s="1">
-        <v>0.99999996930938362</v>
+        <v>0.9999999693093836</v>
       </c>
     </row>
     <row r="26">
@@ -1773,7 +1773,7 @@
         <v>1</v>
       </c>
       <c r="C26" s="1">
-        <v>0.23130065202713013</v>
+        <v>0.2313006520271301</v>
       </c>
       <c r="D26" s="1">
         <v>0</v>
@@ -1782,19 +1782,19 @@
         <v>0</v>
       </c>
       <c r="F26" s="1">
-        <v>-0.074098356068134308</v>
+        <v>-0.07409835606813431</v>
       </c>
       <c r="G26" s="1">
-        <v>1.1572022667202842</v>
+        <v>1.157202266720284</v>
       </c>
       <c r="H26" s="1">
-        <v>0.084411576390266419</v>
+        <v>0.08441157639026642</v>
       </c>
       <c r="I26" s="1">
-        <v>1.0844115428759953</v>
+        <v>1.084411542875995</v>
       </c>
       <c r="J26" s="1">
-        <v>1.0671246302406909</v>
+        <v>1.067124630240691</v>
       </c>
       <c r="K26" s="1"/>
     </row>
@@ -1806,7 +1806,7 @@
         <v>1</v>
       </c>
       <c r="C27" s="1">
-        <v>0.15072794258594513</v>
+        <v>0.1507279425859451</v>
       </c>
       <c r="D27" s="1">
         <v>0</v>
@@ -1815,16 +1815,16 @@
         <v>0</v>
       </c>
       <c r="F27" s="1">
-        <v>-0.048607338219881058</v>
+        <v>-0.04860733821988106</v>
       </c>
       <c r="G27" s="1">
-        <v>1.1021205763790709</v>
+        <v>1.102120576379071</v>
       </c>
       <c r="H27" s="1">
-        <v>0.055380899459123611</v>
+        <v>0.05538089945912361</v>
       </c>
       <c r="I27" s="1">
-        <v>1.0553808728927971</v>
+        <v>1.055380872892797</v>
       </c>
       <c r="J27" s="1">
         <v>1.044287048104406</v>
@@ -1836,10 +1836,10 @@
         <v>40</v>
       </c>
       <c r="B28" s="1">
-        <v>0.73033708333969116</v>
+        <v>0.7303370833396912</v>
       </c>
       <c r="C28" s="1">
-        <v>0.35369142889976501</v>
+        <v>0.353691428899765</v>
       </c>
       <c r="D28" s="1">
         <v>0</v>
@@ -1848,19 +1848,19 @@
         <v>0</v>
       </c>
       <c r="F28" s="1">
-        <v>-0.025115201249718666</v>
+        <v>-0.02511520124971867</v>
       </c>
       <c r="G28" s="1">
-        <v>1.0589132888230104</v>
+        <v>1.05891328882301</v>
       </c>
       <c r="H28" s="1">
-        <v>0.028137603774666786</v>
+        <v>0.02813760377466679</v>
       </c>
       <c r="I28" s="1">
-        <v>1.0281375667548163</v>
+        <v>1.028137566754816</v>
       </c>
       <c r="J28" s="1">
-        <v>1.0299334671383851</v>
+        <v>1.029933467138385</v>
       </c>
       <c r="K28" s="1"/>
     </row>
@@ -1872,28 +1872,28 @@
         <v>1</v>
       </c>
       <c r="C29" s="1">
-        <v>0.0081383399665355682</v>
+        <v>0.008138339966535568</v>
       </c>
       <c r="D29" s="1">
-        <v>0.00038802970722609341</v>
+        <v>0.0003880297072260934</v>
       </c>
       <c r="E29" s="1">
-        <v>0.013801508854764199</v>
+        <v>0.0138015088547642</v>
       </c>
       <c r="F29" s="1">
-        <v>-0.0064310827292501926</v>
+        <v>-0.006431082729250193</v>
       </c>
       <c r="G29" s="1">
-        <v>1.0158967958906851</v>
+        <v>1.015896795890685</v>
       </c>
       <c r="H29" s="1">
-        <v>0.0036839824169874191</v>
+        <v>0.003683982416987419</v>
       </c>
       <c r="I29" s="1">
-        <v>1.0036839825748389</v>
+        <v>1.003683982574839</v>
       </c>
       <c r="J29" s="1">
-        <v>1.0121679306030274</v>
+        <v>1.012167930603027</v>
       </c>
       <c r="K29" s="1">
         <v>1</v>
@@ -1910,19 +1910,19 @@
         <v>0.01809588260948658</v>
       </c>
       <c r="D30" s="1">
-        <v>0.0010730455552728001</v>
+        <v>0.0010730455552728</v>
       </c>
       <c r="E30" s="1">
-        <v>0.030820557847619098</v>
+        <v>0.0308205578476191</v>
       </c>
       <c r="F30" s="1">
-        <v>-0.014299736358225346</v>
+        <v>-0.01429973635822535</v>
       </c>
       <c r="G30" s="1">
-        <v>1.0356897493433741</v>
+        <v>1.035689749343374</v>
       </c>
       <c r="H30" s="1">
-        <v>0.0081832623109221458</v>
+        <v>0.008183262310922146</v>
       </c>
       <c r="I30" s="1">
         <v>1.008183262619448</v>
@@ -1940,16 +1940,16 @@
         <v>1</v>
       </c>
       <c r="C31" s="1">
-        <v>0.0051931971684098244</v>
+        <v>0.005193197168409824</v>
       </c>
       <c r="D31" s="1">
-        <v>8.6975447162100005e-05</v>
+        <v>8.69754471621e-05</v>
       </c>
       <c r="E31" s="1">
-        <v>0.0087058069184422007</v>
+        <v>0.008705806918442201</v>
       </c>
       <c r="F31" s="1">
-        <v>-0.0041037704795598984</v>
+        <v>-0.004103770479559898</v>
       </c>
       <c r="G31" s="1">
         <v>1.009882208940174</v>
@@ -1958,10 +1958,10 @@
         <v>0.002357069868594408</v>
       </c>
       <c r="I31" s="1">
-        <v>1.0023570699883759</v>
+        <v>1.002357069988376</v>
       </c>
       <c r="J31" s="1">
-        <v>1.0075074433823119</v>
+        <v>1.007507443382312</v>
       </c>
       <c r="K31" s="1"/>
     </row>
@@ -1973,28 +1973,28 @@
         <v>1</v>
       </c>
       <c r="C32" s="1">
-        <v>0.0011259414022788405</v>
+        <v>0.001125941402278841</v>
       </c>
       <c r="D32" s="1">
-        <v>4.0681192433799998e-06</v>
+        <v>4.06811924338e-06</v>
       </c>
       <c r="E32" s="1">
         <v>0.0018781617982313</v>
       </c>
       <c r="F32" s="1">
-        <v>-0.00088974187383428216</v>
+        <v>-0.0008897418738342822</v>
       </c>
       <c r="G32" s="1">
         <v>1.002118429388507</v>
       </c>
       <c r="H32" s="1">
-        <v>0.00051161512965336442</v>
+        <v>0.0005116151296533644</v>
       </c>
       <c r="I32" s="1">
-        <v>1.0005116151166931</v>
+        <v>1.000511615116693</v>
       </c>
       <c r="J32" s="1">
-        <v>1.0016059926217109</v>
+        <v>1.001605992621711</v>
       </c>
       <c r="K32" s="1"/>
     </row>
@@ -2003,10 +2003,10 @@
         <v>46</v>
       </c>
       <c r="B33" s="1">
-        <v>0.77409690618515015</v>
+        <v>0.7740969061851501</v>
       </c>
       <c r="C33" s="1">
-        <v>0.26917135715484619</v>
+        <v>0.2691713571548462</v>
       </c>
       <c r="D33" s="1">
         <v>0</v>
@@ -2015,19 +2015,19 @@
         <v>0</v>
       </c>
       <c r="F33" s="1">
-        <v>-0.054134722799062729</v>
+        <v>-0.05413472279906273</v>
       </c>
       <c r="G33" s="1">
-        <v>0.98913354702332623</v>
+        <v>0.9891335470233262</v>
       </c>
       <c r="H33" s="1">
-        <v>0.011765440925955772</v>
+        <v>0.01176544092595577</v>
       </c>
       <c r="I33" s="1">
-        <v>1.0117654359252968</v>
+        <v>1.011765435925297</v>
       </c>
       <c r="J33" s="1">
-        <v>0.97763127088546753</v>
+        <v>0.9776312708854675</v>
       </c>
       <c r="K33" s="1">
         <v>0.9999999950671693</v>
@@ -2038,7 +2038,7 @@
         <v>47</v>
       </c>
       <c r="B34" s="1">
-        <v>0.75000005960464478</v>
+        <v>0.7500000596046448</v>
       </c>
       <c r="C34" s="1">
         <v>0.5441010594367981</v>
@@ -2050,16 +2050,16 @@
         <v>0</v>
       </c>
       <c r="F34" s="1">
-        <v>-0.057457782328128815</v>
+        <v>-0.05745778232812881</v>
       </c>
       <c r="G34" s="1">
-        <v>1.2366432741013118</v>
+        <v>1.236643274101312</v>
       </c>
       <c r="H34" s="1">
-        <v>0.021893683820962906</v>
+        <v>0.02189368382096291</v>
       </c>
       <c r="I34" s="1">
-        <v>1.0218937155935541</v>
+        <v>1.021893715593554</v>
       </c>
       <c r="J34" s="1">
         <v>1.210148624295065</v>
@@ -2074,7 +2074,7 @@
         <v>0.75</v>
       </c>
       <c r="C35" s="1">
-        <v>0.35916638374328613</v>
+        <v>0.3591663837432861</v>
       </c>
       <c r="D35" s="1">
         <v>0</v>
@@ -2083,19 +2083,19 @@
         <v>0</v>
       </c>
       <c r="F35" s="1">
-        <v>-0.11058589816093445</v>
+        <v>-0.1105858981609344</v>
       </c>
       <c r="G35" s="1">
-        <v>0.99858047512384651</v>
+        <v>0.9985804751238465</v>
       </c>
       <c r="H35" s="1">
-        <v>0.018769737333059311</v>
+        <v>0.01876973733305931</v>
       </c>
       <c r="I35" s="1">
-        <v>1.0187697066148542</v>
+        <v>1.018769706614854</v>
       </c>
       <c r="J35" s="1">
-        <v>0.98018273280023993</v>
+        <v>0.9801827328002399</v>
       </c>
       <c r="K35" s="1"/>
     </row>
@@ -2104,10 +2104,10 @@
         <v>51</v>
       </c>
       <c r="B36" s="1">
-        <v>0.87048459053039551</v>
+        <v>0.8704845905303955</v>
       </c>
       <c r="C36" s="1">
-        <v>0.050162136554718018</v>
+        <v>0.05016213655471802</v>
       </c>
       <c r="D36" s="1">
         <v>0</v>
@@ -2116,19 +2116,19 @@
         <v>0</v>
       </c>
       <c r="F36" s="1">
-        <v>-0.0010530698345974088</v>
+        <v>-0.001053069834597409</v>
       </c>
       <c r="G36" s="1">
-        <v>0.91959365171861429</v>
+        <v>0.9195936517186143</v>
       </c>
       <c r="H36" s="1">
-        <v>-0.00023865627008490265</v>
+        <v>-0.0002386562700849026</v>
       </c>
       <c r="I36" s="1">
-        <v>0.99976134696391983</v>
+        <v>0.9997613469639198</v>
       </c>
       <c r="J36" s="1">
-        <v>0.91981316792376577</v>
+        <v>0.9198131679237658</v>
       </c>
       <c r="K36" s="1"/>
     </row>
@@ -2137,10 +2137,10 @@
         <v>49</v>
       </c>
       <c r="B37" s="1">
-        <v>0.75000005960464478</v>
+        <v>0.7500000596046448</v>
       </c>
       <c r="C37" s="1">
-        <v>0.26548650860786438</v>
+        <v>0.2654865086078644</v>
       </c>
       <c r="D37" s="1">
         <v>0</v>
@@ -2152,16 +2152,16 @@
         <v>-0.08817175030708313</v>
       </c>
       <c r="G37" s="1">
-        <v>0.92731475296377719</v>
+        <v>0.9273147529637772</v>
       </c>
       <c r="H37" s="1">
-        <v>0.013294565491378307</v>
+        <v>0.01329456549137831</v>
       </c>
       <c r="I37" s="1">
-        <v>1.0132945673246929</v>
+        <v>1.013294567324693</v>
       </c>
       <c r="J37" s="1">
-        <v>0.91514825290347679</v>
+        <v>0.9151482529034768</v>
       </c>
       <c r="K37" s="1"/>
     </row>
@@ -2170,10 +2170,10 @@
         <v>50</v>
       </c>
       <c r="B38" s="1">
-        <v>0.74999994039535523</v>
+        <v>0.7499999403953552</v>
       </c>
       <c r="C38" s="1">
-        <v>0.12694071233272552</v>
+        <v>0.1269407123327255</v>
       </c>
       <c r="D38" s="1">
         <v>0</v>
@@ -2182,19 +2182,19 @@
         <v>0</v>
       </c>
       <c r="F38" s="1">
-        <v>-0.013405105099081993</v>
+        <v>-0.01340510509908199</v>
       </c>
       <c r="G38" s="1">
-        <v>0.86353558120908203</v>
+        <v>0.863535581209082</v>
       </c>
       <c r="H38" s="1">
-        <v>0.0051078745163977146</v>
+        <v>0.005107874516397715</v>
       </c>
       <c r="I38" s="1">
-        <v>1.0051078431294624</v>
+        <v>1.005107843129462</v>
       </c>
       <c r="J38" s="1">
-        <v>0.85914719212658119</v>
+        <v>0.8591471921265812</v>
       </c>
       <c r="K38" s="1"/>
     </row>
@@ -2203,10 +2203,10 @@
         <v>52</v>
       </c>
       <c r="B39" s="1">
-        <v>0.88749003410339355</v>
+        <v>0.8874900341033936</v>
       </c>
       <c r="C39" s="1">
-        <v>1.6949977874755859</v>
+        <v>1.694997787475586</v>
       </c>
       <c r="D39" s="1">
         <v>0</v>
@@ -2215,22 +2215,22 @@
         <v>0</v>
       </c>
       <c r="F39" s="1">
-        <v>-0.065373122692108154</v>
+        <v>-0.06537312269210815</v>
       </c>
       <c r="G39" s="1">
-        <v>2.5171147370560494</v>
+        <v>2.517114737056049</v>
       </c>
       <c r="H39" s="1">
-        <v>0.010128799825906754</v>
+        <v>0.01012879982590675</v>
       </c>
       <c r="I39" s="1">
-        <v>1.0101287888325596</v>
+        <v>1.01012878883256</v>
       </c>
       <c r="J39" s="1">
         <v>2.491875171661377</v>
       </c>
       <c r="K39" s="1">
-        <v>0.99999999092758574</v>
+        <v>0.9999999909275857</v>
       </c>
     </row>
     <row r="40">
@@ -2238,10 +2238,10 @@
         <v>53</v>
       </c>
       <c r="B40" s="1">
-        <v>0.88212293386459351</v>
+        <v>0.8821229338645935</v>
       </c>
       <c r="C40" s="1">
-        <v>1.9194022417068481</v>
+        <v>1.919402241706848</v>
       </c>
       <c r="D40" s="1">
         <v>0</v>
@@ -2250,16 +2250,16 @@
         <v>0</v>
       </c>
       <c r="F40" s="1">
-        <v>-0.13074624538421631</v>
+        <v>-0.1307462453842163</v>
       </c>
       <c r="G40" s="1">
         <v>2.670778997480296</v>
       </c>
       <c r="H40" s="1">
-        <v>0.038204580545425415</v>
+        <v>0.03820458054542542</v>
       </c>
       <c r="I40" s="1">
-        <v>1.0382045589970401</v>
+        <v>1.03820455899704</v>
       </c>
       <c r="J40" s="1">
         <v>2.572497851541327</v>
@@ -2271,10 +2271,10 @@
         <v>54</v>
       </c>
       <c r="B41" s="1">
-        <v>0.89285707473754883</v>
+        <v>0.8928570747375488</v>
       </c>
       <c r="C41" s="1">
-        <v>1.4705933332443237</v>
+        <v>1.470593333244324</v>
       </c>
       <c r="D41" s="1">
         <v>0</v>
@@ -2286,16 +2286,16 @@
         <v>0</v>
       </c>
       <c r="G41" s="1">
-        <v>2.3634504766318023</v>
+        <v>2.363450476631802</v>
       </c>
       <c r="H41" s="1">
-        <v>-0.017946980893611908</v>
+        <v>-0.01794698089361191</v>
       </c>
       <c r="I41" s="1">
-        <v>0.98205301866807893</v>
+        <v>0.9820530186680789</v>
       </c>
       <c r="J41" s="1">
-        <v>2.4066424436404259</v>
+        <v>2.406642443640426</v>
       </c>
       <c r="K41" s="1"/>
     </row>
@@ -2307,7 +2307,7 @@
         <v>0</v>
       </c>
       <c r="C42" s="1">
-        <v>1.8760761022567749</v>
+        <v>1.876076102256775</v>
       </c>
       <c r="D42" s="1">
         <v>0</v>
@@ -2316,22 +2316,22 @@
         <v>0</v>
       </c>
       <c r="F42" s="1">
-        <v>-0.030173782259225845</v>
+        <v>-0.03017378225922585</v>
       </c>
       <c r="G42" s="1">
-        <v>1.8459022823447036</v>
+        <v>1.845902282344704</v>
       </c>
       <c r="H42" s="1">
         <v>-0.05101698637008667</v>
       </c>
       <c r="I42" s="1">
-        <v>0.94898300331981866</v>
+        <v>0.9489830033198187</v>
       </c>
       <c r="J42" s="1">
-        <v>1.9451373815536499</v>
+        <v>1.94513738155365</v>
       </c>
       <c r="K42" s="1">
-        <v>0.99999999373325155</v>
+        <v>0.9999999937332515</v>
       </c>
     </row>
     <row r="43">
@@ -2342,7 +2342,7 @@
         <v>0</v>
       </c>
       <c r="C43" s="1">
-        <v>3.4663870334625244</v>
+        <v>3.466387033462524</v>
       </c>
       <c r="D43" s="1">
         <v>0</v>
@@ -2351,19 +2351,19 @@
         <v>0</v>
       </c>
       <c r="F43" s="1">
-        <v>-0.24427735805511475</v>
+        <v>-0.2442773580551147</v>
       </c>
       <c r="G43" s="1">
-        <v>3.2221095866315883</v>
+        <v>3.222109586631588</v>
       </c>
       <c r="H43" s="1">
-        <v>0.071891963481903076</v>
+        <v>0.07189196348190308</v>
       </c>
       <c r="I43" s="1">
-        <v>1.0718919172648322</v>
+        <v>1.071891917264832</v>
       </c>
       <c r="J43" s="1">
-        <v>3.0060023167760321</v>
+        <v>3.006002316776032</v>
       </c>
       <c r="K43" s="1"/>
     </row>
@@ -2375,7 +2375,7 @@
         <v>0</v>
       </c>
       <c r="C44" s="1">
-        <v>2.9060337543487549</v>
+        <v>2.906033754348755</v>
       </c>
       <c r="D44" s="1">
         <v>0</v>
@@ -2384,19 +2384,19 @@
         <v>0</v>
       </c>
       <c r="F44" s="1">
-        <v>-0.20478908717632294</v>
+        <v>-0.2047890871763229</v>
       </c>
       <c r="G44" s="1">
-        <v>2.7012446898909319</v>
+        <v>2.701244689890932</v>
       </c>
       <c r="H44" s="1">
-        <v>0.060270372778177261</v>
+        <v>0.06027037277817726</v>
       </c>
       <c r="I44" s="1">
         <v>1.060270363576397</v>
       </c>
       <c r="J44" s="1">
-        <v>2.5476942322327729</v>
+        <v>2.547694232232773</v>
       </c>
       <c r="K44" s="1"/>
     </row>
@@ -2408,7 +2408,7 @@
         <v>0</v>
       </c>
       <c r="C45" s="1">
-        <v>0.29357260465621948</v>
+        <v>0.2935726046562195</v>
       </c>
       <c r="D45" s="1">
         <v>0</v>
@@ -2417,16 +2417,16 @@
         <v>0</v>
       </c>
       <c r="F45" s="1">
-        <v>0.69504320621490479</v>
+        <v>0.6950432062149048</v>
       </c>
       <c r="G45" s="1">
-        <v>0.98861578807241179</v>
+        <v>0.9886157880724118</v>
       </c>
       <c r="H45" s="1">
-        <v>-0.38204297423362732</v>
+        <v>-0.3820429742336273</v>
       </c>
       <c r="I45" s="1">
-        <v>0.61795700982480406</v>
+        <v>0.6179570098248041</v>
       </c>
       <c r="J45" s="1">
         <v>1.599813210878039</v>
@@ -2441,7 +2441,7 @@
         <v>0</v>
       </c>
       <c r="C46" s="1">
-        <v>0.83831095695495605</v>
+        <v>0.8383109569549561</v>
       </c>
       <c r="D46" s="1">
         <v>0</v>
@@ -2450,19 +2450,19 @@
         <v>0</v>
       </c>
       <c r="F46" s="1">
-        <v>-0.36667189002037048</v>
+        <v>-0.3666718900203705</v>
       </c>
       <c r="G46" s="1">
-        <v>0.47163906478388201</v>
+        <v>0.471639064783882</v>
       </c>
       <c r="H46" s="1">
-        <v>0.045812685042619705</v>
+        <v>0.04581268504261971</v>
       </c>
       <c r="I46" s="1">
         <v>1.045812722613241</v>
       </c>
       <c r="J46" s="1">
-        <v>0.45097851133935962</v>
+        <v>0.4509785113393596</v>
       </c>
       <c r="K46" s="1"/>
     </row>
@@ -2471,7 +2471,7 @@
         <v>60</v>
       </c>
       <c r="B47" s="1">
-        <v>0.50691342353820801</v>
+        <v>0.506913423538208</v>
       </c>
       <c r="C47" s="1">
         <v>4.350517749786377</v>
@@ -2483,22 +2483,22 @@
         <v>0</v>
       </c>
       <c r="F47" s="1">
-        <v>-0.65891975164413452</v>
+        <v>-0.6589197516441345</v>
       </c>
       <c r="G47" s="1">
-        <v>4.1985114305085389</v>
+        <v>4.198511430508539</v>
       </c>
       <c r="H47" s="1">
-        <v>2.1667380332946777</v>
+        <v>2.166738033294678</v>
       </c>
       <c r="I47" s="1">
         <v>3.166738061842937</v>
       </c>
       <c r="J47" s="1">
-        <v>1.3258157968521118</v>
+        <v>1.325815796852112</v>
       </c>
       <c r="K47" s="1">
-        <v>1.0000000063824837</v>
+        <v>1.000000006382484</v>
       </c>
     </row>
     <row r="48">
@@ -2509,7 +2509,7 @@
         <v>0</v>
       </c>
       <c r="C48" s="1">
-        <v>8.0499057769775391</v>
+        <v>8.049905776977539</v>
       </c>
       <c r="D48" s="1">
         <v>0</v>
@@ -2518,19 +2518,19 @@
         <v>0</v>
       </c>
       <c r="F48" s="1">
-        <v>-0.54240739345550537</v>
+        <v>-0.5424073934555054</v>
       </c>
       <c r="G48" s="1">
-        <v>7.5074983877944215</v>
+        <v>7.507498387794421</v>
       </c>
       <c r="H48" s="1">
-        <v>2.5465481281280518</v>
+        <v>2.546548128128052</v>
       </c>
       <c r="I48" s="1">
-        <v>3.5465480368609774</v>
+        <v>3.546548036860977</v>
       </c>
       <c r="J48" s="1">
-        <v>2.1168466660441041</v>
+        <v>2.116846666044104</v>
       </c>
       <c r="K48" s="1"/>
     </row>
@@ -2539,10 +2539,10 @@
         <v>61</v>
       </c>
       <c r="B49" s="1">
-        <v>1.1445080041885376</v>
+        <v>1.144508004188538</v>
       </c>
       <c r="C49" s="1">
-        <v>13.524042129516602</v>
+        <v>13.5240421295166</v>
       </c>
       <c r="D49" s="1">
         <v>0</v>
@@ -2551,19 +2551,19 @@
         <v>0</v>
       </c>
       <c r="F49" s="1">
-        <v>-1.8443533182144165</v>
+        <v>-1.844353318214417</v>
       </c>
       <c r="G49" s="1">
-        <v>12.824197040698165</v>
+        <v>12.82419704069816</v>
       </c>
       <c r="H49" s="1">
-        <v>6.0909366607666016</v>
+        <v>6.090936660766602</v>
       </c>
       <c r="I49" s="1">
-        <v>7.0909369231712276</v>
+        <v>7.090936923171228</v>
       </c>
       <c r="J49" s="1">
-        <v>1.8085335096963311</v>
+        <v>1.808533509696331</v>
       </c>
       <c r="K49" s="1"/>
     </row>
@@ -2572,10 +2572,10 @@
         <v>63</v>
       </c>
       <c r="B50" s="1">
-        <v>0.41578948497772217</v>
+        <v>0.4157894849777222</v>
       </c>
       <c r="C50" s="1">
-        <v>1.4386543035507202</v>
+        <v>1.43865430355072</v>
       </c>
       <c r="D50" s="1">
         <v>0</v>
@@ -2584,16 +2584,16 @@
         <v>0</v>
       </c>
       <c r="F50" s="1">
-        <v>-0.62925827503204346</v>
+        <v>-0.6292582750320435</v>
       </c>
       <c r="G50" s="1">
-        <v>1.2251855399546887</v>
+        <v>1.225185539954689</v>
       </c>
       <c r="H50" s="1">
-        <v>0.074874639511108399</v>
+        <v>0.0748746395111084</v>
       </c>
       <c r="I50" s="1">
-        <v>1.0748746572441301</v>
+        <v>1.07487465724413</v>
       </c>
       <c r="J50" s="1">
         <v>1.139840382036674</v>
@@ -2605,7 +2605,7 @@
         <v>64</v>
       </c>
       <c r="B51" s="1">
-        <v>0.73860436677932739</v>
+        <v>0.7386043667793274</v>
       </c>
       <c r="C51" s="1">
         <v>0.4515421986579895</v>
@@ -2617,16 +2617,16 @@
         <v>0</v>
       </c>
       <c r="F51" s="1">
-        <v>-0.10469947755336761</v>
+        <v>-0.1046994775533676</v>
       </c>
       <c r="G51" s="1">
-        <v>1.0854470716582245</v>
+        <v>1.085447071658225</v>
       </c>
       <c r="H51" s="1">
-        <v>0.014980290085077286</v>
+        <v>0.01498029008507729</v>
       </c>
       <c r="I51" s="1">
-        <v>1.0149802849140723</v>
+        <v>1.014980284914072</v>
       </c>
       <c r="J51" s="1">
         <v>1.06942675418579</v>
@@ -2638,10 +2638,10 @@
         <v>65</v>
       </c>
       <c r="B52" s="1">
-        <v>0.74257856607437134</v>
+        <v>0.7425785660743713</v>
       </c>
       <c r="C52" s="1">
-        <v>0.43616145849227905</v>
+        <v>0.4361614584922791</v>
       </c>
       <c r="D52" s="1">
         <v>0</v>
@@ -2650,16 +2650,16 @@
         <v>0</v>
       </c>
       <c r="F52" s="1">
-        <v>-0.10121941566467285</v>
+        <v>-0.1012194156646729</v>
       </c>
       <c r="G52" s="1">
-        <v>1.0775206134819309</v>
+        <v>1.077520613481931</v>
       </c>
       <c r="H52" s="1">
-        <v>0.014169283211231232</v>
+        <v>0.01416928321123123</v>
       </c>
       <c r="I52" s="1">
-        <v>1.0141692889899752</v>
+        <v>1.014169288989975</v>
       </c>
       <c r="J52" s="1">
         <v>1.062466222532777</v>
@@ -2674,7 +2674,7 @@
         <v>0</v>
       </c>
       <c r="C53" s="1">
-        <v>2.2028005123138428</v>
+        <v>2.202800512313843</v>
       </c>
       <c r="D53" s="1">
         <v>0</v>
@@ -2683,16 +2683,16 @@
         <v>0</v>
       </c>
       <c r="F53" s="1">
-        <v>-0.73158061504364014</v>
+        <v>-0.7315806150436401</v>
       </c>
       <c r="G53" s="1">
-        <v>1.4712199294638038</v>
+        <v>1.471219929463804</v>
       </c>
       <c r="H53" s="1">
-        <v>4.2589192390441895</v>
+        <v>4.258919239044189</v>
       </c>
       <c r="I53" s="1">
-        <v>5.2589191798772408</v>
+        <v>5.258919179877241</v>
       </c>
       <c r="J53" s="1">
         <v>0.2797570906001538</v>
@@ -2707,28 +2707,28 @@
         <v>1</v>
       </c>
       <c r="C54" s="1">
-        <v>-0.43251758813858032</v>
+        <v>-0.4325175881385803</v>
       </c>
       <c r="D54" s="1">
-        <v>-0.00024505497117680003</v>
+        <v>-0.0002450549711768</v>
       </c>
       <c r="E54" s="1">
-        <v>-0.0019315717316659004</v>
+        <v>-0.0019315717316659</v>
       </c>
       <c r="F54" s="1">
-        <v>0.059814266860485077</v>
+        <v>0.05981426686048508</v>
       </c>
       <c r="G54" s="1">
         <v>0.625120042656791</v>
       </c>
       <c r="H54" s="1">
-        <v>-0.069056332111358643</v>
+        <v>-0.06905633211135864</v>
       </c>
       <c r="I54" s="1">
-        <v>0.93094366875917156</v>
+        <v>0.9309436687591716</v>
       </c>
       <c r="J54" s="1">
-        <v>0.67149072885513306</v>
+        <v>0.6714907288551331</v>
       </c>
       <c r="K54" s="1">
         <v>1</v>
@@ -2742,28 +2742,28 @@
         <v>1</v>
       </c>
       <c r="C55" s="1">
-        <v>-0.70757150650024414</v>
+        <v>-0.7075715065002441</v>
       </c>
       <c r="D55" s="1">
-        <v>-0.00024505497117679998</v>
+        <v>-0.0002450549711768</v>
       </c>
       <c r="E55" s="1">
-        <v>-0.0019315717316658999</v>
+        <v>-0.0019315717316659</v>
       </c>
       <c r="F55" s="1">
-        <v>0.097820498049259186</v>
+        <v>0.09782049804925919</v>
       </c>
       <c r="G55" s="1">
-        <v>0.38807237697991642</v>
+        <v>0.3880723769799164</v>
       </c>
       <c r="H55" s="1">
         <v>-0.1128244623541832</v>
       </c>
       <c r="I55" s="1">
-        <v>0.88717553696826357</v>
+        <v>0.8871755369682636</v>
       </c>
       <c r="J55" s="1">
-        <v>0.43742456910621369</v>
+        <v>0.4374245691062137</v>
       </c>
       <c r="K55" s="1"/>
     </row>
@@ -2775,28 +2775,28 @@
         <v>1</v>
       </c>
       <c r="C56" s="1">
-        <v>-0.61056160926818848</v>
+        <v>-0.6105616092681885</v>
       </c>
       <c r="D56" s="1">
-        <v>-0.00024505497117679998</v>
+        <v>-0.0002450549711768</v>
       </c>
       <c r="E56" s="1">
-        <v>-0.0019315717316658999</v>
+        <v>-0.0019315717316659</v>
       </c>
       <c r="F56" s="1">
-        <v>0.084415920078754425</v>
+        <v>0.08441592007875443</v>
       </c>
       <c r="G56" s="1">
-        <v>0.47167771183026291</v>
+        <v>0.4716777118302629</v>
       </c>
       <c r="H56" s="1">
-        <v>-0.097387701272964478</v>
+        <v>-0.09738770127296448</v>
       </c>
       <c r="I56" s="1">
-        <v>0.90261230283433613</v>
+        <v>0.9026123028343361</v>
       </c>
       <c r="J56" s="1">
-        <v>0.52256955765961211</v>
+        <v>0.5225695576596121</v>
       </c>
       <c r="K56" s="1"/>
     </row>
@@ -2808,28 +2808,28 @@
         <v>1</v>
       </c>
       <c r="C57" s="1">
-        <v>-0.56590622663497925</v>
+        <v>-0.5659062266349792</v>
       </c>
       <c r="D57" s="1">
-        <v>-0.00024505497117679998</v>
+        <v>-0.0002450549711768</v>
       </c>
       <c r="E57" s="1">
-        <v>-0.0019315717316658999</v>
+        <v>-0.0019315717316659</v>
       </c>
       <c r="F57" s="1">
-        <v>0.078245557844638824</v>
+        <v>0.07824555784463882</v>
       </c>
       <c r="G57" s="1">
-        <v>0.51016270723756463</v>
+        <v>0.5101627072375646</v>
       </c>
       <c r="H57" s="1">
-        <v>-0.090281888842582703</v>
+        <v>-0.0902818888425827</v>
       </c>
       <c r="I57" s="1">
-        <v>0.90971811569332184</v>
+        <v>0.9097181156933218</v>
       </c>
       <c r="J57" s="1">
-        <v>0.56079207222201488</v>
+        <v>0.5607920722220149</v>
       </c>
       <c r="K57" s="1"/>
     </row>
@@ -2841,13 +2841,13 @@
         <v>1</v>
       </c>
       <c r="C58" s="1">
-        <v>-0.54588830471038818</v>
+        <v>-0.5458883047103882</v>
       </c>
       <c r="D58" s="1">
-        <v>-0.00024505497117679998</v>
+        <v>-0.0002450549711768</v>
       </c>
       <c r="E58" s="1">
-        <v>-0.0019315717316658999</v>
+        <v>-0.0019315717316659</v>
       </c>
       <c r="F58" s="1">
         <v>0.07547953724861145</v>
@@ -2856,13 +2856,13 @@
         <v>0.5274146017304937</v>
       </c>
       <c r="H58" s="1">
-        <v>-0.087096519768238068</v>
+        <v>-0.08709651976823807</v>
       </c>
       <c r="I58" s="1">
         <v>0.9129034800783844</v>
       </c>
       <c r="J58" s="1">
-        <v>0.57773314839944356</v>
+        <v>0.5777331483994436</v>
       </c>
       <c r="K58" s="1"/>
     </row>
@@ -2874,25 +2874,25 @@
         <v>1</v>
       </c>
       <c r="C59" s="1">
-        <v>-0.51355165243148804</v>
+        <v>-0.513551652431488</v>
       </c>
       <c r="D59" s="1">
-        <v>-0.00024505497117679998</v>
+        <v>-0.0002450549711768</v>
       </c>
       <c r="E59" s="1">
-        <v>-0.0019315717316658999</v>
+        <v>-0.0019315717316659</v>
       </c>
       <c r="F59" s="1">
-        <v>0.071011342108249664</v>
+        <v>0.07101134210824966</v>
       </c>
       <c r="G59" s="1">
         <v>0.5552830466806089</v>
       </c>
       <c r="H59" s="1">
-        <v>-0.081950932741165161</v>
+        <v>-0.08195093274116516</v>
       </c>
       <c r="I59" s="1">
-        <v>0.91804906870040848</v>
+        <v>0.9180490687004085</v>
       </c>
       <c r="J59" s="1">
         <v>0.6048511627670059</v>
@@ -2907,28 +2907,28 @@
         <v>1</v>
       </c>
       <c r="C60" s="1">
-        <v>-0.49661344289779663</v>
+        <v>-0.4966134428977966</v>
       </c>
       <c r="D60" s="1">
-        <v>-0.00024505497117679998</v>
+        <v>-0.0002450549711768</v>
       </c>
       <c r="E60" s="1">
-        <v>-0.0019315717316658999</v>
+        <v>-0.0019315717316659</v>
       </c>
       <c r="F60" s="1">
-        <v>0.068670861423015594</v>
+        <v>0.06867086142301559</v>
       </c>
       <c r="G60" s="1">
-        <v>0.56988080355924098</v>
+        <v>0.569880803559241</v>
       </c>
       <c r="H60" s="1">
-        <v>-0.079255625605583191</v>
+        <v>-0.07925562560558319</v>
       </c>
       <c r="I60" s="1">
         <v>0.9207443770262308</v>
       </c>
       <c r="J60" s="1">
-        <v>0.61893487245592571</v>
+        <v>0.6189348724559257</v>
       </c>
       <c r="K60" s="1"/>
     </row>
@@ -2940,25 +2940,25 @@
         <v>1</v>
       </c>
       <c r="C61" s="1">
-        <v>-0.45349791646003723</v>
+        <v>-0.4534979164600372</v>
       </c>
       <c r="D61" s="1">
-        <v>-0.00024505497117679998</v>
+        <v>-0.0002450549711768</v>
       </c>
       <c r="E61" s="1">
-        <v>-0.0019315717316658999</v>
+        <v>-0.0019315717316659</v>
       </c>
       <c r="F61" s="1">
-        <v>0.062713272869586945</v>
+        <v>0.06271327286958694</v>
       </c>
       <c r="G61" s="1">
-        <v>0.60703873015939502</v>
+        <v>0.607038730159395</v>
       </c>
       <c r="H61" s="1">
         <v>-0.07239484041929245</v>
       </c>
       <c r="I61" s="1">
-        <v>0.92760516185559638</v>
+        <v>0.9276051618555964</v>
       </c>
       <c r="J61" s="1">
         <v>0.6544149980203483</v>
@@ -2976,25 +2976,25 @@
         <v>-0.4304003119468689</v>
       </c>
       <c r="D62" s="1">
-        <v>-0.00024505497117679998</v>
+        <v>-0.0002450549711768</v>
       </c>
       <c r="E62" s="1">
-        <v>-0.0019315717316658999</v>
+        <v>-0.0019315717316659</v>
       </c>
       <c r="F62" s="1">
-        <v>0.059521708637475968</v>
+        <v>0.05952170863747597</v>
       </c>
       <c r="G62" s="1">
-        <v>0.62694476226661988</v>
+        <v>0.6269447622666199</v>
       </c>
       <c r="H62" s="1">
-        <v>-0.068719416856765747</v>
+        <v>-0.06871941685676575</v>
       </c>
       <c r="I62" s="1">
         <v>0.9312805822998993</v>
       </c>
       <c r="J62" s="1">
-        <v>0.67320716675774683</v>
+        <v>0.6732071667577468</v>
       </c>
       <c r="K62" s="1"/>
     </row>
@@ -3006,28 +3006,28 @@
         <v>1</v>
       </c>
       <c r="C63" s="1">
-        <v>-0.30413344502449036</v>
+        <v>-0.3041334450244904</v>
       </c>
       <c r="D63" s="1">
-        <v>-0.00024505497117679998</v>
+        <v>-0.0002450549711768</v>
       </c>
       <c r="E63" s="1">
-        <v>-0.0019315717316658999</v>
+        <v>-0.0019315717316659</v>
       </c>
       <c r="F63" s="1">
-        <v>0.042074479162693024</v>
+        <v>0.04207447916269302</v>
       </c>
       <c r="G63" s="1">
-        <v>0.73576440445278524</v>
+        <v>0.7357644044527852</v>
       </c>
       <c r="H63" s="1">
-        <v>-0.048627115786075592</v>
+        <v>-0.04862711578607559</v>
       </c>
       <c r="I63" s="1">
-        <v>0.95137288072875559</v>
+        <v>0.9513728807287556</v>
       </c>
       <c r="J63" s="1">
-        <v>0.77337121895800376</v>
+        <v>0.7733712189580038</v>
       </c>
       <c r="K63" s="1"/>
     </row>
@@ -3039,28 +3039,28 @@
         <v>1</v>
       </c>
       <c r="C64" s="1">
-        <v>-0.25177890062332153</v>
+        <v>-0.2517789006233215</v>
       </c>
       <c r="D64" s="1">
-        <v>-0.00024505497117679998</v>
+        <v>-0.0002450549711768</v>
       </c>
       <c r="E64" s="1">
-        <v>-0.0019315717316658999</v>
+        <v>-0.0019315717316659</v>
       </c>
       <c r="F64" s="1">
-        <v>0.034840263426303864</v>
+        <v>0.03484026342630386</v>
       </c>
       <c r="G64" s="1">
-        <v>0.78088474389582918</v>
+        <v>0.7808847438958292</v>
       </c>
       <c r="H64" s="1">
-        <v>-0.040296163409948349</v>
+        <v>-0.04029616340994835</v>
       </c>
       <c r="I64" s="1">
-        <v>0.95970383373584212</v>
+        <v>0.9597038337358421</v>
       </c>
       <c r="J64" s="1">
-        <v>0.81367263154100022</v>
+        <v>0.8136726315410002</v>
       </c>
       <c r="K64" s="1"/>
     </row>
@@ -3072,28 +3072,28 @@
         <v>1</v>
       </c>
       <c r="C65" s="1">
-        <v>-0.24638944864273071</v>
+        <v>-0.2463894486427307</v>
       </c>
       <c r="D65" s="1">
-        <v>-0.00024505497117679998</v>
+        <v>-0.0002450549711768</v>
       </c>
       <c r="E65" s="1">
-        <v>-0.0019315717316658999</v>
+        <v>-0.0019315717316659</v>
       </c>
       <c r="F65" s="1">
-        <v>0.034095566719770432</v>
+        <v>0.03409556671977043</v>
       </c>
       <c r="G65" s="1">
-        <v>0.78552948472084816</v>
+        <v>0.7855294847208482</v>
       </c>
       <c r="H65" s="1">
         <v>-0.03943856805562973</v>
       </c>
       <c r="I65" s="1">
-        <v>0.96056143183951281</v>
+        <v>0.9605614318395128</v>
       </c>
       <c r="J65" s="1">
-        <v>0.81778162091780882</v>
+        <v>0.8177816209178088</v>
       </c>
       <c r="K65" s="1"/>
     </row>
@@ -3105,28 +3105,28 @@
         <v>1</v>
       </c>
       <c r="C66" s="1">
-        <v>-0.063918434083461761</v>
+        <v>-0.06391843408346176</v>
       </c>
       <c r="D66" s="1">
-        <v>-0.00024505497117679998</v>
+        <v>-0.0002450549711768</v>
       </c>
       <c r="E66" s="1">
-        <v>-0.0019315717316658999</v>
+        <v>-0.0019315717316659</v>
       </c>
       <c r="F66" s="1">
-        <v>0.0088821966201066971</v>
+        <v>0.008882196620106697</v>
       </c>
       <c r="G66" s="1">
-        <v>0.94278713836792827</v>
+        <v>0.9427871383679283</v>
       </c>
       <c r="H66" s="1">
-        <v>-0.010402746498584747</v>
+        <v>-0.01040274649858475</v>
       </c>
       <c r="I66" s="1">
-        <v>0.98959725334950643</v>
+        <v>0.9895972533495064</v>
       </c>
       <c r="J66" s="1">
-        <v>0.95269781234422468</v>
+        <v>0.9526978123442247</v>
       </c>
       <c r="K66" s="1"/>
     </row>
@@ -3138,7 +3138,7 @@
         <v>1</v>
       </c>
       <c r="C67" s="1">
-        <v>-0.25068572163581848</v>
+        <v>-0.2506857216358185</v>
       </c>
       <c r="D67" s="1">
         <v>0</v>
@@ -3147,19 +3147,19 @@
         <v>0</v>
       </c>
       <c r="F67" s="1">
-        <v>0.025273289531469345</v>
+        <v>0.02527328953146935</v>
       </c>
       <c r="G67" s="1">
-        <v>0.77458756601580703</v>
+        <v>0.774587566015807</v>
       </c>
       <c r="H67" s="1">
-        <v>-0.029754288494586945</v>
+        <v>-0.02975428849458694</v>
       </c>
       <c r="I67" s="1">
-        <v>0.97024571126736858</v>
+        <v>0.9702457112673686</v>
       </c>
       <c r="J67" s="1">
-        <v>0.79834163188934326</v>
+        <v>0.7983416318893433</v>
       </c>
       <c r="K67" s="1">
         <v>1</v>
@@ -3173,7 +3173,7 @@
         <v>1</v>
       </c>
       <c r="C68" s="1">
-        <v>-0.31315138936042786</v>
+        <v>-0.3131513893604279</v>
       </c>
       <c r="D68" s="1">
         <v>0</v>
@@ -3182,19 +3182,19 @@
         <v>0</v>
       </c>
       <c r="F68" s="1">
-        <v>0.035553950816392899</v>
+        <v>0.0355539508163929</v>
       </c>
       <c r="G68" s="1">
-        <v>0.72240255941561327</v>
+        <v>0.7224025594156133</v>
       </c>
       <c r="H68" s="1">
-        <v>-0.041854549199342728</v>
+        <v>-0.04185454919934273</v>
       </c>
       <c r="I68" s="1">
-        <v>0.95814545175330634</v>
+        <v>0.9581454517533063</v>
       </c>
       <c r="J68" s="1">
-        <v>0.75395918030367082</v>
+        <v>0.7539591803036708</v>
       </c>
       <c r="K68" s="1"/>
     </row>
@@ -3206,7 +3206,7 @@
         <v>1</v>
       </c>
       <c r="C69" s="1">
-        <v>-0.18822005391120911</v>
+        <v>-0.1882200539112091</v>
       </c>
       <c r="D69" s="1">
         <v>0</v>
@@ -3215,19 +3215,19 @@
         <v>0</v>
       </c>
       <c r="F69" s="1">
-        <v>0.014992630109190941</v>
+        <v>0.01499263010919094</v>
       </c>
       <c r="G69" s="1">
-        <v>0.82677257261600079</v>
+        <v>0.8267725726160008</v>
       </c>
       <c r="H69" s="1">
-        <v>-0.017654029652476311</v>
+        <v>-0.01765402965247631</v>
       </c>
       <c r="I69" s="1">
-        <v>0.98234597078143093</v>
+        <v>0.9823459707814309</v>
       </c>
       <c r="J69" s="1">
-        <v>0.84163074640426783</v>
+        <v>0.8416307464042678</v>
       </c>
       <c r="K69" s="1"/>
     </row>
@@ -3236,10 +3236,10 @@
         <v>83</v>
       </c>
       <c r="B70" s="1">
-        <v>0.97859328985214233</v>
+        <v>0.9785932898521423</v>
       </c>
       <c r="C70" s="1">
-        <v>-0.15148329734802246</v>
+        <v>-0.1514832973480225</v>
       </c>
       <c r="D70" s="1">
         <v>0</v>
@@ -3248,22 +3248,22 @@
         <v>0</v>
       </c>
       <c r="F70" s="1">
-        <v>-0.10828401148319244</v>
+        <v>-0.1082840114831924</v>
       </c>
       <c r="G70" s="1">
-        <v>0.71882598112470453</v>
+        <v>0.7188259811247045</v>
       </c>
       <c r="H70" s="1">
-        <v>0.11173103749752045</v>
+        <v>0.1117310374975204</v>
       </c>
       <c r="I70" s="1">
         <v>1.111731071247424</v>
       </c>
       <c r="J70" s="1">
-        <v>0.64658260345458984</v>
+        <v>0.6465826034545898</v>
       </c>
       <c r="K70" s="1">
-        <v>1.0000000298539797</v>
+        <v>1.00000002985398</v>
       </c>
     </row>
     <row r="71">
@@ -3274,7 +3274,7 @@
         <v>1</v>
       </c>
       <c r="C71" s="1">
-        <v>-0.13648629188537598</v>
+        <v>-0.136486291885376</v>
       </c>
       <c r="D71" s="1">
         <v>0</v>
@@ -3283,19 +3283,19 @@
         <v>0</v>
       </c>
       <c r="F71" s="1">
-        <v>-0.32313022017478943</v>
+        <v>-0.3231302201747894</v>
       </c>
       <c r="G71" s="1">
-        <v>0.54038350855374273</v>
+        <v>0.5403835085537427</v>
       </c>
       <c r="H71" s="1">
-        <v>0.17761437594890595</v>
+        <v>0.1776143759489059</v>
       </c>
       <c r="I71" s="1">
-        <v>1.1776143992212429</v>
+        <v>1.177614399221243</v>
       </c>
       <c r="J71" s="1">
-        <v>0.45887984123758901</v>
+        <v>0.458879841237589</v>
       </c>
       <c r="K71" s="1"/>
     </row>
@@ -3307,7 +3307,7 @@
         <v>0.935779869556427</v>
       </c>
       <c r="C72" s="1">
-        <v>-0.26776653528213501</v>
+        <v>-0.267766535282135</v>
       </c>
       <c r="D72" s="1">
         <v>0</v>
@@ -3316,19 +3316,19 @@
         <v>0</v>
       </c>
       <c r="F72" s="1">
-        <v>0.11711938679218292</v>
+        <v>0.1171193867921829</v>
       </c>
       <c r="G72" s="1">
         <v>0.785132704777319</v>
       </c>
       <c r="H72" s="1">
-        <v>0.092255525290966034</v>
+        <v>0.09225552529096603</v>
       </c>
       <c r="I72" s="1">
-        <v>1.0922555714969193</v>
+        <v>1.092255571496919</v>
       </c>
       <c r="J72" s="1">
-        <v>0.71881776139746023</v>
+        <v>0.7188177613974602</v>
       </c>
       <c r="K72" s="1"/>
     </row>
@@ -3340,7 +3340,7 @@
         <v>1</v>
       </c>
       <c r="C73" s="1">
-        <v>-0.050197083503007889</v>
+        <v>-0.05019708350300789</v>
       </c>
       <c r="D73" s="1">
         <v>0</v>
@@ -3349,19 +3349,19 @@
         <v>0</v>
       </c>
       <c r="F73" s="1">
-        <v>-0.11884120851755142</v>
+        <v>-0.1188412085175514</v>
       </c>
       <c r="G73" s="1">
-        <v>0.83096173004305207</v>
+        <v>0.8309617300430521</v>
       </c>
       <c r="H73" s="1">
-        <v>0.065323218703269959</v>
+        <v>0.06532321870326996</v>
       </c>
       <c r="I73" s="1">
-        <v>1.0653232430241102</v>
+        <v>1.06532324302411</v>
       </c>
       <c r="J73" s="1">
-        <v>0.78000901180398441</v>
+        <v>0.7800090118039844</v>
       </c>
       <c r="K73" s="1"/>
     </row>
@@ -3373,7 +3373,7 @@
         <v>1</v>
       </c>
       <c r="C74" s="1">
-        <v>-0.85432893037796021</v>
+        <v>-0.8543289303779602</v>
       </c>
       <c r="D74" s="1">
         <v>0</v>
@@ -3385,19 +3385,19 @@
         <v>0</v>
       </c>
       <c r="G74" s="1">
-        <v>0.14567108927239725</v>
+        <v>0.1456710892723972</v>
       </c>
       <c r="H74" s="1">
-        <v>-0.020820101723074913</v>
+        <v>-0.02082010172307491</v>
       </c>
       <c r="I74" s="1">
-        <v>0.97917989605686928</v>
+        <v>0.9791798960568693</v>
       </c>
       <c r="J74" s="1">
-        <v>0.14876846969127655</v>
+        <v>0.1487684696912766</v>
       </c>
       <c r="K74" s="1">
-        <v>0.99999999795647909</v>
+        <v>0.9999999979564791</v>
       </c>
     </row>
     <row r="75">
@@ -3408,7 +3408,7 @@
         <v>1</v>
       </c>
       <c r="C75" s="1">
-        <v>-1.6460220813751221</v>
+        <v>-1.646022081375122</v>
       </c>
       <c r="D75" s="1">
         <v>0</v>
@@ -3423,10 +3423,10 @@
         <v>-0.6460220366516285</v>
       </c>
       <c r="H75" s="1">
-        <v>-0.037312746047973633</v>
+        <v>-0.03731274604797363</v>
       </c>
       <c r="I75" s="1">
-        <v>0.96268727033733292</v>
+        <v>0.9626872703373329</v>
       </c>
       <c r="J75" s="1">
         <v>-0.6710611603135227</v>
@@ -3441,7 +3441,7 @@
         <v>1</v>
       </c>
       <c r="C76" s="1">
-        <v>-0.062635764479637146</v>
+        <v>-0.06263576447963715</v>
       </c>
       <c r="D76" s="1">
         <v>0</v>
@@ -3453,16 +3453,16 @@
         <v>0</v>
       </c>
       <c r="G76" s="1">
-        <v>0.93736421519642299</v>
+        <v>0.937364215196423</v>
       </c>
       <c r="H76" s="1">
-        <v>-0.0043274569325149059</v>
+        <v>-0.004327456932514906</v>
       </c>
       <c r="I76" s="1">
-        <v>0.99567252177640564</v>
+        <v>0.9956725217764056</v>
       </c>
       <c r="J76" s="1">
-        <v>0.94143826880352866</v>
+        <v>0.9414382688035287</v>
       </c>
       <c r="K76" s="1"/>
     </row>
@@ -3474,7 +3474,7 @@
         <v>4.100581169128418</v>
       </c>
       <c r="C77" s="1">
-        <v>20.102590560913086</v>
+        <v>20.10259056091309</v>
       </c>
       <c r="D77" s="1">
         <v>0</v>
@@ -3486,19 +3486,19 @@
         <v>0</v>
       </c>
       <c r="G77" s="1">
-        <v>24.203172493549179</v>
+        <v>24.20317249354918</v>
       </c>
       <c r="H77" s="1">
-        <v>-0.39258512854576111</v>
+        <v>-0.3925851285457611</v>
       </c>
       <c r="I77" s="1">
-        <v>0.60741488821226142</v>
+        <v>0.6074148882122614</v>
       </c>
       <c r="J77" s="1">
-        <v>39.846195220947266</v>
+        <v>39.84619522094727</v>
       </c>
       <c r="K77" s="1">
-        <v>0.99999999341593182</v>
+        <v>0.9999999934159318</v>
       </c>
     </row>
     <row r="78">
@@ -3506,10 +3506,10 @@
         <v>91</v>
       </c>
       <c r="B78" s="1">
-        <v>7.6558742523193359</v>
+        <v>7.655874252319336</v>
       </c>
       <c r="C78" s="1">
-        <v>43.160907745361328</v>
+        <v>43.16090774536133</v>
       </c>
       <c r="D78" s="1">
         <v>0</v>
@@ -3521,16 +3521,16 @@
         <v>0</v>
       </c>
       <c r="G78" s="1">
-        <v>50.816781954220716</v>
+        <v>50.81678195422072</v>
       </c>
       <c r="H78" s="1">
-        <v>-0.84289282560348511</v>
+        <v>-0.8428928256034851</v>
       </c>
       <c r="I78" s="1">
-        <v>0.15710718857644204</v>
+        <v>0.157107188576442</v>
       </c>
       <c r="J78" s="1">
-        <v>323.45293945283288</v>
+        <v>323.4529394528329</v>
       </c>
       <c r="K78" s="1"/>
     </row>
@@ -3539,10 +3539,10 @@
         <v>92</v>
       </c>
       <c r="B79" s="1">
-        <v>0.54528802633285523</v>
+        <v>0.5452880263328552</v>
       </c>
       <c r="C79" s="1">
-        <v>-2.9557249546051025</v>
+        <v>-2.955724954605103</v>
       </c>
       <c r="D79" s="1">
         <v>0</v>
@@ -3554,16 +3554,16 @@
         <v>0</v>
       </c>
       <c r="G79" s="1">
-        <v>-2.4104369671223593</v>
+        <v>-2.410436967122359</v>
       </c>
       <c r="H79" s="1">
-        <v>0.057722587138414383</v>
+        <v>0.05772258713841438</v>
       </c>
       <c r="I79" s="1">
-        <v>1.0577225878480807</v>
+        <v>1.057722587848081</v>
       </c>
       <c r="J79" s="1">
-        <v>-2.2788933457744851</v>
+        <v>-2.278893345774485</v>
       </c>
       <c r="K79" s="1"/>
     </row>
@@ -3572,10 +3572,10 @@
         <v>93</v>
       </c>
       <c r="B80" s="1">
-        <v>0.46187901496887207</v>
+        <v>0.4618790149688721</v>
       </c>
       <c r="C80" s="1">
-        <v>14.443218231201172</v>
+        <v>14.44321823120117</v>
       </c>
       <c r="D80" s="1">
         <v>0</v>
@@ -3587,19 +3587,19 @@
         <v>0</v>
       </c>
       <c r="G80" s="1">
-        <v>14.905097157081519</v>
+        <v>14.90509715708152</v>
       </c>
       <c r="H80" s="1">
-        <v>-0.28206273913383484</v>
+        <v>-0.2820627391338348</v>
       </c>
       <c r="I80" s="1">
-        <v>0.71793724426445926</v>
+        <v>0.7179372442644593</v>
       </c>
       <c r="J80" s="1">
-        <v>20.761003494262695</v>
+        <v>20.7610034942627</v>
       </c>
       <c r="K80" s="1">
-        <v>0.99999999970256681</v>
+        <v>0.9999999997025668</v>
       </c>
     </row>
     <row r="81">
@@ -3610,7 +3610,7 @@
         <v>0</v>
       </c>
       <c r="C81" s="1">
-        <v>35.840240478515625</v>
+        <v>35.84024047851563</v>
       </c>
       <c r="D81" s="1">
         <v>0</v>
@@ -3622,16 +3622,16 @@
         <v>0</v>
       </c>
       <c r="G81" s="1">
-        <v>35.840238968239156</v>
+        <v>35.84023896823916</v>
       </c>
       <c r="H81" s="1">
-        <v>-0.69992685317993164</v>
+        <v>-0.6999268531799316</v>
       </c>
       <c r="I81" s="1">
-        <v>0.30007312869368025</v>
+        <v>0.3000731286936802</v>
       </c>
       <c r="J81" s="1">
-        <v>119.43834865942119</v>
+        <v>119.4383486594212</v>
       </c>
       <c r="K81" s="1"/>
     </row>
@@ -3640,10 +3640,10 @@
         <v>95</v>
       </c>
       <c r="B82" s="1">
-        <v>0.42063704133033753</v>
+        <v>0.4206370413303375</v>
       </c>
       <c r="C82" s="1">
-        <v>4.5379939079284668</v>
+        <v>4.537993907928467</v>
       </c>
       <c r="D82" s="1">
         <v>0</v>
@@ -3655,16 +3655,16 @@
         <v>0</v>
       </c>
       <c r="G82" s="1">
-        <v>4.9586310259887707</v>
+        <v>4.958631025988771</v>
       </c>
       <c r="H82" s="1">
-        <v>-0.088622845709323883</v>
+        <v>-0.08862284570932388</v>
       </c>
       <c r="I82" s="1">
-        <v>0.91137711802378296</v>
+        <v>0.911377118023783</v>
       </c>
       <c r="J82" s="1">
-        <v>5.4408114137657906</v>
+        <v>5.440811413765791</v>
       </c>
       <c r="K82" s="1"/>
     </row>
@@ -3676,7 +3676,7 @@
         <v>0.9649999737739563</v>
       </c>
       <c r="C83" s="1">
-        <v>2.9514214992523193</v>
+        <v>2.951421499252319</v>
       </c>
       <c r="D83" s="1">
         <v>0</v>
@@ -3688,16 +3688,16 @@
         <v>0</v>
       </c>
       <c r="G83" s="1">
-        <v>3.9164214770166264</v>
+        <v>3.916421477016626</v>
       </c>
       <c r="H83" s="1">
-        <v>-0.057638544589281082</v>
+        <v>-0.05763854458928108</v>
       </c>
       <c r="I83" s="1">
-        <v>0.94236148607591441</v>
+        <v>0.9423614860759144</v>
       </c>
       <c r="J83" s="1">
-        <v>4.1559651310931534</v>
+        <v>4.155965131093153</v>
       </c>
       <c r="K83" s="1"/>
     </row>
@@ -3706,10 +3706,10 @@
         <v>97</v>
       </c>
       <c r="B84" s="1">
-        <v>0.94373363256454468</v>
+        <v>0.9437336325645447</v>
       </c>
       <c r="C84" s="1">
-        <v>9.3849077224731445</v>
+        <v>9.384907722473145</v>
       </c>
       <c r="D84" s="1">
         <v>0</v>
@@ -3721,19 +3721,19 @@
         <v>0</v>
       </c>
       <c r="G84" s="1">
-        <v>10.328641125439791</v>
+        <v>10.32864112543979</v>
       </c>
       <c r="H84" s="1">
-        <v>-0.18327860534191132</v>
+        <v>-0.1832786053419113</v>
       </c>
       <c r="I84" s="1">
-        <v>0.81672140017750727</v>
+        <v>0.8167214001775073</v>
       </c>
       <c r="J84" s="1">
-        <v>12.646468162536621</v>
+        <v>12.64646816253662</v>
       </c>
       <c r="K84" s="1">
-        <v>1.0000000048780253</v>
+        <v>1.000000004878025</v>
       </c>
     </row>
     <row r="85">
@@ -3741,10 +3741,10 @@
         <v>98</v>
       </c>
       <c r="B85" s="1">
-        <v>0.97221297025680542</v>
+        <v>0.9722129702568054</v>
       </c>
       <c r="C85" s="1">
-        <v>10.642144203186035</v>
+        <v>10.64214420318604</v>
       </c>
       <c r="D85" s="1">
         <v>0</v>
@@ -3756,13 +3756,13 @@
         <v>0</v>
       </c>
       <c r="G85" s="1">
-        <v>11.614357089007134</v>
+        <v>11.61435708900713</v>
       </c>
       <c r="H85" s="1">
-        <v>-0.20783127844333649</v>
+        <v>-0.2078312784433365</v>
       </c>
       <c r="I85" s="1">
-        <v>0.79216870519684135</v>
+        <v>0.7921687051968413</v>
       </c>
       <c r="J85" s="1">
         <v>14.66146922090434</v>
@@ -3774,10 +3774,10 @@
         <v>99</v>
       </c>
       <c r="B86" s="1">
-        <v>0.91525429487228394</v>
+        <v>0.9152542948722839</v>
       </c>
       <c r="C86" s="1">
-        <v>8.1276712417602539</v>
+        <v>8.127671241760254</v>
       </c>
       <c r="D86" s="1">
         <v>0</v>
@@ -3792,7 +3792,7 @@
         <v>9.04292516187245</v>
       </c>
       <c r="H86" s="1">
-        <v>-0.15872593224048615</v>
+        <v>-0.1587259322404861</v>
       </c>
       <c r="I86" s="1">
         <v>0.8412740951581732</v>
@@ -3810,7 +3810,7 @@
         <v>1</v>
       </c>
       <c r="C87" s="1">
-        <v>7.4946699142456055</v>
+        <v>7.494669914245605</v>
       </c>
       <c r="D87" s="1">
         <v>0</v>
@@ -3822,19 +3822,19 @@
         <v>0</v>
       </c>
       <c r="G87" s="1">
-        <v>8.4946700372651858</v>
+        <v>8.494670037265186</v>
       </c>
       <c r="H87" s="1">
-        <v>0.11169739812612534</v>
+        <v>0.1116973981261253</v>
       </c>
       <c r="I87" s="1">
         <v>1.111697405491312</v>
       </c>
       <c r="J87" s="1">
-        <v>7.6411709785461426</v>
+        <v>7.641170978546143</v>
       </c>
       <c r="K87" s="1">
-        <v>0.99999997956364628</v>
+        <v>0.9999999795636463</v>
       </c>
     </row>
     <row r="88">
@@ -3845,7 +3845,7 @@
         <v>1</v>
       </c>
       <c r="C88" s="1">
-        <v>7.4946699142456055</v>
+        <v>7.494669914245605</v>
       </c>
       <c r="D88" s="1">
         <v>0</v>
@@ -3857,16 +3857,16 @@
         <v>0</v>
       </c>
       <c r="G88" s="1">
-        <v>8.4946700372651858</v>
+        <v>8.494670037265186</v>
       </c>
       <c r="H88" s="1">
-        <v>0.11169739812612534</v>
+        <v>0.1116973981261253</v>
       </c>
       <c r="I88" s="1">
         <v>1.111697405491312</v>
       </c>
       <c r="J88" s="1">
-        <v>7.6411710554554961</v>
+        <v>7.641171055455496</v>
       </c>
       <c r="K88" s="1"/>
     </row>
@@ -3875,10 +3875,10 @@
         <v>102</v>
       </c>
       <c r="B89" s="1">
-        <v>0.66666668653488159</v>
+        <v>0.6666666865348816</v>
       </c>
       <c r="C89" s="1">
-        <v>-0.017558688297867775</v>
+        <v>-0.01755868829786777</v>
       </c>
       <c r="D89" s="1">
         <v>0</v>
@@ -3890,19 +3890,19 @@
         <v>0</v>
       </c>
       <c r="G89" s="1">
-        <v>0.64910796076575128</v>
+        <v>0.6491079607657513</v>
       </c>
       <c r="H89" s="1">
-        <v>0.00034290508483536542</v>
+        <v>0.0003429050848353654</v>
       </c>
       <c r="I89" s="1">
-        <v>1.0003428845712827</v>
+        <v>1.000342884571283</v>
       </c>
       <c r="J89" s="1">
-        <v>0.64888548851013184</v>
+        <v>0.6488854885101318</v>
       </c>
       <c r="K89" s="1">
-        <v>0.99999997952016351</v>
+        <v>0.9999999795201635</v>
       </c>
     </row>
     <row r="90">
@@ -3913,7 +3913,7 @@
         <v>0.75</v>
       </c>
       <c r="C90" s="1">
-        <v>0.10035629570484161</v>
+        <v>0.1003562957048416</v>
       </c>
       <c r="D90" s="1">
         <v>0</v>
@@ -3925,16 +3925,16 @@
         <v>0</v>
       </c>
       <c r="G90" s="1">
-        <v>0.85035626444875501</v>
+        <v>0.850356264448755</v>
       </c>
       <c r="H90" s="1">
-        <v>-0.0019598659127950668</v>
+        <v>-0.001959865912795067</v>
       </c>
       <c r="I90" s="1">
-        <v>0.99804009613332434</v>
+        <v>0.9980400961333243</v>
       </c>
       <c r="J90" s="1">
-        <v>0.85202615380210056</v>
+        <v>0.8520261538021006</v>
       </c>
       <c r="K90" s="1"/>
     </row>
@@ -3946,7 +3946,7 @@
         <v>0.75</v>
       </c>
       <c r="C91" s="1">
-        <v>-0.075490139424800873</v>
+        <v>-0.07549013942480087</v>
       </c>
       <c r="D91" s="1">
         <v>0</v>
@@ -3958,16 +3958,16 @@
         <v>0</v>
       </c>
       <c r="G91" s="1">
-        <v>0.67450983447803648</v>
+        <v>0.6745098344780365</v>
       </c>
       <c r="H91" s="1">
         <v>0.001474253018386662</v>
       </c>
       <c r="I91" s="1">
-        <v>1.0014742215912018</v>
+        <v>1.001474221591202</v>
       </c>
       <c r="J91" s="1">
-        <v>0.67351692129063001</v>
+        <v>0.67351692129063</v>
       </c>
       <c r="K91" s="1"/>
     </row>
@@ -3979,7 +3979,7 @@
         <v>0.5</v>
       </c>
       <c r="C92" s="1">
-        <v>-0.077542223036289215</v>
+        <v>-0.07754222303628922</v>
       </c>
       <c r="D92" s="1">
         <v>0</v>
@@ -3994,13 +3994,13 @@
         <v>0.4224577833704623</v>
       </c>
       <c r="H92" s="1">
-        <v>0.0015143281780183315</v>
+        <v>0.001514328178018332</v>
       </c>
       <c r="I92" s="1">
-        <v>1.0015143359893219</v>
+        <v>1.001514335989322</v>
       </c>
       <c r="J92" s="1">
-        <v>0.42181900766617331</v>
+        <v>0.4218190076661733</v>
       </c>
       <c r="K92" s="1"/>
     </row>
@@ -4017,7 +4017,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5BF7382-BA68-4FFF-972D-6F46E493258F}">
   <dimension ref="E1:AL129"/>
-  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultColWidth="9.109375" defaultRowHeight="28.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="28.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="4" width="9.109375" style="25"/>
     <col min="5" max="5" width="9.109375" style="25" customWidth="true"/>
@@ -4039,7 +4039,7 @@
     <col min="28" max="16384" width="9.109375" style="25"/>
   </cols>
   <sheetData>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" s="2" customFormat="true" ht="19.8" x14ac:dyDescent="0.3">
+    <row r="1" s="2" customFormat="true" ht="19.8" x14ac:dyDescent="0.3">
       <c r="F1" s="3"/>
       <c r="K1" s="6"/>
       <c r="L1" s="6"/>
@@ -4053,7 +4053,7 @@
       <c r="T1" s="6"/>
       <c r="V1" s="3"/>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" s="2" customFormat="true" ht="19.8" x14ac:dyDescent="0.3">
+    <row r="2" s="2" customFormat="true" ht="19.8" x14ac:dyDescent="0.3">
       <c r="F2" s="3"/>
       <c r="K2" s="6"/>
       <c r="L2" s="6"/>
@@ -4067,7 +4067,7 @@
       <c r="T2" s="6"/>
       <c r="V2" s="3"/>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" s="2" customFormat="true" ht="19.8" x14ac:dyDescent="0.3">
+    <row r="3" s="2" customFormat="true" ht="19.8" x14ac:dyDescent="0.3">
       <c r="F3" s="3"/>
       <c r="K3" s="6"/>
       <c r="L3" s="6"/>
@@ -4081,7 +4081,7 @@
       <c r="T3" s="6"/>
       <c r="V3" s="3"/>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" s="2" customFormat="true" ht="19.8" x14ac:dyDescent="0.3">
+    <row r="4" s="2" customFormat="true" ht="19.8" x14ac:dyDescent="0.3">
       <c r="F4" s="3"/>
       <c r="K4" s="6"/>
       <c r="L4" s="6"/>
@@ -4095,7 +4095,7 @@
       <c r="T4" s="6"/>
       <c r="V4" s="3"/>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" s="2" customFormat="true" ht="19.8" x14ac:dyDescent="0.3">
+    <row r="5" s="2" customFormat="true" ht="19.8" x14ac:dyDescent="0.3">
       <c r="F5" s="3"/>
       <c r="K5" s="6"/>
       <c r="L5" s="6"/>
@@ -4109,7 +4109,7 @@
       <c r="T5" s="6"/>
       <c r="V5" s="3"/>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" s="2" customFormat="true" ht="20.4" thickBot="true" x14ac:dyDescent="0.35">
+    <row r="6" s="2" customFormat="true" ht="20.4" thickBot="true" x14ac:dyDescent="0.35">
       <c r="F6" s="3"/>
       <c r="K6" s="6"/>
       <c r="L6" s="6"/>
@@ -4123,7 +4123,7 @@
       <c r="T6" s="6"/>
       <c r="V6" s="3"/>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" s="2" customFormat="true" ht="10.2" customHeight="true" thickTop="true" x14ac:dyDescent="0.3">
+    <row r="7" s="2" customFormat="true" ht="10.2" customHeight="true" thickTop="true" x14ac:dyDescent="0.3">
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
@@ -4142,7 +4142,7 @@
       <c r="U7" s="4"/>
       <c r="V7" s="4"/>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" s="10" customFormat="true" ht="31.8" thickBot="true" x14ac:dyDescent="0.35">
+    <row r="8" s="10" customFormat="true" ht="31.8" thickBot="true" x14ac:dyDescent="0.35">
       <c r="J8" s="44" t="s">
         <v>12</v>
       </c>
@@ -4159,7 +4159,7 @@
       <c r="S8" s="44"/>
       <c r="T8" s="35"/>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" s="2" customFormat="true" ht="10.2" customHeight="true" thickTop="true" x14ac:dyDescent="0.3">
+    <row r="9" s="2" customFormat="true" ht="10.2" customHeight="true" thickTop="true" x14ac:dyDescent="0.3">
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
@@ -4178,7 +4178,7 @@
       <c r="U9" s="3"/>
       <c r="V9" s="3"/>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" s="11" customFormat="true" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
+    <row r="10" s="11" customFormat="true" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
       <c r="F10" s="8"/>
       <c r="K10" s="13"/>
       <c r="L10" s="13"/>
@@ -4194,7 +4194,7 @@
       <c r="T10" s="8"/>
       <c r="V10" s="8"/>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" s="16" customFormat="true" ht="40.05" customHeight="true" thickTop="true" thickBot="true" x14ac:dyDescent="0.75">
+    <row r="11" s="16" customFormat="true" ht="40.05" customHeight="true" thickTop="true" thickBot="true" x14ac:dyDescent="0.75">
       <c r="E11" s="39"/>
       <c r="F11" s="40" t="s">
         <v>0</v>
@@ -4250,7 +4250,7 @@
       <c r="AK11" s="15"/>
       <c r="AL11" s="15"/>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" s="16" customFormat="true" ht="10.2" customHeight="true" thickTop="true" x14ac:dyDescent="0.3">
+    <row r="12" s="16" customFormat="true" ht="10.2" customHeight="true" thickTop="true" x14ac:dyDescent="0.3">
       <c r="F12" s="17"/>
       <c r="G12" s="17"/>
       <c r="H12" s="17"/>
@@ -4269,7 +4269,7 @@
       <c r="U12" s="17"/>
       <c r="V12" s="17"/>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" s="23" customFormat="true" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
+    <row r="13" s="23" customFormat="true" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
       <c r="F13" s="19"/>
       <c r="G13" s="20" t="str">
         <f>data_export!A2</f>
@@ -4318,7 +4318,7 @@
       <c r="U13" s="21"/>
       <c r="V13" s="19"/>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="14" x14ac:dyDescent="0.3">
+    <row r="14" x14ac:dyDescent="0.3">
       <c r="H14" s="26" t="str">
         <f>data_export!A3</f>
         <v>PTC (Shrimali)</v>
@@ -4361,7 +4361,7 @@
         <v>7.5466899999999999</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="15" x14ac:dyDescent="0.3">
+    <row r="15" x14ac:dyDescent="0.3">
       <c r="H15" s="26" t="str">
         <f>data_export!A4</f>
         <v>PTC (Metcalf)</v>
@@ -4404,7 +4404,7 @@
         <v>5.2980609999999997</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="16" x14ac:dyDescent="0.3">
+    <row r="16" x14ac:dyDescent="0.3">
       <c r="H16" s="26" t="str">
         <f>data_export!A5</f>
         <v>PTC (Hitaj)</v>
@@ -4447,8 +4447,8 @@
         <v>4.6260130000000004</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="17" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="18" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
+    <row r="17" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
+    <row r="18" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
       <c r="G18" s="20"/>
       <c r="H18" s="20" t="str">
         <f>data_export!A6</f>
@@ -4495,7 +4495,7 @@
       </c>
       <c r="U18" s="21"/>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="19" x14ac:dyDescent="0.3">
+    <row r="19" x14ac:dyDescent="0.3">
       <c r="H19" s="26" t="str">
         <f>data_export!A7</f>
         <v>CSI</v>
@@ -4538,7 +4538,7 @@
         <v>5.0632710000000003</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="20" x14ac:dyDescent="0.3">
+    <row r="20" x14ac:dyDescent="0.3">
       <c r="H20" s="26" t="str">
         <f>data_export!A8</f>
         <v>NE Solar</v>
@@ -4581,7 +4581,7 @@
         <v>4.6760539999999997</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="21" x14ac:dyDescent="0.3">
+    <row r="21" x14ac:dyDescent="0.3">
       <c r="H21" s="26" t="str">
         <f>data_export!A9</f>
         <v>CSI (TPO)</v>
@@ -4624,7 +4624,7 @@
         <v>3.8154659999999998</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="22" x14ac:dyDescent="0.3">
+    <row r="22" x14ac:dyDescent="0.3">
       <c r="H22" s="26" t="str">
         <f>data_export!A10</f>
         <v>CSI (HO)</v>
@@ -4667,7 +4667,7 @@
         <v>2.7115860000000001</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="23" x14ac:dyDescent="0.3">
+    <row r="23" x14ac:dyDescent="0.3">
       <c r="H23" s="26" t="str">
         <f>data_export!A11</f>
         <v>CT Solar</v>
@@ -4710,8 +4710,8 @@
         <v>1.633623</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="24" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="25" s="23" customFormat="true" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
+    <row r="24" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
+    <row r="25" s="23" customFormat="true" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
       <c r="F25" s="19"/>
       <c r="G25" s="20" t="str">
         <f>data_export!A12</f>
@@ -4760,7 +4760,7 @@
       <c r="U25" s="21"/>
       <c r="V25" s="19"/>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="26" x14ac:dyDescent="0.3">
+    <row r="26" x14ac:dyDescent="0.3">
       <c r="H26" s="26" t="str">
         <f>data_export!A13</f>
         <v>BEV (State - Rebate)</v>
@@ -4803,7 +4803,7 @@
         <v>1.561256</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="27" x14ac:dyDescent="0.3">
+    <row r="27" x14ac:dyDescent="0.3">
       <c r="H27" s="26" t="str">
         <f>data_export!A14</f>
         <v>ITC (EV)</v>
@@ -4846,7 +4846,7 @@
         <v>1.473692</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="28" x14ac:dyDescent="0.3">
+    <row r="28" x14ac:dyDescent="0.3">
       <c r="H28" s="26" t="str">
         <f>data_export!A15</f>
         <v>EFMP</v>
@@ -4889,8 +4889,8 @@
         <v>1.2961830000000001</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="29" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="30" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
+    <row r="29" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
+    <row r="30" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
       <c r="G30" s="20" t="str">
         <f>data_export!A16</f>
         <v>Appliance Rebates</v>
@@ -4938,7 +4938,7 @@
       <c r="U30" s="22"/>
       <c r="V30" s="19"/>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="31" x14ac:dyDescent="0.3">
+    <row r="31" x14ac:dyDescent="0.3">
       <c r="H31" s="26" t="str">
         <f>data_export!A17</f>
         <v>C4A (CW)</v>
@@ -4981,7 +4981,7 @@
         <v>1.405106</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="32" x14ac:dyDescent="0.3">
+    <row r="32" x14ac:dyDescent="0.3">
       <c r="H32" s="26" t="str">
         <f>data_export!A18</f>
         <v>ES (WH)</v>
@@ -5024,7 +5024,7 @@
         <v>1.340039</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="33" x14ac:dyDescent="0.3">
+    <row r="33" x14ac:dyDescent="0.3">
       <c r="H33" s="26" t="str">
         <f>data_export!A19</f>
         <v>ES (CW)</v>
@@ -5066,7 +5066,7 @@
         <v>1.3096449999999999</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="34" s="23" customFormat="true" x14ac:dyDescent="0.3">
+    <row r="34" s="23" customFormat="true" x14ac:dyDescent="0.3">
       <c r="F34" s="19"/>
       <c r="G34" s="24"/>
       <c r="H34" s="26" t="str">
@@ -5115,7 +5115,7 @@
       <c r="U34" s="27"/>
       <c r="V34" s="24"/>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="35" x14ac:dyDescent="0.3">
+    <row r="35" x14ac:dyDescent="0.3">
       <c r="H35" s="26" t="str">
         <f>data_export!A21</f>
         <v>ES (DW)</v>
@@ -5158,7 +5158,7 @@
         <v>1.0533790000000001</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="36" x14ac:dyDescent="0.3">
+    <row r="36" x14ac:dyDescent="0.3">
       <c r="H36" s="26" t="str">
         <f>data_export!A22</f>
         <v>C4A (Fridge)</v>
@@ -5201,7 +5201,7 @@
         <v>1.041846</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="37" x14ac:dyDescent="0.3">
+    <row r="37" x14ac:dyDescent="0.3">
       <c r="H37" s="26" t="str">
         <f>data_export!A23</f>
         <v>ES (Fridge)</v>
@@ -5244,7 +5244,7 @@
         <v>1.0114190000000001</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="38" x14ac:dyDescent="0.3">
+    <row r="38" x14ac:dyDescent="0.3">
       <c r="H38" s="26" t="str">
         <f>data_export!A24</f>
         <v>CA ESA</v>
@@ -5287,8 +5287,8 @@
         <v>0.95832660000000003</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="39" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="40" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
+    <row r="39" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
+    <row r="40" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
       <c r="G40" s="20" t="str">
         <f>data_export!A25</f>
         <v>Vehicle Retirement</v>
@@ -5336,7 +5336,7 @@
       <c r="U40" s="22"/>
       <c r="V40" s="19"/>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="41" x14ac:dyDescent="0.3">
+    <row r="41" x14ac:dyDescent="0.3">
       <c r="H41" s="26" t="str">
         <f>data_export!A26</f>
         <v>C4C (TX)</v>
@@ -5379,7 +5379,7 @@
         <v>1.0671250000000001</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="42" x14ac:dyDescent="0.3">
+    <row r="42" x14ac:dyDescent="0.3">
       <c r="H42" s="26" t="str">
         <f>data_export!A27</f>
         <v>C4C (US)</v>
@@ -5422,7 +5422,7 @@
         <v>1.044287</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="43" x14ac:dyDescent="0.3">
+    <row r="43" x14ac:dyDescent="0.3">
       <c r="H43" s="26" t="str">
         <f>data_export!A28</f>
         <v>BAAQMD</v>
@@ -5466,8 +5466,8 @@
       </c>
       <c r="AA43" s="38"/>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="44" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="45" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
+    <row r="44" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
+    <row r="45" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
       <c r="G45" s="20" t="str">
         <f>data_export!A29</f>
         <v>Hybrid Vehicles</v>
@@ -5515,7 +5515,7 @@
       <c r="U45" s="22"/>
       <c r="V45" s="19"/>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="46" x14ac:dyDescent="0.3">
+    <row r="46" x14ac:dyDescent="0.3">
       <c r="H46" s="26" t="str">
         <f>data_export!A30</f>
         <v>HY (S-STW)</v>
@@ -5558,7 +5558,7 @@
         <v>1.0272870000000001</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="47" x14ac:dyDescent="0.3">
+    <row r="47" x14ac:dyDescent="0.3">
       <c r="H47" s="26" t="str">
         <f>data_export!A31</f>
         <v>HY (F-ITC)</v>
@@ -5601,7 +5601,7 @@
         <v>1.0075080000000001</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="48" x14ac:dyDescent="0.3">
+    <row r="48" x14ac:dyDescent="0.3">
       <c r="H48" s="26" t="str">
         <f>data_export!A32</f>
         <v>HY (S-ITC)</v>
@@ -5644,8 +5644,8 @@
         <v>1.001606</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="49" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="50" s="23" customFormat="true" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
+    <row r="49" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
+    <row r="50" s="23" customFormat="true" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
       <c r="F50" s="19"/>
       <c r="G50" s="20" t="str">
         <f>data_export!A33</f>
@@ -5694,7 +5694,7 @@
       <c r="U50" s="21"/>
       <c r="V50" s="19"/>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="51" x14ac:dyDescent="0.3">
+    <row r="51" x14ac:dyDescent="0.3">
       <c r="H51" s="26" t="str">
         <f>data_export!A34</f>
         <v>EPP</v>
@@ -5737,7 +5737,7 @@
         <v>1.2101489999999999</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="52" x14ac:dyDescent="0.3">
+    <row r="52" x14ac:dyDescent="0.3">
       <c r="H52" s="26" t="str">
         <f>data_export!A35</f>
         <v>IHWAP</v>
@@ -5780,7 +5780,7 @@
         <v>0.98018269999999996</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="53" x14ac:dyDescent="0.3">
+    <row r="53" x14ac:dyDescent="0.3">
       <c r="H53" s="26" t="str">
         <f>data_export!A36</f>
         <v>WI RF</v>
@@ -5823,7 +5823,7 @@
         <v>0.9198132</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="54" s="23" customFormat="true" x14ac:dyDescent="0.3">
+    <row r="54" s="23" customFormat="true" x14ac:dyDescent="0.3">
       <c r="F54" s="19"/>
       <c r="G54" s="37"/>
       <c r="H54" s="26" t="str">
@@ -5872,7 +5872,7 @@
       <c r="U54" s="25"/>
       <c r="V54" s="19"/>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="55" x14ac:dyDescent="0.3">
+    <row r="55" x14ac:dyDescent="0.3">
       <c r="H55" s="26" t="str">
         <f>data_export!A38</f>
         <v>LEEP+</v>
@@ -5915,8 +5915,8 @@
         <v>0.8591472</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="56" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="57" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
+    <row r="56" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
+    <row r="57" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
       <c r="F57" s="37"/>
       <c r="G57" s="21" t="str">
         <f>data_export!A39</f>
@@ -5965,7 +5965,7 @@
       <c r="U57" s="21"/>
       <c r="V57" s="19"/>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="58" x14ac:dyDescent="0.3">
+    <row r="58" x14ac:dyDescent="0.3">
       <c r="H58" s="26" t="str">
         <f>data_export!A40</f>
         <v>CA 20/20</v>
@@ -6008,7 +6008,7 @@
         <v>2.572498</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="59" s="23" customFormat="true" x14ac:dyDescent="0.3">
+    <row r="59" s="23" customFormat="true" x14ac:dyDescent="0.3">
       <c r="F59" s="19"/>
       <c r="G59" s="37"/>
       <c r="H59" s="26" t="str">
@@ -6057,8 +6057,8 @@
       <c r="U59" s="25"/>
       <c r="V59" s="19"/>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="60" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="61" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
+    <row r="60" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
+    <row r="61" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
       <c r="F61" s="19" t="s">
         <v>1</v>
       </c>
@@ -6079,7 +6079,7 @@
       <c r="U61" s="24"/>
       <c r="W61" s="24"/>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="62" ht="10.2" customHeight="true" thickTop="true" x14ac:dyDescent="0.3">
+    <row r="62" ht="10.2" customHeight="true" thickTop="true" x14ac:dyDescent="0.3">
       <c r="F62" s="30"/>
       <c r="G62" s="30"/>
       <c r="H62" s="30"/>
@@ -6098,7 +6098,7 @@
       <c r="U62" s="30"/>
       <c r="V62" s="30"/>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="63" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
+    <row r="63" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
       <c r="F63" s="19"/>
       <c r="G63" s="20" t="str">
         <f>data_export!A42</f>
@@ -6147,7 +6147,7 @@
       <c r="U63" s="21"/>
       <c r="V63" s="28"/>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="64" x14ac:dyDescent="0.3">
+    <row r="64" x14ac:dyDescent="0.3">
       <c r="H64" s="26" t="str">
         <f>data_export!A43</f>
         <v>HER (17 RCTs)</v>
@@ -6190,7 +6190,7 @@
         <v>3.0060020000000001</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="65" x14ac:dyDescent="0.3">
+    <row r="65" x14ac:dyDescent="0.3">
       <c r="H65" s="26" t="str">
         <f>data_export!A44</f>
         <v>Opower Elec. (166 RCTs)</v>
@@ -6233,7 +6233,7 @@
         <v>2.5476939999999999</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="66" x14ac:dyDescent="0.3">
+    <row r="66" x14ac:dyDescent="0.3">
       <c r="H66" s="26" t="str">
         <f>data_export!A45</f>
         <v>PER</v>
@@ -6276,7 +6276,7 @@
         <v>1.5998129999999999</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="67" x14ac:dyDescent="0.3">
+    <row r="67" x14ac:dyDescent="0.3">
       <c r="H67" s="26" t="str">
         <f>data_export!A46</f>
         <v>Opower Nat. Gas (52 RCTs)</v>
@@ -6319,8 +6319,8 @@
         <v>0.4509785</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="68" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="69" s="23" customFormat="true" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
+    <row r="68" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
+    <row r="69" s="23" customFormat="true" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
       <c r="F69" s="19"/>
       <c r="G69" s="20" t="str">
         <f>data_export!A47</f>
@@ -6369,7 +6369,7 @@
       <c r="U69" s="21"/>
       <c r="V69" s="19"/>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="70" x14ac:dyDescent="0.3">
+    <row r="70" x14ac:dyDescent="0.3">
       <c r="H70" s="26" t="str">
         <f>data_export!A48</f>
         <v>Audit Nudge</v>
@@ -6412,7 +6412,7 @@
         <v>2.1168469999999999</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="71" x14ac:dyDescent="0.3">
+    <row r="71" x14ac:dyDescent="0.3">
       <c r="H71" s="26" t="str">
         <f>data_export!A49</f>
         <v>Solarize</v>
@@ -6455,7 +6455,7 @@
         <v>1.8085340000000001</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="72" x14ac:dyDescent="0.3">
+    <row r="72" x14ac:dyDescent="0.3">
       <c r="F72" s="19"/>
       <c r="G72" s="19"/>
       <c r="H72" s="25" t="str">
@@ -6502,7 +6502,7 @@
       <c r="U72" s="27"/>
       <c r="V72" s="19"/>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="73" x14ac:dyDescent="0.3">
+    <row r="73" x14ac:dyDescent="0.3">
       <c r="H73" s="26" t="str">
         <f>data_export!A51</f>
         <v>IHWAP + Nudge (H)</v>
@@ -6545,7 +6545,7 @@
         <v>1.0694269999999999</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="74" x14ac:dyDescent="0.3">
+    <row r="74" x14ac:dyDescent="0.3">
       <c r="H74" s="26" t="str">
         <f>data_export!A52</f>
         <v>IHWAP + Nudge (L)</v>
@@ -6588,7 +6588,7 @@
         <v>1.0624659999999999</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="75" x14ac:dyDescent="0.3">
+    <row r="75" x14ac:dyDescent="0.3">
       <c r="H75" s="26" t="str">
         <f>data_export!A53</f>
         <v>WAP + Nudge</v>
@@ -6631,8 +6631,8 @@
         <v>0.27975709999999998</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="76" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="77" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
+    <row r="76" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
+    <row r="77" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
       <c r="F77" s="19" t="s">
         <v>2</v>
       </c>
@@ -6653,7 +6653,7 @@
       <c r="U77" s="24"/>
       <c r="W77" s="24"/>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="78" ht="10.2" customHeight="true" thickTop="true" x14ac:dyDescent="0.3">
+    <row r="78" ht="10.2" customHeight="true" thickTop="true" x14ac:dyDescent="0.3">
       <c r="F78" s="30"/>
       <c r="G78" s="30"/>
       <c r="H78" s="30"/>
@@ -6672,7 +6672,7 @@
       <c r="U78" s="30"/>
       <c r="V78" s="30"/>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="79" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
+    <row r="79" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
       <c r="F79" s="19"/>
       <c r="G79" s="20" t="str">
         <f>data_export!A54</f>
@@ -6720,7 +6720,7 @@
       </c>
       <c r="U79" s="21"/>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="80" s="23" customFormat="true" x14ac:dyDescent="0.3">
+    <row r="80" s="23" customFormat="true" x14ac:dyDescent="0.3">
       <c r="F80" s="25"/>
       <c r="G80" s="26"/>
       <c r="H80" s="26" t="str">
@@ -6769,7 +6769,7 @@
       <c r="U80" s="19"/>
       <c r="V80" s="19"/>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="81" x14ac:dyDescent="0.3">
+    <row r="81" x14ac:dyDescent="0.3">
       <c r="H81" s="26" t="str">
         <f>data_export!A56</f>
         <v>Gas (Su)</v>
@@ -6812,7 +6812,7 @@
         <v>0.52256800000000003</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="82" x14ac:dyDescent="0.3">
+    <row r="82" x14ac:dyDescent="0.3">
       <c r="H82" s="26" t="str">
         <f>data_export!A57</f>
         <v>Gas (Coglianese)</v>
@@ -6855,7 +6855,7 @@
         <v>0.56079049999999997</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="83" x14ac:dyDescent="0.3">
+    <row r="83" x14ac:dyDescent="0.3">
       <c r="H83" s="26" t="str">
         <f>data_export!A58</f>
         <v>Gas (Manzan)</v>
@@ -6898,7 +6898,7 @@
         <v>0.57773160000000001</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="84" x14ac:dyDescent="0.3">
+    <row r="84" x14ac:dyDescent="0.3">
       <c r="H84" s="26" t="str">
         <f>data_export!A59</f>
         <v>Gas (Small)</v>
@@ -6941,7 +6941,7 @@
         <v>0.60484959999999999</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="85" x14ac:dyDescent="0.3">
+    <row r="85" x14ac:dyDescent="0.3">
       <c r="H85" s="26" t="str">
         <f>data_export!A60</f>
         <v>Gas (Li)</v>
@@ -6984,7 +6984,7 @@
         <v>0.61893330000000002</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="86" x14ac:dyDescent="0.3">
+    <row r="86" x14ac:dyDescent="0.3">
       <c r="H86" s="26" t="str">
         <f>data_export!A61</f>
         <v>Gas (Levin)</v>
@@ -7027,7 +7027,7 @@
         <v>0.65441349999999998</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="87" x14ac:dyDescent="0.3">
+    <row r="87" x14ac:dyDescent="0.3">
       <c r="H87" s="26" t="str">
         <f>data_export!A62</f>
         <v>Gas (Sentenac-Chemin)</v>
@@ -7070,7 +7070,7 @@
         <v>0.67320559999999996</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="88" s="23" customFormat="true" x14ac:dyDescent="0.3">
+    <row r="88" s="23" customFormat="true" x14ac:dyDescent="0.3">
       <c r="F88" s="25"/>
       <c r="G88" s="26"/>
       <c r="H88" s="26" t="str">
@@ -7121,7 +7121,7 @@
       <c r="W88" s="25"/>
       <c r="X88" s="24"/>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="89" x14ac:dyDescent="0.3">
+    <row r="89" x14ac:dyDescent="0.3">
       <c r="H89" s="26" t="str">
         <f>data_export!A64</f>
         <v>Gas (Gelman)</v>
@@ -7164,7 +7164,7 @@
         <v>0.81367109999999998</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="90" x14ac:dyDescent="0.3">
+    <row r="90" x14ac:dyDescent="0.3">
       <c r="H90" s="26" t="str">
         <f>data_export!A65</f>
         <v>Gas (Park)</v>
@@ -7207,7 +7207,7 @@
         <v>0.81778010000000001</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="91" x14ac:dyDescent="0.3">
+    <row r="91" x14ac:dyDescent="0.3">
       <c r="H91" s="26" t="str">
         <f>data_export!A66</f>
         <v>Gas (Hughes)</v>
@@ -7250,8 +7250,8 @@
         <v>0.9526964</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="92" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="93" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
+    <row r="92" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
+    <row r="93" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
       <c r="F93" s="37"/>
       <c r="G93" s="21" t="str">
         <f>data_export!A67</f>
@@ -7299,7 +7299,7 @@
       </c>
       <c r="U93" s="21"/>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="94" x14ac:dyDescent="0.3">
+    <row r="94" x14ac:dyDescent="0.3">
       <c r="H94" s="26" t="str">
         <f>data_export!A68</f>
         <v>Jet Fuel</v>
@@ -7342,7 +7342,7 @@
         <v>0.75395920000000005</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="95" x14ac:dyDescent="0.3">
+    <row r="95" x14ac:dyDescent="0.3">
       <c r="H95" s="26" t="str">
         <f>data_export!A69</f>
         <v>Diesel</v>
@@ -7385,8 +7385,8 @@
         <v>0.84163069999999995</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="96" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="97" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
+    <row r="96" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
+    <row r="97" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
       <c r="F97" s="37"/>
       <c r="G97" s="21" t="str">
         <f>data_export!A70</f>
@@ -7434,7 +7434,7 @@
       </c>
       <c r="U97" s="21"/>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="98" x14ac:dyDescent="0.3">
+    <row r="98" x14ac:dyDescent="0.3">
       <c r="H98" s="26" t="str">
         <f>data_export!A71</f>
         <v>CPP (AJ)</v>
@@ -7477,7 +7477,7 @@
         <v>0.4588798</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="99" x14ac:dyDescent="0.3">
+    <row r="99" x14ac:dyDescent="0.3">
       <c r="H99" s="26" t="str">
         <f>data_export!A72</f>
         <v>CARE</v>
@@ -7520,7 +7520,7 @@
         <v>0.71881779999999995</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="100" x14ac:dyDescent="0.3">
+    <row r="100" x14ac:dyDescent="0.3">
       <c r="H100" s="26" t="str">
         <f>data_export!A73</f>
         <v>CPP (PJ)</v>
@@ -7563,8 +7563,8 @@
         <v>0.78000899999999995</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="101" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="102" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
+    <row r="101" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
+    <row r="102" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
       <c r="F102" s="37"/>
       <c r="G102" s="21" t="str">
         <f>data_export!A74</f>
@@ -7612,7 +7612,7 @@
       </c>
       <c r="U102" s="21"/>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="103" x14ac:dyDescent="0.3">
+    <row r="103" x14ac:dyDescent="0.3">
       <c r="H103" s="26" t="str">
         <f>data_export!A75</f>
         <v>RGGI</v>
@@ -7655,7 +7655,7 @@
         <v>-0.67106120000000002</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="104" x14ac:dyDescent="0.3">
+    <row r="104" x14ac:dyDescent="0.3">
       <c r="H104" s="26" t="str">
         <f>data_export!A76</f>
         <v>CA CT</v>
@@ -7698,8 +7698,8 @@
         <v>0.94143829999999995</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="105" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="106" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
+    <row r="105" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
+    <row r="106" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
       <c r="F106" s="19" t="s">
         <v>3</v>
       </c>
@@ -7720,7 +7720,7 @@
       <c r="U106" s="24"/>
       <c r="W106" s="24"/>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="107" ht="10.2" customHeight="true" thickTop="true" x14ac:dyDescent="0.3">
+    <row r="107" ht="10.2" customHeight="true" thickTop="true" x14ac:dyDescent="0.3">
       <c r="F107" s="30"/>
       <c r="G107" s="30"/>
       <c r="H107" s="30"/>
@@ -7740,7 +7740,7 @@
       <c r="V107" s="30"/>
       <c r="W107" s="24"/>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="108" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
+    <row r="108" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
       <c r="F108" s="37"/>
       <c r="G108" s="21" t="str">
         <f>data_export!A77</f>
@@ -7788,7 +7788,7 @@
       </c>
       <c r="U108" s="21"/>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="109" x14ac:dyDescent="0.3">
+    <row r="109" x14ac:dyDescent="0.3">
       <c r="H109" s="26" t="str">
         <f>data_export!A78</f>
         <v>Cookstove (Kenya)</v>
@@ -7831,7 +7831,7 @@
         <v>323.4529</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="110" x14ac:dyDescent="0.3">
+    <row r="110" x14ac:dyDescent="0.3">
       <c r="H110" s="26" t="str">
         <f>data_export!A79</f>
         <v>Cookstove (India)</v>
@@ -7874,8 +7874,8 @@
         <v>-2.2788930000000001</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="111" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="112" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
+    <row r="111" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
+    <row r="112" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
       <c r="F112" s="37"/>
       <c r="G112" s="21" t="str">
         <f>data_export!A80</f>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="U112" s="21"/>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="113" x14ac:dyDescent="0.3">
+    <row r="113" x14ac:dyDescent="0.3">
       <c r="H113" s="26" t="str">
         <f>data_export!A81</f>
         <v>REDD+ (SL)</v>
@@ -7966,7 +7966,7 @@
         <v>119.4383</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="114" s="23" customFormat="true" x14ac:dyDescent="0.3">
+    <row r="114" s="23" customFormat="true" x14ac:dyDescent="0.3">
       <c r="F114" s="19"/>
       <c r="G114" s="26"/>
       <c r="H114" s="26" t="str">
@@ -8015,7 +8015,7 @@
       <c r="U114" s="19"/>
       <c r="V114" s="19"/>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="115" x14ac:dyDescent="0.3">
+    <row r="115" x14ac:dyDescent="0.3">
       <c r="H115" s="26" t="str">
         <f>data_export!A83</f>
         <v>REDD+</v>
@@ -8058,8 +8058,8 @@
         <v>4.1559650000000001</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="116" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="117" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
+    <row r="116" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
+    <row r="117" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
       <c r="F117" s="37"/>
       <c r="G117" s="21" t="str">
         <f>data_export!A84</f>
@@ -8107,7 +8107,7 @@
       </c>
       <c r="U117" s="21"/>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="118" x14ac:dyDescent="0.3">
+    <row r="118" x14ac:dyDescent="0.3">
       <c r="H118" s="26" t="str">
         <f>data_export!A85</f>
         <v>India PES (Upfront)</v>
@@ -8150,7 +8150,7 @@
         <v>14.66147</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="119" x14ac:dyDescent="0.3">
+    <row r="119" x14ac:dyDescent="0.3">
       <c r="H119" s="26" t="str">
         <f>data_export!A86</f>
         <v>India PES (Standard)</v>
@@ -8193,8 +8193,8 @@
         <v>10.749079999999999</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="120" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="121" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
+    <row r="120" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
+    <row r="121" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
       <c r="F121" s="37"/>
       <c r="G121" s="20" t="str">
         <f>data_export!A87</f>
@@ -8243,7 +8243,7 @@
       <c r="U121" s="21"/>
       <c r="V121" s="25"/>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="122" x14ac:dyDescent="0.3">
+    <row r="122" x14ac:dyDescent="0.3">
       <c r="H122" s="26" t="str">
         <f>data_export!A88</f>
         <v>Offset (India)</v>
@@ -8286,11 +8286,11 @@
         <v>7.6411709999999999</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="123" ht="10.2" customHeight="true" x14ac:dyDescent="0.3">
+    <row r="123" ht="10.2" customHeight="true" x14ac:dyDescent="0.3">
       <c r="H123" s="26"/>
       <c r="I123" s="26"/>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="124" s="23" customFormat="true" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
+    <row r="124" s="23" customFormat="true" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
       <c r="F124" s="19"/>
       <c r="G124" s="20" t="str">
         <f>data_export!A89</f>
@@ -8339,7 +8339,7 @@
       <c r="U124" s="21"/>
       <c r="V124" s="19"/>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="125" x14ac:dyDescent="0.3">
+    <row r="125" x14ac:dyDescent="0.3">
       <c r="H125" s="26" t="str">
         <f>data_export!A90</f>
         <v>Fridge (Mexico)</v>
@@ -8382,7 +8382,7 @@
         <v>0.85202619999999996</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="126" x14ac:dyDescent="0.3">
+    <row r="126" x14ac:dyDescent="0.3">
       <c r="H126" s="26" t="str">
         <f>data_export!A91</f>
         <v>AC (Mexico)</v>
@@ -8425,7 +8425,7 @@
         <v>0.67351689999999997</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="127" x14ac:dyDescent="0.3">
+    <row r="127" x14ac:dyDescent="0.3">
       <c r="H127" s="26" t="str">
         <f>data_export!A92</f>
         <v>WAP (Mexico)</v>
@@ -8468,8 +8468,8 @@
         <v>0.421819</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="128" ht="10.2" customHeight="true" thickBot="true" x14ac:dyDescent="0.35"/>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="129" ht="29.4" thickTop="true" x14ac:dyDescent="0.3">
+    <row r="128" ht="10.2" customHeight="true" thickBot="true" x14ac:dyDescent="0.35"/>
+    <row r="129" ht="29.4" thickTop="true" x14ac:dyDescent="0.3">
       <c r="F129" s="32"/>
       <c r="G129" s="32"/>
       <c r="H129" s="32"/>

--- a/outputs/Table1_scc193_main.xlsx
+++ b/outputs/Table1_scc193_main.xlsx
@@ -912,7 +912,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K92"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.6640625" style="1" bestFit="true" customWidth="true"/>
     <col min="2" max="2" width="57.88671875" style="1" bestFit="true" customWidth="true"/>
@@ -971,10 +971,10 @@
         <v>1</v>
       </c>
       <c r="C2" s="1">
-        <v>4.247780323028564</v>
+        <v>4.2477803230285645</v>
       </c>
       <c r="D2" s="1">
-        <v>1.90031755529949</v>
+        <v>1.9003175552994895</v>
       </c>
       <c r="E2" s="1">
         <v>0.6449316181257877</v>
@@ -983,19 +983,19 @@
         <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>7.793029627376487</v>
+        <v>7.7930296273764865</v>
       </c>
       <c r="H2" s="1">
-        <v>0.3276403248310089</v>
+        <v>0.32764032483100891</v>
       </c>
       <c r="I2" s="1">
-        <v>1.327640289731547</v>
+        <v>1.3276402897315467</v>
       </c>
       <c r="J2" s="1">
         <v>5.869835376739502</v>
       </c>
       <c r="K2" s="1">
-        <v>0.999999990375296</v>
+        <v>0.99999999037529597</v>
       </c>
     </row>
     <row r="3">
@@ -1006,28 +1006,28 @@
         <v>1</v>
       </c>
       <c r="C3" s="1">
-        <v>5.325597286224365</v>
+        <v>5.3255972862243652</v>
       </c>
       <c r="D3" s="1">
         <v>3.276528843806986</v>
       </c>
       <c r="E3" s="1">
-        <v>0.9196210415067382</v>
+        <v>0.91962104150673818</v>
       </c>
       <c r="F3" s="1">
         <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>10.52174704278041</v>
+        <v>10.521747042780412</v>
       </c>
       <c r="H3" s="1">
-        <v>0.3942200839519501</v>
+        <v>0.39422008395195007</v>
       </c>
       <c r="I3" s="1">
-        <v>1.394220063842681</v>
+        <v>1.3942200638426809</v>
       </c>
       <c r="J3" s="1">
-        <v>7.546690307827653</v>
+        <v>7.5466903078276531</v>
       </c>
       <c r="K3" s="1"/>
     </row>
@@ -1039,13 +1039,13 @@
         <v>1</v>
       </c>
       <c r="C4" s="1">
-        <v>3.966324806213379</v>
+        <v>3.9663248062133789</v>
       </c>
       <c r="D4" s="1">
-        <v>1.426829012813075</v>
+        <v>1.4268290128130754</v>
       </c>
       <c r="E4" s="1">
-        <v>0.5598809069152365</v>
+        <v>0.55988090691523651</v>
       </c>
       <c r="F4" s="1">
         <v>0</v>
@@ -1054,13 +1054,13 @@
         <v>6.95303471610241</v>
       </c>
       <c r="H4" s="1">
-        <v>0.3123733997344971</v>
+        <v>0.31237339973449707</v>
       </c>
       <c r="I4" s="1">
-        <v>1.312373375909993</v>
+        <v>1.3123733759099934</v>
       </c>
       <c r="J4" s="1">
-        <v>5.298061392994359</v>
+        <v>5.2980613929943594</v>
       </c>
       <c r="K4" s="1"/>
     </row>
@@ -1072,19 +1072,19 @@
         <v>1</v>
       </c>
       <c r="C5" s="1">
-        <v>3.451419353485107</v>
+        <v>3.4514193534851074</v>
       </c>
       <c r="D5" s="1">
-        <v>0.997594809278407</v>
+        <v>0.99759480927840705</v>
       </c>
       <c r="E5" s="1">
-        <v>0.4552929059553886</v>
+        <v>0.45529290595538857</v>
       </c>
       <c r="F5" s="1">
         <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>5.904307123246637</v>
+        <v>5.9043071232466371</v>
       </c>
       <c r="H5" s="1">
         <v>0.2763274610042572</v>
@@ -1093,7 +1093,7 @@
         <v>1.276327429441966</v>
       </c>
       <c r="J5" s="1">
-        <v>4.626012876514069</v>
+        <v>4.6260128765140687</v>
       </c>
       <c r="K5" s="1"/>
     </row>
@@ -1102,31 +1102,31 @@
         <v>19</v>
       </c>
       <c r="B6" s="1">
-        <v>1.105599999427795</v>
+        <v>1.1055999994277954</v>
       </c>
       <c r="C6" s="1">
-        <v>1.548539280891418</v>
+        <v>1.5485392808914185</v>
       </c>
       <c r="D6" s="1">
-        <v>2.279867155223056</v>
+        <v>2.2798671552230556</v>
       </c>
       <c r="E6" s="1">
-        <v>1.63564274674972</v>
+        <v>1.6356427467497199</v>
       </c>
       <c r="F6" s="1">
-        <v>-0.2137665003538132</v>
+        <v>-0.21376650035381317</v>
       </c>
       <c r="G6" s="1">
-        <v>6.355882713316444</v>
+        <v>6.3558827133164444</v>
       </c>
       <c r="H6" s="1">
-        <v>0.6458963751792908</v>
+        <v>0.64589637517929077</v>
       </c>
       <c r="I6" s="1">
-        <v>1.645896340749021</v>
+        <v>1.6458963407490212</v>
       </c>
       <c r="J6" s="1">
-        <v>3.861654281616211</v>
+        <v>3.8616542816162109</v>
       </c>
       <c r="K6" s="1">
         <v>1</v>
@@ -1140,28 +1140,28 @@
         <v>1</v>
       </c>
       <c r="C7" s="1">
-        <v>3.875874757766724</v>
+        <v>3.8758747577667236</v>
       </c>
       <c r="D7" s="1">
-        <v>4.987632538479263</v>
+        <v>4.9876325384792626</v>
       </c>
       <c r="E7" s="1">
-        <v>3.987389582709476</v>
+        <v>3.9873895827094756</v>
       </c>
       <c r="F7" s="1">
-        <v>-0.5350410938262939</v>
+        <v>-0.53504109382629395</v>
       </c>
       <c r="G7" s="1">
-        <v>13.31585581009459</v>
+        <v>13.315855810094593</v>
       </c>
       <c r="H7" s="1">
-        <v>1.629891872406006</v>
+        <v>1.6298918724060059</v>
       </c>
       <c r="I7" s="1">
-        <v>2.629891883666734</v>
+        <v>2.6298918836667342</v>
       </c>
       <c r="J7" s="1">
-        <v>5.063271191030456</v>
+        <v>5.0632711910304558</v>
       </c>
       <c r="K7" s="1"/>
     </row>
@@ -1173,28 +1173,28 @@
         <v>1</v>
       </c>
       <c r="C8" s="1">
-        <v>1.099670648574829</v>
+        <v>1.0996706485748291</v>
       </c>
       <c r="D8" s="1">
-        <v>3.132328211051226</v>
+        <v>3.1323282110512265</v>
       </c>
       <c r="E8" s="1">
-        <v>1.609878420829773</v>
+        <v>1.6098784208297734</v>
       </c>
       <c r="F8" s="1">
-        <v>-0.1518028825521469</v>
+        <v>-0.15180288255214691</v>
       </c>
       <c r="G8" s="1">
-        <v>6.690074366463067</v>
+        <v>6.6900743664630671</v>
       </c>
       <c r="H8" s="1">
         <v>0.4307093620300293</v>
       </c>
       <c r="I8" s="1">
-        <v>1.43070936778892</v>
+        <v>1.4307093677889202</v>
       </c>
       <c r="J8" s="1">
-        <v>4.67605407295417</v>
+        <v>4.6760540729541704</v>
       </c>
       <c r="K8" s="1"/>
     </row>
@@ -1203,28 +1203,28 @@
         <v>22</v>
       </c>
       <c r="B9" s="1">
-        <v>1.527999997138977</v>
+        <v>1.5279999971389771</v>
       </c>
       <c r="C9" s="1">
-        <v>1.446457147598267</v>
+        <v>1.4464571475982666</v>
       </c>
       <c r="D9" s="1">
-        <v>1.982251101496815</v>
+        <v>1.9822511014968154</v>
       </c>
       <c r="E9" s="1">
-        <v>1.371067404747009</v>
+        <v>1.3710674047470091</v>
       </c>
       <c r="F9" s="1">
-        <v>-0.1996746808290482</v>
+        <v>-0.19967468082904816</v>
       </c>
       <c r="G9" s="1">
-        <v>6.12810099612286</v>
+        <v>6.1281009961228596</v>
       </c>
       <c r="H9" s="1">
         <v>0.6061214804649353</v>
       </c>
       <c r="I9" s="1">
-        <v>1.606121434728078</v>
+        <v>1.6061214347280783</v>
       </c>
       <c r="J9" s="1">
         <v>3.815465545517962</v>
@@ -1239,28 +1239,28 @@
         <v>1</v>
       </c>
       <c r="C10" s="1">
-        <v>0.8401305079460144</v>
+        <v>0.84013050794601441</v>
       </c>
       <c r="D10" s="1">
-        <v>1.081114238039255</v>
+        <v>1.0811142380392549</v>
       </c>
       <c r="E10" s="1">
-        <v>0.8643024563789368</v>
+        <v>0.86430245637893677</v>
       </c>
       <c r="F10" s="1">
-        <v>-0.1159749403595924</v>
+        <v>-0.11597494035959244</v>
       </c>
       <c r="G10" s="1">
-        <v>3.66957227943602</v>
+        <v>3.6695722794360197</v>
       </c>
       <c r="H10" s="1">
-        <v>0.3532936573028564</v>
+        <v>0.35329365730285645</v>
       </c>
       <c r="I10" s="1">
-        <v>1.353293639765714</v>
+        <v>1.3532936397657145</v>
       </c>
       <c r="J10" s="1">
-        <v>2.711586141845243</v>
+        <v>2.7115861418452432</v>
       </c>
       <c r="K10" s="1"/>
     </row>
@@ -1272,22 +1272,22 @@
         <v>1</v>
       </c>
       <c r="C11" s="1">
-        <v>0.4805634319782257</v>
+        <v>0.48056343197822571</v>
       </c>
       <c r="D11" s="1">
-        <v>0.2160096870487183</v>
+        <v>0.21600968704871831</v>
       </c>
       <c r="E11" s="1">
-        <v>0.3455758690834045</v>
+        <v>0.34557586908340449</v>
       </c>
       <c r="F11" s="1">
-        <v>-0.06633888185024261</v>
+        <v>-0.066338881850242615</v>
       </c>
       <c r="G11" s="1">
-        <v>1.975810114465683</v>
+        <v>1.9758101144656826</v>
       </c>
       <c r="H11" s="1">
-        <v>0.2094653695821762</v>
+        <v>0.20946536958217621</v>
       </c>
       <c r="I11" s="1">
         <v>1.209465377795659</v>
@@ -1305,28 +1305,28 @@
         <v>1</v>
       </c>
       <c r="C12" s="1">
-        <v>0.08899783343076706</v>
+        <v>0.088997833430767059</v>
       </c>
       <c r="D12" s="1">
-        <v>0.07337944031894673</v>
+        <v>0.073379440318946734</v>
       </c>
       <c r="E12" s="1">
-        <v>0.4512390265862147</v>
+        <v>0.45123902658621473</v>
       </c>
       <c r="F12" s="1">
-        <v>-0.04278992861509323</v>
+        <v>-0.042789928615093231</v>
       </c>
       <c r="G12" s="1">
-        <v>1.57082636794944</v>
+        <v>1.5708263679494401</v>
       </c>
       <c r="H12" s="1">
-        <v>0.08715097606182098</v>
+        <v>0.087150976061820984</v>
       </c>
       <c r="I12" s="1">
-        <v>1.087150972585287</v>
+        <v>1.0871509725852866</v>
       </c>
       <c r="J12" s="1">
-        <v>1.444901823997498</v>
+        <v>1.4449018239974976</v>
       </c>
       <c r="K12" s="1">
         <v>1</v>
@@ -1340,22 +1340,22 @@
         <v>1</v>
       </c>
       <c r="C13" s="1">
-        <v>0.1067965552210808</v>
+        <v>0.10679655522108078</v>
       </c>
       <c r="D13" s="1">
-        <v>0.1027528815342486</v>
+        <v>0.10275288153424859</v>
       </c>
       <c r="E13" s="1">
-        <v>0.5631865859031677</v>
+        <v>0.56318658590316773</v>
       </c>
       <c r="F13" s="1">
-        <v>-0.0513475090265274</v>
+        <v>-0.051347509026527405</v>
       </c>
       <c r="G13" s="1">
-        <v>1.721388510902716</v>
+        <v>1.7213885109027161</v>
       </c>
       <c r="H13" s="1">
-        <v>0.1028937548398972</v>
+        <v>0.10289375483989716</v>
       </c>
       <c r="I13" s="1">
         <v>1.102893754428349</v>
@@ -1376,25 +1376,25 @@
         <v>0.09515073150396347</v>
       </c>
       <c r="D14" s="1">
-        <v>0.0777344269905985</v>
+        <v>0.077734426990598501</v>
       </c>
       <c r="E14" s="1">
-        <v>0.4816110730171204</v>
+        <v>0.48161107301712042</v>
       </c>
       <c r="F14" s="1">
-        <v>-0.04574823006987572</v>
+        <v>-0.045748230069875717</v>
       </c>
       <c r="G14" s="1">
         <v>1.608748003206723</v>
       </c>
       <c r="H14" s="1">
-        <v>0.09191800653934479</v>
+        <v>0.091918006539344788</v>
       </c>
       <c r="I14" s="1">
         <v>1.091918002728935</v>
       </c>
       <c r="J14" s="1">
-        <v>1.473323087618411</v>
+        <v>1.4733230876184109</v>
       </c>
       <c r="K14" s="1"/>
     </row>
@@ -1406,7 +1406,7 @@
         <v>1</v>
       </c>
       <c r="C15" s="1">
-        <v>0.06504620611667633</v>
+        <v>0.065046206116676331</v>
       </c>
       <c r="D15" s="1">
         <v>0.0396510124319931</v>
@@ -1421,13 +1421,13 @@
         <v>1.382342589738881</v>
       </c>
       <c r="H15" s="1">
-        <v>0.06664115935564041</v>
+        <v>0.066641159355640411</v>
       </c>
       <c r="I15" s="1">
         <v>1.066641160598576</v>
       </c>
       <c r="J15" s="1">
-        <v>1.295977167206955</v>
+        <v>1.2959771672069551</v>
       </c>
       <c r="K15" s="1"/>
     </row>
@@ -1436,10 +1436,10 @@
         <v>29</v>
       </c>
       <c r="B16" s="1">
-        <v>0.8674782514572144</v>
+        <v>0.86747825145721436</v>
       </c>
       <c r="C16" s="1">
-        <v>0.4506498575210571</v>
+        <v>0.45064985752105713</v>
       </c>
       <c r="D16" s="1">
         <v>0</v>
@@ -1448,19 +1448,19 @@
         <v>0</v>
       </c>
       <c r="F16" s="1">
-        <v>-0.1031324416399002</v>
+        <v>-0.10313244163990021</v>
       </c>
       <c r="G16" s="1">
-        <v>1.214995665926638</v>
+        <v>1.2149956659266381</v>
       </c>
       <c r="H16" s="1">
-        <v>0.04358679056167603</v>
+        <v>0.043586790561676025</v>
       </c>
       <c r="I16" s="1">
-        <v>1.043586792629843</v>
+        <v>1.0435867926298426</v>
       </c>
       <c r="J16" s="1">
-        <v>1.164249777793884</v>
+        <v>1.1642497777938843</v>
       </c>
       <c r="K16" s="1">
         <v>1.000000001580061</v>
@@ -1471,10 +1471,10 @@
         <v>30</v>
       </c>
       <c r="B17" s="1">
-        <v>0.9524999856948853</v>
+        <v>0.95249998569488525</v>
       </c>
       <c r="C17" s="1">
-        <v>0.5088033676147461</v>
+        <v>0.50880336761474609</v>
       </c>
       <c r="D17" s="1">
         <v>0</v>
@@ -1483,19 +1483,19 @@
         <v>0</v>
       </c>
       <c r="F17" s="1">
-        <v>-0.03875209018588066</v>
+        <v>-0.038752090185880661</v>
       </c>
       <c r="G17" s="1">
-        <v>1.422551245702855</v>
+        <v>1.4225512457028553</v>
       </c>
       <c r="H17" s="1">
-        <v>0.01241566520184278</v>
+        <v>0.012415665201842785</v>
       </c>
       <c r="I17" s="1">
-        <v>1.012415658662605</v>
+        <v>1.0124156586626045</v>
       </c>
       <c r="J17" s="1">
-        <v>1.405105930090056</v>
+        <v>1.4051059300900559</v>
       </c>
       <c r="K17" s="1"/>
     </row>
@@ -1504,10 +1504,10 @@
         <v>32</v>
       </c>
       <c r="B18" s="1">
-        <v>0.5978260636329651</v>
+        <v>0.59782606363296509</v>
       </c>
       <c r="C18" s="1">
-        <v>1.505917191505432</v>
+        <v>1.5059171915054321</v>
       </c>
       <c r="D18" s="1">
         <v>0</v>
@@ -1516,16 +1516,16 @@
         <v>0</v>
       </c>
       <c r="F18" s="1">
-        <v>-0.6586786508560181</v>
+        <v>-0.65867865085601807</v>
       </c>
       <c r="G18" s="1">
         <v>1.445064617251252</v>
       </c>
       <c r="H18" s="1">
-        <v>0.07837533205747604</v>
+        <v>0.078375332057476044</v>
       </c>
       <c r="I18" s="1">
-        <v>1.078375303946742</v>
+        <v>1.0783753039467419</v>
       </c>
       <c r="J18" s="1">
         <v>1.340038678521722</v>
@@ -1540,7 +1540,7 @@
         <v>1</v>
       </c>
       <c r="C19" s="1">
-        <v>0.7938316464424133</v>
+        <v>0.79383164644241333</v>
       </c>
       <c r="D19" s="1">
         <v>0</v>
@@ -1549,19 +1549,19 @@
         <v>0</v>
       </c>
       <c r="F19" s="1">
-        <v>-0.07186365872621536</v>
+        <v>-0.071863658726215363</v>
       </c>
       <c r="G19" s="1">
-        <v>1.721967964438142</v>
+        <v>1.7219679644381421</v>
       </c>
       <c r="H19" s="1">
-        <v>0.3148359954357147</v>
+        <v>0.31483599543571472</v>
       </c>
       <c r="I19" s="1">
         <v>1.314835995386064</v>
       </c>
       <c r="J19" s="1">
-        <v>1.309644678485194</v>
+        <v>1.3096446784851941</v>
       </c>
       <c r="K19" s="1"/>
     </row>
@@ -1570,10 +1570,10 @@
         <v>33</v>
       </c>
       <c r="B20" s="1">
-        <v>0.9294999837875366</v>
+        <v>0.92949998378753662</v>
       </c>
       <c r="C20" s="1">
-        <v>0.2253946214914322</v>
+        <v>0.22539462149143219</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
@@ -1582,16 +1582,16 @@
         <v>0</v>
       </c>
       <c r="F20" s="1">
-        <v>-0.01661630347371101</v>
+        <v>-0.016616303473711014</v>
       </c>
       <c r="G20" s="1">
-        <v>1.138278350379594</v>
+        <v>1.1382783503795941</v>
       </c>
       <c r="H20" s="1">
-        <v>0.0052036396227777</v>
+        <v>0.0052036396227777004</v>
       </c>
       <c r="I20" s="1">
-        <v>1.00520367046613</v>
+        <v>1.0052036704661302</v>
       </c>
       <c r="J20" s="1">
         <v>1.132385787898839</v>
@@ -1606,7 +1606,7 @@
         <v>1</v>
       </c>
       <c r="C21" s="1">
-        <v>-0.2053293734788895</v>
+        <v>-0.20532937347888947</v>
       </c>
       <c r="D21" s="1">
         <v>0</v>
@@ -1615,19 +1615,19 @@
         <v>0</v>
       </c>
       <c r="F21" s="1">
-        <v>0.01858797296881676</v>
+        <v>0.018587972968816757</v>
       </c>
       <c r="G21" s="1">
-        <v>0.8132585916279141</v>
+        <v>0.81325859162791414</v>
       </c>
       <c r="H21" s="1">
-        <v>-0.2279526889324188</v>
+        <v>-0.22795268893241882</v>
       </c>
       <c r="I21" s="1">
-        <v>0.7720472998566242</v>
+        <v>0.77204729985662424</v>
       </c>
       <c r="J21" s="1">
-        <v>1.053379231789222</v>
+        <v>1.0533792317892221</v>
       </c>
       <c r="K21" s="1"/>
     </row>
@@ -1636,7 +1636,7 @@
         <v>34</v>
       </c>
       <c r="B22" s="1">
-        <v>0.9599999189376831</v>
+        <v>0.95999991893768311</v>
       </c>
       <c r="C22" s="1">
         <v>0.09147227555513382</v>
@@ -1648,19 +1648,19 @@
         <v>0</v>
       </c>
       <c r="F22" s="1">
-        <v>-0.007180713582783937</v>
+        <v>-0.0071807135827839375</v>
       </c>
       <c r="G22" s="1">
         <v>1.044291550132193</v>
       </c>
       <c r="H22" s="1">
-        <v>0.002347236732020974</v>
+        <v>0.0023472367320209742</v>
       </c>
       <c r="I22" s="1">
-        <v>1.002347224599736</v>
+        <v>1.0023472245997365</v>
       </c>
       <c r="J22" s="1">
-        <v>1.041846103329319</v>
+        <v>1.0418461033293189</v>
       </c>
       <c r="K22" s="1"/>
     </row>
@@ -1672,7 +1672,7 @@
         <v>1</v>
       </c>
       <c r="C23" s="1">
-        <v>0.1832726746797562</v>
+        <v>0.18327267467975616</v>
       </c>
       <c r="D23" s="1">
         <v>0</v>
@@ -1681,19 +1681,19 @@
         <v>0</v>
       </c>
       <c r="F23" s="1">
-        <v>-0.01659123227000237</v>
+        <v>-0.016591232270002365</v>
       </c>
       <c r="G23" s="1">
         <v>1.166681438228496</v>
       </c>
       <c r="H23" s="1">
-        <v>0.1535091400146484</v>
+        <v>0.15350914001464844</v>
       </c>
       <c r="I23" s="1">
-        <v>1.15350914563875</v>
+        <v>1.1535091456387501</v>
       </c>
       <c r="J23" s="1">
-        <v>1.011419322195709</v>
+        <v>1.0114193221957091</v>
       </c>
       <c r="K23" s="1"/>
     </row>
@@ -1705,7 +1705,7 @@
         <v>0.5</v>
       </c>
       <c r="C24" s="1">
-        <v>0.5018364191055298</v>
+        <v>0.50183641910552979</v>
       </c>
       <c r="D24" s="1">
         <v>0</v>
@@ -1714,19 +1714,19 @@
         <v>0</v>
       </c>
       <c r="F24" s="1">
-        <v>-0.0339648611843586</v>
+        <v>-0.033964861184358597</v>
       </c>
       <c r="G24" s="1">
-        <v>0.9678715696526574</v>
+        <v>0.96787156965265742</v>
       </c>
       <c r="H24" s="1">
-        <v>0.009960019029676914</v>
+        <v>0.0099600190296769142</v>
       </c>
       <c r="I24" s="1">
-        <v>1.00996004248209</v>
+        <v>1.0099600424820896</v>
       </c>
       <c r="J24" s="1">
-        <v>0.9583265960443396</v>
+        <v>0.95832659604433956</v>
       </c>
       <c r="K24" s="1"/>
     </row>
@@ -1735,10 +1735,10 @@
         <v>38</v>
       </c>
       <c r="B25" s="1">
-        <v>0.9101123809814453</v>
+        <v>0.91011238098144531</v>
       </c>
       <c r="C25" s="1">
-        <v>0.2452400028705597</v>
+        <v>0.24524000287055969</v>
       </c>
       <c r="D25" s="1">
         <v>0</v>
@@ -1750,19 +1750,19 @@
         <v>-0.04927363246679306</v>
       </c>
       <c r="G25" s="1">
-        <v>1.106078710640788</v>
+        <v>1.1060787106407883</v>
       </c>
       <c r="H25" s="1">
-        <v>0.05597669258713722</v>
+        <v>0.055976692587137222</v>
       </c>
       <c r="I25" s="1">
-        <v>1.055976660841203</v>
+        <v>1.0559766608412027</v>
       </c>
       <c r="J25" s="1">
-        <v>1.047446131706238</v>
+        <v>1.0474461317062378</v>
       </c>
       <c r="K25" s="1">
-        <v>0.9999999693093836</v>
+        <v>0.99999996930938362</v>
       </c>
     </row>
     <row r="26">
@@ -1773,7 +1773,7 @@
         <v>1</v>
       </c>
       <c r="C26" s="1">
-        <v>0.2313006520271301</v>
+        <v>0.23130065202713013</v>
       </c>
       <c r="D26" s="1">
         <v>0</v>
@@ -1782,19 +1782,19 @@
         <v>0</v>
       </c>
       <c r="F26" s="1">
-        <v>-0.07409835606813431</v>
+        <v>-0.074098356068134308</v>
       </c>
       <c r="G26" s="1">
-        <v>1.157202266720284</v>
+        <v>1.1572022667202842</v>
       </c>
       <c r="H26" s="1">
-        <v>0.08441157639026642</v>
+        <v>0.084411576390266419</v>
       </c>
       <c r="I26" s="1">
-        <v>1.084411542875995</v>
+        <v>1.0844115428759953</v>
       </c>
       <c r="J26" s="1">
-        <v>1.067124630240691</v>
+        <v>1.0671246302406909</v>
       </c>
       <c r="K26" s="1"/>
     </row>
@@ -1806,7 +1806,7 @@
         <v>1</v>
       </c>
       <c r="C27" s="1">
-        <v>0.1507279425859451</v>
+        <v>0.15072794258594513</v>
       </c>
       <c r="D27" s="1">
         <v>0</v>
@@ -1815,16 +1815,16 @@
         <v>0</v>
       </c>
       <c r="F27" s="1">
-        <v>-0.04860733821988106</v>
+        <v>-0.048607338219881058</v>
       </c>
       <c r="G27" s="1">
-        <v>1.102120576379071</v>
+        <v>1.1021205763790709</v>
       </c>
       <c r="H27" s="1">
-        <v>0.05538089945912361</v>
+        <v>0.055380899459123611</v>
       </c>
       <c r="I27" s="1">
-        <v>1.055380872892797</v>
+        <v>1.0553808728927971</v>
       </c>
       <c r="J27" s="1">
         <v>1.044287048104406</v>
@@ -1836,10 +1836,10 @@
         <v>40</v>
       </c>
       <c r="B28" s="1">
-        <v>0.7303370833396912</v>
+        <v>0.73033708333969116</v>
       </c>
       <c r="C28" s="1">
-        <v>0.353691428899765</v>
+        <v>0.35369142889976501</v>
       </c>
       <c r="D28" s="1">
         <v>0</v>
@@ -1848,19 +1848,19 @@
         <v>0</v>
       </c>
       <c r="F28" s="1">
-        <v>-0.02511520124971867</v>
+        <v>-0.025115201249718666</v>
       </c>
       <c r="G28" s="1">
-        <v>1.05891328882301</v>
+        <v>1.0589132888230104</v>
       </c>
       <c r="H28" s="1">
-        <v>0.02813760377466679</v>
+        <v>0.028137603774666786</v>
       </c>
       <c r="I28" s="1">
-        <v>1.028137566754816</v>
+        <v>1.0281375667548163</v>
       </c>
       <c r="J28" s="1">
-        <v>1.029933467138385</v>
+        <v>1.0299334671383851</v>
       </c>
       <c r="K28" s="1"/>
     </row>
@@ -1872,28 +1872,28 @@
         <v>1</v>
       </c>
       <c r="C29" s="1">
-        <v>0.008138339966535568</v>
+        <v>0.0081383399665355682</v>
       </c>
       <c r="D29" s="1">
-        <v>0.0003880297072260934</v>
+        <v>0.00038802970722609341</v>
       </c>
       <c r="E29" s="1">
-        <v>0.0138015088547642</v>
+        <v>0.013801508854764199</v>
       </c>
       <c r="F29" s="1">
-        <v>-0.006431082729250193</v>
+        <v>-0.0064310827292501926</v>
       </c>
       <c r="G29" s="1">
-        <v>1.015896795890685</v>
+        <v>1.0158967958906851</v>
       </c>
       <c r="H29" s="1">
-        <v>0.003683982416987419</v>
+        <v>0.0036839824169874191</v>
       </c>
       <c r="I29" s="1">
-        <v>1.003683982574839</v>
+        <v>1.0036839825748389</v>
       </c>
       <c r="J29" s="1">
-        <v>1.012167930603027</v>
+        <v>1.0121679306030274</v>
       </c>
       <c r="K29" s="1">
         <v>1</v>
@@ -1910,19 +1910,19 @@
         <v>0.01809588260948658</v>
       </c>
       <c r="D30" s="1">
-        <v>0.0010730455552728</v>
+        <v>0.0010730455552728001</v>
       </c>
       <c r="E30" s="1">
-        <v>0.0308205578476191</v>
+        <v>0.030820557847619098</v>
       </c>
       <c r="F30" s="1">
-        <v>-0.01429973635822535</v>
+        <v>-0.014299736358225346</v>
       </c>
       <c r="G30" s="1">
-        <v>1.035689749343374</v>
+        <v>1.0356897493433741</v>
       </c>
       <c r="H30" s="1">
-        <v>0.008183262310922146</v>
+        <v>0.0081832623109221458</v>
       </c>
       <c r="I30" s="1">
         <v>1.008183262619448</v>
@@ -1940,16 +1940,16 @@
         <v>1</v>
       </c>
       <c r="C31" s="1">
-        <v>0.005193197168409824</v>
+        <v>0.0051931971684098244</v>
       </c>
       <c r="D31" s="1">
-        <v>8.69754471621e-05</v>
+        <v>8.6975447162100005e-05</v>
       </c>
       <c r="E31" s="1">
-        <v>0.008705806918442201</v>
+        <v>0.0087058069184422007</v>
       </c>
       <c r="F31" s="1">
-        <v>-0.004103770479559898</v>
+        <v>-0.0041037704795598984</v>
       </c>
       <c r="G31" s="1">
         <v>1.009882208940174</v>
@@ -1958,10 +1958,10 @@
         <v>0.002357069868594408</v>
       </c>
       <c r="I31" s="1">
-        <v>1.002357069988376</v>
+        <v>1.0023570699883759</v>
       </c>
       <c r="J31" s="1">
-        <v>1.007507443382312</v>
+        <v>1.0075074433823119</v>
       </c>
       <c r="K31" s="1"/>
     </row>
@@ -1973,28 +1973,28 @@
         <v>1</v>
       </c>
       <c r="C32" s="1">
-        <v>0.001125941402278841</v>
+        <v>0.0011259414022788405</v>
       </c>
       <c r="D32" s="1">
-        <v>4.06811924338e-06</v>
+        <v>4.0681192433799998e-06</v>
       </c>
       <c r="E32" s="1">
         <v>0.0018781617982313</v>
       </c>
       <c r="F32" s="1">
-        <v>-0.0008897418738342822</v>
+        <v>-0.00088974187383428216</v>
       </c>
       <c r="G32" s="1">
         <v>1.002118429388507</v>
       </c>
       <c r="H32" s="1">
-        <v>0.0005116151296533644</v>
+        <v>0.00051161512965336442</v>
       </c>
       <c r="I32" s="1">
-        <v>1.000511615116693</v>
+        <v>1.0005116151166931</v>
       </c>
       <c r="J32" s="1">
-        <v>1.001605992621711</v>
+        <v>1.0016059926217109</v>
       </c>
       <c r="K32" s="1"/>
     </row>
@@ -2003,10 +2003,10 @@
         <v>46</v>
       </c>
       <c r="B33" s="1">
-        <v>0.7740969061851501</v>
+        <v>0.77409690618515015</v>
       </c>
       <c r="C33" s="1">
-        <v>0.2691713571548462</v>
+        <v>0.26917135715484619</v>
       </c>
       <c r="D33" s="1">
         <v>0</v>
@@ -2015,19 +2015,19 @@
         <v>0</v>
       </c>
       <c r="F33" s="1">
-        <v>-0.05413472279906273</v>
+        <v>-0.054134722799062729</v>
       </c>
       <c r="G33" s="1">
-        <v>0.9891335470233262</v>
+        <v>0.98913354702332623</v>
       </c>
       <c r="H33" s="1">
-        <v>0.01176544092595577</v>
+        <v>0.011765440925955772</v>
       </c>
       <c r="I33" s="1">
-        <v>1.011765435925297</v>
+        <v>1.0117654359252968</v>
       </c>
       <c r="J33" s="1">
-        <v>0.9776312708854675</v>
+        <v>0.97763127088546753</v>
       </c>
       <c r="K33" s="1">
         <v>0.9999999950671693</v>
@@ -2038,7 +2038,7 @@
         <v>47</v>
       </c>
       <c r="B34" s="1">
-        <v>0.7500000596046448</v>
+        <v>0.75000005960464478</v>
       </c>
       <c r="C34" s="1">
         <v>0.5441010594367981</v>
@@ -2050,16 +2050,16 @@
         <v>0</v>
       </c>
       <c r="F34" s="1">
-        <v>-0.05745778232812881</v>
+        <v>-0.057457782328128815</v>
       </c>
       <c r="G34" s="1">
-        <v>1.236643274101312</v>
+        <v>1.2366432741013118</v>
       </c>
       <c r="H34" s="1">
-        <v>0.02189368382096291</v>
+        <v>0.021893683820962906</v>
       </c>
       <c r="I34" s="1">
-        <v>1.021893715593554</v>
+        <v>1.0218937155935541</v>
       </c>
       <c r="J34" s="1">
         <v>1.210148624295065</v>
@@ -2074,7 +2074,7 @@
         <v>0.75</v>
       </c>
       <c r="C35" s="1">
-        <v>0.3591663837432861</v>
+        <v>0.35916638374328613</v>
       </c>
       <c r="D35" s="1">
         <v>0</v>
@@ -2083,19 +2083,19 @@
         <v>0</v>
       </c>
       <c r="F35" s="1">
-        <v>-0.1105858981609344</v>
+        <v>-0.11058589816093445</v>
       </c>
       <c r="G35" s="1">
-        <v>0.9985804751238465</v>
+        <v>0.99858047512384651</v>
       </c>
       <c r="H35" s="1">
-        <v>0.01876973733305931</v>
+        <v>0.018769737333059311</v>
       </c>
       <c r="I35" s="1">
-        <v>1.018769706614854</v>
+        <v>1.0187697066148542</v>
       </c>
       <c r="J35" s="1">
-        <v>0.9801827328002399</v>
+        <v>0.98018273280023993</v>
       </c>
       <c r="K35" s="1"/>
     </row>
@@ -2104,10 +2104,10 @@
         <v>51</v>
       </c>
       <c r="B36" s="1">
-        <v>0.8704845905303955</v>
+        <v>0.87048459053039551</v>
       </c>
       <c r="C36" s="1">
-        <v>0.05016213655471802</v>
+        <v>0.050162136554718018</v>
       </c>
       <c r="D36" s="1">
         <v>0</v>
@@ -2116,19 +2116,19 @@
         <v>0</v>
       </c>
       <c r="F36" s="1">
-        <v>-0.001053069834597409</v>
+        <v>-0.0010530698345974088</v>
       </c>
       <c r="G36" s="1">
-        <v>0.9195936517186143</v>
+        <v>0.91959365171861429</v>
       </c>
       <c r="H36" s="1">
-        <v>-0.0002386562700849026</v>
+        <v>-0.00023865627008490265</v>
       </c>
       <c r="I36" s="1">
-        <v>0.9997613469639198</v>
+        <v>0.99976134696391983</v>
       </c>
       <c r="J36" s="1">
-        <v>0.9198131679237658</v>
+        <v>0.91981316792376577</v>
       </c>
       <c r="K36" s="1"/>
     </row>
@@ -2137,10 +2137,10 @@
         <v>49</v>
       </c>
       <c r="B37" s="1">
-        <v>0.7500000596046448</v>
+        <v>0.75000005960464478</v>
       </c>
       <c r="C37" s="1">
-        <v>0.2654865086078644</v>
+        <v>0.26548650860786438</v>
       </c>
       <c r="D37" s="1">
         <v>0</v>
@@ -2152,16 +2152,16 @@
         <v>-0.08817175030708313</v>
       </c>
       <c r="G37" s="1">
-        <v>0.9273147529637772</v>
+        <v>0.92731475296377719</v>
       </c>
       <c r="H37" s="1">
-        <v>0.01329456549137831</v>
+        <v>0.013294565491378307</v>
       </c>
       <c r="I37" s="1">
-        <v>1.013294567324693</v>
+        <v>1.0132945673246929</v>
       </c>
       <c r="J37" s="1">
-        <v>0.9151482529034768</v>
+        <v>0.91514825290347679</v>
       </c>
       <c r="K37" s="1"/>
     </row>
@@ -2170,10 +2170,10 @@
         <v>50</v>
       </c>
       <c r="B38" s="1">
-        <v>0.7499999403953552</v>
+        <v>0.74999994039535523</v>
       </c>
       <c r="C38" s="1">
-        <v>0.1269407123327255</v>
+        <v>0.12694071233272552</v>
       </c>
       <c r="D38" s="1">
         <v>0</v>
@@ -2182,19 +2182,19 @@
         <v>0</v>
       </c>
       <c r="F38" s="1">
-        <v>-0.01340510509908199</v>
+        <v>-0.013405105099081993</v>
       </c>
       <c r="G38" s="1">
-        <v>0.863535581209082</v>
+        <v>0.86353558120908203</v>
       </c>
       <c r="H38" s="1">
-        <v>0.005107874516397715</v>
+        <v>0.0051078745163977146</v>
       </c>
       <c r="I38" s="1">
-        <v>1.005107843129462</v>
+        <v>1.0051078431294624</v>
       </c>
       <c r="J38" s="1">
-        <v>0.8591471921265812</v>
+        <v>0.85914719212658119</v>
       </c>
       <c r="K38" s="1"/>
     </row>
@@ -2203,10 +2203,10 @@
         <v>52</v>
       </c>
       <c r="B39" s="1">
-        <v>0.8874900341033936</v>
+        <v>0.88749003410339355</v>
       </c>
       <c r="C39" s="1">
-        <v>1.694997787475586</v>
+        <v>1.6949977874755859</v>
       </c>
       <c r="D39" s="1">
         <v>0</v>
@@ -2215,22 +2215,22 @@
         <v>0</v>
       </c>
       <c r="F39" s="1">
-        <v>-0.06537312269210815</v>
+        <v>-0.065373122692108154</v>
       </c>
       <c r="G39" s="1">
-        <v>2.517114737056049</v>
+        <v>2.5171147370560494</v>
       </c>
       <c r="H39" s="1">
-        <v>0.01012879982590675</v>
+        <v>0.010128799825906754</v>
       </c>
       <c r="I39" s="1">
-        <v>1.01012878883256</v>
+        <v>1.0101287888325596</v>
       </c>
       <c r="J39" s="1">
         <v>2.491875171661377</v>
       </c>
       <c r="K39" s="1">
-        <v>0.9999999909275857</v>
+        <v>0.99999999092758574</v>
       </c>
     </row>
     <row r="40">
@@ -2238,10 +2238,10 @@
         <v>53</v>
       </c>
       <c r="B40" s="1">
-        <v>0.8821229338645935</v>
+        <v>0.88212293386459351</v>
       </c>
       <c r="C40" s="1">
-        <v>1.919402241706848</v>
+        <v>1.9194022417068481</v>
       </c>
       <c r="D40" s="1">
         <v>0</v>
@@ -2250,16 +2250,16 @@
         <v>0</v>
       </c>
       <c r="F40" s="1">
-        <v>-0.1307462453842163</v>
+        <v>-0.13074624538421631</v>
       </c>
       <c r="G40" s="1">
         <v>2.670778997480296</v>
       </c>
       <c r="H40" s="1">
-        <v>0.03820458054542542</v>
+        <v>0.038204580545425415</v>
       </c>
       <c r="I40" s="1">
-        <v>1.03820455899704</v>
+        <v>1.0382045589970401</v>
       </c>
       <c r="J40" s="1">
         <v>2.572497851541327</v>
@@ -2271,10 +2271,10 @@
         <v>54</v>
       </c>
       <c r="B41" s="1">
-        <v>0.8928570747375488</v>
+        <v>0.89285707473754883</v>
       </c>
       <c r="C41" s="1">
-        <v>1.470593333244324</v>
+        <v>1.4705933332443237</v>
       </c>
       <c r="D41" s="1">
         <v>0</v>
@@ -2286,16 +2286,16 @@
         <v>0</v>
       </c>
       <c r="G41" s="1">
-        <v>2.363450476631802</v>
+        <v>2.3634504766318023</v>
       </c>
       <c r="H41" s="1">
-        <v>-0.01794698089361191</v>
+        <v>-0.017946980893611908</v>
       </c>
       <c r="I41" s="1">
-        <v>0.9820530186680789</v>
+        <v>0.98205301866807893</v>
       </c>
       <c r="J41" s="1">
-        <v>2.406642443640426</v>
+        <v>2.4066424436404259</v>
       </c>
       <c r="K41" s="1"/>
     </row>
@@ -2307,7 +2307,7 @@
         <v>0</v>
       </c>
       <c r="C42" s="1">
-        <v>1.876076102256775</v>
+        <v>1.8760761022567749</v>
       </c>
       <c r="D42" s="1">
         <v>0</v>
@@ -2316,22 +2316,22 @@
         <v>0</v>
       </c>
       <c r="F42" s="1">
-        <v>-0.03017378225922585</v>
+        <v>-0.030173782259225845</v>
       </c>
       <c r="G42" s="1">
-        <v>1.845902282344704</v>
+        <v>1.8459022823447036</v>
       </c>
       <c r="H42" s="1">
         <v>-0.05101698637008667</v>
       </c>
       <c r="I42" s="1">
-        <v>0.9489830033198187</v>
+        <v>0.94898300331981866</v>
       </c>
       <c r="J42" s="1">
-        <v>1.94513738155365</v>
+        <v>1.9451373815536499</v>
       </c>
       <c r="K42" s="1">
-        <v>0.9999999937332515</v>
+        <v>0.99999999373325155</v>
       </c>
     </row>
     <row r="43">
@@ -2342,7 +2342,7 @@
         <v>0</v>
       </c>
       <c r="C43" s="1">
-        <v>3.466387033462524</v>
+        <v>3.4663870334625244</v>
       </c>
       <c r="D43" s="1">
         <v>0</v>
@@ -2351,19 +2351,19 @@
         <v>0</v>
       </c>
       <c r="F43" s="1">
-        <v>-0.2442773580551147</v>
+        <v>-0.24427735805511475</v>
       </c>
       <c r="G43" s="1">
-        <v>3.222109586631588</v>
+        <v>3.2221095866315883</v>
       </c>
       <c r="H43" s="1">
-        <v>0.07189196348190308</v>
+        <v>0.071891963481903076</v>
       </c>
       <c r="I43" s="1">
-        <v>1.071891917264832</v>
+        <v>1.0718919172648322</v>
       </c>
       <c r="J43" s="1">
-        <v>3.006002316776032</v>
+        <v>3.0060023167760321</v>
       </c>
       <c r="K43" s="1"/>
     </row>
@@ -2375,7 +2375,7 @@
         <v>0</v>
       </c>
       <c r="C44" s="1">
-        <v>2.906033754348755</v>
+        <v>2.9060337543487549</v>
       </c>
       <c r="D44" s="1">
         <v>0</v>
@@ -2384,19 +2384,19 @@
         <v>0</v>
       </c>
       <c r="F44" s="1">
-        <v>-0.2047890871763229</v>
+        <v>-0.20478908717632294</v>
       </c>
       <c r="G44" s="1">
-        <v>2.701244689890932</v>
+        <v>2.7012446898909319</v>
       </c>
       <c r="H44" s="1">
-        <v>0.06027037277817726</v>
+        <v>0.060270372778177261</v>
       </c>
       <c r="I44" s="1">
         <v>1.060270363576397</v>
       </c>
       <c r="J44" s="1">
-        <v>2.547694232232773</v>
+        <v>2.5476942322327729</v>
       </c>
       <c r="K44" s="1"/>
     </row>
@@ -2408,7 +2408,7 @@
         <v>0</v>
       </c>
       <c r="C45" s="1">
-        <v>0.2935726046562195</v>
+        <v>0.29357260465621948</v>
       </c>
       <c r="D45" s="1">
         <v>0</v>
@@ -2417,16 +2417,16 @@
         <v>0</v>
       </c>
       <c r="F45" s="1">
-        <v>0.6950432062149048</v>
+        <v>0.69504320621490479</v>
       </c>
       <c r="G45" s="1">
-        <v>0.9886157880724118</v>
+        <v>0.98861578807241179</v>
       </c>
       <c r="H45" s="1">
-        <v>-0.3820429742336273</v>
+        <v>-0.38204297423362732</v>
       </c>
       <c r="I45" s="1">
-        <v>0.6179570098248041</v>
+        <v>0.61795700982480406</v>
       </c>
       <c r="J45" s="1">
         <v>1.599813210878039</v>
@@ -2441,7 +2441,7 @@
         <v>0</v>
       </c>
       <c r="C46" s="1">
-        <v>0.8383109569549561</v>
+        <v>0.83831095695495605</v>
       </c>
       <c r="D46" s="1">
         <v>0</v>
@@ -2450,19 +2450,19 @@
         <v>0</v>
       </c>
       <c r="F46" s="1">
-        <v>-0.3666718900203705</v>
+        <v>-0.36667189002037048</v>
       </c>
       <c r="G46" s="1">
-        <v>0.471639064783882</v>
+        <v>0.47163906478388201</v>
       </c>
       <c r="H46" s="1">
-        <v>0.04581268504261971</v>
+        <v>0.045812685042619705</v>
       </c>
       <c r="I46" s="1">
         <v>1.045812722613241</v>
       </c>
       <c r="J46" s="1">
-        <v>0.4509785113393596</v>
+        <v>0.45097851133935962</v>
       </c>
       <c r="K46" s="1"/>
     </row>
@@ -2471,7 +2471,7 @@
         <v>60</v>
       </c>
       <c r="B47" s="1">
-        <v>0.506913423538208</v>
+        <v>0.50691342353820801</v>
       </c>
       <c r="C47" s="1">
         <v>4.350517749786377</v>
@@ -2483,22 +2483,22 @@
         <v>0</v>
       </c>
       <c r="F47" s="1">
-        <v>-0.6589197516441345</v>
+        <v>-0.65891975164413452</v>
       </c>
       <c r="G47" s="1">
-        <v>4.198511430508539</v>
+        <v>4.1985114305085389</v>
       </c>
       <c r="H47" s="1">
-        <v>2.166738033294678</v>
+        <v>2.1667380332946777</v>
       </c>
       <c r="I47" s="1">
         <v>3.166738061842937</v>
       </c>
       <c r="J47" s="1">
-        <v>1.325815796852112</v>
+        <v>1.3258157968521118</v>
       </c>
       <c r="K47" s="1">
-        <v>1.000000006382484</v>
+        <v>1.0000000063824837</v>
       </c>
     </row>
     <row r="48">
@@ -2509,7 +2509,7 @@
         <v>0</v>
       </c>
       <c r="C48" s="1">
-        <v>8.049905776977539</v>
+        <v>8.0499057769775391</v>
       </c>
       <c r="D48" s="1">
         <v>0</v>
@@ -2518,19 +2518,19 @@
         <v>0</v>
       </c>
       <c r="F48" s="1">
-        <v>-0.5424073934555054</v>
+        <v>-0.54240739345550537</v>
       </c>
       <c r="G48" s="1">
-        <v>7.507498387794421</v>
+        <v>7.5074983877944215</v>
       </c>
       <c r="H48" s="1">
-        <v>2.546548128128052</v>
+        <v>2.5465481281280518</v>
       </c>
       <c r="I48" s="1">
-        <v>3.546548036860977</v>
+        <v>3.5465480368609774</v>
       </c>
       <c r="J48" s="1">
-        <v>2.116846666044104</v>
+        <v>2.1168466660441041</v>
       </c>
       <c r="K48" s="1"/>
     </row>
@@ -2539,10 +2539,10 @@
         <v>61</v>
       </c>
       <c r="B49" s="1">
-        <v>1.144508004188538</v>
+        <v>1.1445080041885376</v>
       </c>
       <c r="C49" s="1">
-        <v>13.5240421295166</v>
+        <v>13.524042129516602</v>
       </c>
       <c r="D49" s="1">
         <v>0</v>
@@ -2551,19 +2551,19 @@
         <v>0</v>
       </c>
       <c r="F49" s="1">
-        <v>-1.844353318214417</v>
+        <v>-1.8443533182144165</v>
       </c>
       <c r="G49" s="1">
-        <v>12.82419704069816</v>
+        <v>12.824197040698165</v>
       </c>
       <c r="H49" s="1">
-        <v>6.090936660766602</v>
+        <v>6.0909366607666016</v>
       </c>
       <c r="I49" s="1">
-        <v>7.090936923171228</v>
+        <v>7.0909369231712276</v>
       </c>
       <c r="J49" s="1">
-        <v>1.808533509696331</v>
+        <v>1.8085335096963311</v>
       </c>
       <c r="K49" s="1"/>
     </row>
@@ -2572,10 +2572,10 @@
         <v>63</v>
       </c>
       <c r="B50" s="1">
-        <v>0.4157894849777222</v>
+        <v>0.41578948497772217</v>
       </c>
       <c r="C50" s="1">
-        <v>1.43865430355072</v>
+        <v>1.4386543035507202</v>
       </c>
       <c r="D50" s="1">
         <v>0</v>
@@ -2584,16 +2584,16 @@
         <v>0</v>
       </c>
       <c r="F50" s="1">
-        <v>-0.6292582750320435</v>
+        <v>-0.62925827503204346</v>
       </c>
       <c r="G50" s="1">
-        <v>1.225185539954689</v>
+        <v>1.2251855399546887</v>
       </c>
       <c r="H50" s="1">
-        <v>0.0748746395111084</v>
+        <v>0.074874639511108399</v>
       </c>
       <c r="I50" s="1">
-        <v>1.07487465724413</v>
+        <v>1.0748746572441301</v>
       </c>
       <c r="J50" s="1">
         <v>1.139840382036674</v>
@@ -2605,7 +2605,7 @@
         <v>64</v>
       </c>
       <c r="B51" s="1">
-        <v>0.7386043667793274</v>
+        <v>0.73860436677932739</v>
       </c>
       <c r="C51" s="1">
         <v>0.4515421986579895</v>
@@ -2617,16 +2617,16 @@
         <v>0</v>
       </c>
       <c r="F51" s="1">
-        <v>-0.1046994775533676</v>
+        <v>-0.10469947755336761</v>
       </c>
       <c r="G51" s="1">
-        <v>1.085447071658225</v>
+        <v>1.0854470716582245</v>
       </c>
       <c r="H51" s="1">
-        <v>0.01498029008507729</v>
+        <v>0.014980290085077286</v>
       </c>
       <c r="I51" s="1">
-        <v>1.014980284914072</v>
+        <v>1.0149802849140723</v>
       </c>
       <c r="J51" s="1">
         <v>1.06942675418579</v>
@@ -2638,10 +2638,10 @@
         <v>65</v>
       </c>
       <c r="B52" s="1">
-        <v>0.7425785660743713</v>
+        <v>0.74257856607437134</v>
       </c>
       <c r="C52" s="1">
-        <v>0.4361614584922791</v>
+        <v>0.43616145849227905</v>
       </c>
       <c r="D52" s="1">
         <v>0</v>
@@ -2650,16 +2650,16 @@
         <v>0</v>
       </c>
       <c r="F52" s="1">
-        <v>-0.1012194156646729</v>
+        <v>-0.10121941566467285</v>
       </c>
       <c r="G52" s="1">
-        <v>1.077520613481931</v>
+        <v>1.0775206134819309</v>
       </c>
       <c r="H52" s="1">
-        <v>0.01416928321123123</v>
+        <v>0.014169283211231232</v>
       </c>
       <c r="I52" s="1">
-        <v>1.014169288989975</v>
+        <v>1.0141692889899752</v>
       </c>
       <c r="J52" s="1">
         <v>1.062466222532777</v>
@@ -2674,7 +2674,7 @@
         <v>0</v>
       </c>
       <c r="C53" s="1">
-        <v>2.202800512313843</v>
+        <v>2.2028005123138428</v>
       </c>
       <c r="D53" s="1">
         <v>0</v>
@@ -2683,16 +2683,16 @@
         <v>0</v>
       </c>
       <c r="F53" s="1">
-        <v>-0.7315806150436401</v>
+        <v>-0.73158061504364014</v>
       </c>
       <c r="G53" s="1">
-        <v>1.471219929463804</v>
+        <v>1.4712199294638038</v>
       </c>
       <c r="H53" s="1">
-        <v>4.258919239044189</v>
+        <v>4.2589192390441895</v>
       </c>
       <c r="I53" s="1">
-        <v>5.258919179877241</v>
+        <v>5.2589191798772408</v>
       </c>
       <c r="J53" s="1">
         <v>0.2797570906001538</v>
@@ -2707,28 +2707,28 @@
         <v>1</v>
       </c>
       <c r="C54" s="1">
-        <v>-0.4325175881385803</v>
+        <v>-0.43251758813858032</v>
       </c>
       <c r="D54" s="1">
-        <v>-0.0002450549711768</v>
+        <v>-0.00024505497117680003</v>
       </c>
       <c r="E54" s="1">
-        <v>-0.0019315717316659</v>
+        <v>-0.0019315717316659004</v>
       </c>
       <c r="F54" s="1">
-        <v>0.05981426686048508</v>
+        <v>0.059814266860485077</v>
       </c>
       <c r="G54" s="1">
         <v>0.625120042656791</v>
       </c>
       <c r="H54" s="1">
-        <v>-0.06905633211135864</v>
+        <v>-0.069056332111358643</v>
       </c>
       <c r="I54" s="1">
-        <v>0.9309436687591716</v>
+        <v>0.93094366875917156</v>
       </c>
       <c r="J54" s="1">
-        <v>0.6714907288551331</v>
+        <v>0.67149072885513306</v>
       </c>
       <c r="K54" s="1">
         <v>1</v>
@@ -2742,28 +2742,28 @@
         <v>1</v>
       </c>
       <c r="C55" s="1">
-        <v>-0.7075715065002441</v>
+        <v>-0.70757150650024414</v>
       </c>
       <c r="D55" s="1">
-        <v>-0.0002450549711768</v>
+        <v>-0.00024505497117679998</v>
       </c>
       <c r="E55" s="1">
-        <v>-0.0019315717316659</v>
+        <v>-0.0019315717316658999</v>
       </c>
       <c r="F55" s="1">
-        <v>0.09782049804925919</v>
+        <v>0.097820498049259186</v>
       </c>
       <c r="G55" s="1">
-        <v>0.3880723769799164</v>
+        <v>0.38807237697991642</v>
       </c>
       <c r="H55" s="1">
         <v>-0.1128244623541832</v>
       </c>
       <c r="I55" s="1">
-        <v>0.8871755369682636</v>
+        <v>0.88717553696826357</v>
       </c>
       <c r="J55" s="1">
-        <v>0.4374245691062137</v>
+        <v>0.43742456910621369</v>
       </c>
       <c r="K55" s="1"/>
     </row>
@@ -2775,28 +2775,28 @@
         <v>1</v>
       </c>
       <c r="C56" s="1">
-        <v>-0.6105616092681885</v>
+        <v>-0.61056160926818848</v>
       </c>
       <c r="D56" s="1">
-        <v>-0.0002450549711768</v>
+        <v>-0.00024505497117679998</v>
       </c>
       <c r="E56" s="1">
-        <v>-0.0019315717316659</v>
+        <v>-0.0019315717316658999</v>
       </c>
       <c r="F56" s="1">
-        <v>0.08441592007875443</v>
+        <v>0.084415920078754425</v>
       </c>
       <c r="G56" s="1">
-        <v>0.4716777118302629</v>
+        <v>0.47167771183026291</v>
       </c>
       <c r="H56" s="1">
-        <v>-0.09738770127296448</v>
+        <v>-0.097387701272964478</v>
       </c>
       <c r="I56" s="1">
-        <v>0.9026123028343361</v>
+        <v>0.90261230283433613</v>
       </c>
       <c r="J56" s="1">
-        <v>0.5225695576596121</v>
+        <v>0.52256955765961211</v>
       </c>
       <c r="K56" s="1"/>
     </row>
@@ -2808,28 +2808,28 @@
         <v>1</v>
       </c>
       <c r="C57" s="1">
-        <v>-0.5659062266349792</v>
+        <v>-0.56590622663497925</v>
       </c>
       <c r="D57" s="1">
-        <v>-0.0002450549711768</v>
+        <v>-0.00024505497117679998</v>
       </c>
       <c r="E57" s="1">
-        <v>-0.0019315717316659</v>
+        <v>-0.0019315717316658999</v>
       </c>
       <c r="F57" s="1">
-        <v>0.07824555784463882</v>
+        <v>0.078245557844638824</v>
       </c>
       <c r="G57" s="1">
-        <v>0.5101627072375646</v>
+        <v>0.51016270723756463</v>
       </c>
       <c r="H57" s="1">
-        <v>-0.0902818888425827</v>
+        <v>-0.090281888842582703</v>
       </c>
       <c r="I57" s="1">
-        <v>0.9097181156933218</v>
+        <v>0.90971811569332184</v>
       </c>
       <c r="J57" s="1">
-        <v>0.5607920722220149</v>
+        <v>0.56079207222201488</v>
       </c>
       <c r="K57" s="1"/>
     </row>
@@ -2841,13 +2841,13 @@
         <v>1</v>
       </c>
       <c r="C58" s="1">
-        <v>-0.5458883047103882</v>
+        <v>-0.54588830471038818</v>
       </c>
       <c r="D58" s="1">
-        <v>-0.0002450549711768</v>
+        <v>-0.00024505497117679998</v>
       </c>
       <c r="E58" s="1">
-        <v>-0.0019315717316659</v>
+        <v>-0.0019315717316658999</v>
       </c>
       <c r="F58" s="1">
         <v>0.07547953724861145</v>
@@ -2856,13 +2856,13 @@
         <v>0.5274146017304937</v>
       </c>
       <c r="H58" s="1">
-        <v>-0.08709651976823807</v>
+        <v>-0.087096519768238068</v>
       </c>
       <c r="I58" s="1">
         <v>0.9129034800783844</v>
       </c>
       <c r="J58" s="1">
-        <v>0.5777331483994436</v>
+        <v>0.57773314839944356</v>
       </c>
       <c r="K58" s="1"/>
     </row>
@@ -2874,25 +2874,25 @@
         <v>1</v>
       </c>
       <c r="C59" s="1">
-        <v>-0.513551652431488</v>
+        <v>-0.51355165243148804</v>
       </c>
       <c r="D59" s="1">
-        <v>-0.0002450549711768</v>
+        <v>-0.00024505497117679998</v>
       </c>
       <c r="E59" s="1">
-        <v>-0.0019315717316659</v>
+        <v>-0.0019315717316658999</v>
       </c>
       <c r="F59" s="1">
-        <v>0.07101134210824966</v>
+        <v>0.071011342108249664</v>
       </c>
       <c r="G59" s="1">
         <v>0.5552830466806089</v>
       </c>
       <c r="H59" s="1">
-        <v>-0.08195093274116516</v>
+        <v>-0.081950932741165161</v>
       </c>
       <c r="I59" s="1">
-        <v>0.9180490687004085</v>
+        <v>0.91804906870040848</v>
       </c>
       <c r="J59" s="1">
         <v>0.6048511627670059</v>
@@ -2907,28 +2907,28 @@
         <v>1</v>
       </c>
       <c r="C60" s="1">
-        <v>-0.4966134428977966</v>
+        <v>-0.49661344289779663</v>
       </c>
       <c r="D60" s="1">
-        <v>-0.0002450549711768</v>
+        <v>-0.00024505497117679998</v>
       </c>
       <c r="E60" s="1">
-        <v>-0.0019315717316659</v>
+        <v>-0.0019315717316658999</v>
       </c>
       <c r="F60" s="1">
-        <v>0.06867086142301559</v>
+        <v>0.068670861423015594</v>
       </c>
       <c r="G60" s="1">
-        <v>0.569880803559241</v>
+        <v>0.56988080355924098</v>
       </c>
       <c r="H60" s="1">
-        <v>-0.07925562560558319</v>
+        <v>-0.079255625605583191</v>
       </c>
       <c r="I60" s="1">
         <v>0.9207443770262308</v>
       </c>
       <c r="J60" s="1">
-        <v>0.6189348724559257</v>
+        <v>0.61893487245592571</v>
       </c>
       <c r="K60" s="1"/>
     </row>
@@ -2940,25 +2940,25 @@
         <v>1</v>
       </c>
       <c r="C61" s="1">
-        <v>-0.4534979164600372</v>
+        <v>-0.45349791646003723</v>
       </c>
       <c r="D61" s="1">
-        <v>-0.0002450549711768</v>
+        <v>-0.00024505497117679998</v>
       </c>
       <c r="E61" s="1">
-        <v>-0.0019315717316659</v>
+        <v>-0.0019315717316658999</v>
       </c>
       <c r="F61" s="1">
-        <v>0.06271327286958694</v>
+        <v>0.062713272869586945</v>
       </c>
       <c r="G61" s="1">
-        <v>0.607038730159395</v>
+        <v>0.60703873015939502</v>
       </c>
       <c r="H61" s="1">
         <v>-0.07239484041929245</v>
       </c>
       <c r="I61" s="1">
-        <v>0.9276051618555964</v>
+        <v>0.92760516185559638</v>
       </c>
       <c r="J61" s="1">
         <v>0.6544149980203483</v>
@@ -2976,25 +2976,25 @@
         <v>-0.4304003119468689</v>
       </c>
       <c r="D62" s="1">
-        <v>-0.0002450549711768</v>
+        <v>-0.00024505497117679998</v>
       </c>
       <c r="E62" s="1">
-        <v>-0.0019315717316659</v>
+        <v>-0.0019315717316658999</v>
       </c>
       <c r="F62" s="1">
-        <v>0.05952170863747597</v>
+        <v>0.059521708637475968</v>
       </c>
       <c r="G62" s="1">
-        <v>0.6269447622666199</v>
+        <v>0.62694476226661988</v>
       </c>
       <c r="H62" s="1">
-        <v>-0.06871941685676575</v>
+        <v>-0.068719416856765747</v>
       </c>
       <c r="I62" s="1">
         <v>0.9312805822998993</v>
       </c>
       <c r="J62" s="1">
-        <v>0.6732071667577468</v>
+        <v>0.67320716675774683</v>
       </c>
       <c r="K62" s="1"/>
     </row>
@@ -3006,28 +3006,28 @@
         <v>1</v>
       </c>
       <c r="C63" s="1">
-        <v>-0.3041334450244904</v>
+        <v>-0.30413344502449036</v>
       </c>
       <c r="D63" s="1">
-        <v>-0.0002450549711768</v>
+        <v>-0.00024505497117679998</v>
       </c>
       <c r="E63" s="1">
-        <v>-0.0019315717316659</v>
+        <v>-0.0019315717316658999</v>
       </c>
       <c r="F63" s="1">
-        <v>0.04207447916269302</v>
+        <v>0.042074479162693024</v>
       </c>
       <c r="G63" s="1">
-        <v>0.7357644044527852</v>
+        <v>0.73576440445278524</v>
       </c>
       <c r="H63" s="1">
-        <v>-0.04862711578607559</v>
+        <v>-0.048627115786075592</v>
       </c>
       <c r="I63" s="1">
-        <v>0.9513728807287556</v>
+        <v>0.95137288072875559</v>
       </c>
       <c r="J63" s="1">
-        <v>0.7733712189580038</v>
+        <v>0.77337121895800376</v>
       </c>
       <c r="K63" s="1"/>
     </row>
@@ -3039,28 +3039,28 @@
         <v>1</v>
       </c>
       <c r="C64" s="1">
-        <v>-0.2517789006233215</v>
+        <v>-0.25177890062332153</v>
       </c>
       <c r="D64" s="1">
-        <v>-0.0002450549711768</v>
+        <v>-0.00024505497117679998</v>
       </c>
       <c r="E64" s="1">
-        <v>-0.0019315717316659</v>
+        <v>-0.0019315717316658999</v>
       </c>
       <c r="F64" s="1">
-        <v>0.03484026342630386</v>
+        <v>0.034840263426303864</v>
       </c>
       <c r="G64" s="1">
-        <v>0.7808847438958292</v>
+        <v>0.78088474389582918</v>
       </c>
       <c r="H64" s="1">
-        <v>-0.04029616340994835</v>
+        <v>-0.040296163409948349</v>
       </c>
       <c r="I64" s="1">
-        <v>0.9597038337358421</v>
+        <v>0.95970383373584212</v>
       </c>
       <c r="J64" s="1">
-        <v>0.8136726315410002</v>
+        <v>0.81367263154100022</v>
       </c>
       <c r="K64" s="1"/>
     </row>
@@ -3072,28 +3072,28 @@
         <v>1</v>
       </c>
       <c r="C65" s="1">
-        <v>-0.2463894486427307</v>
+        <v>-0.24638944864273071</v>
       </c>
       <c r="D65" s="1">
-        <v>-0.0002450549711768</v>
+        <v>-0.00024505497117679998</v>
       </c>
       <c r="E65" s="1">
-        <v>-0.0019315717316659</v>
+        <v>-0.0019315717316658999</v>
       </c>
       <c r="F65" s="1">
-        <v>0.03409556671977043</v>
+        <v>0.034095566719770432</v>
       </c>
       <c r="G65" s="1">
-        <v>0.7855294847208482</v>
+        <v>0.78552948472084816</v>
       </c>
       <c r="H65" s="1">
         <v>-0.03943856805562973</v>
       </c>
       <c r="I65" s="1">
-        <v>0.9605614318395128</v>
+        <v>0.96056143183951281</v>
       </c>
       <c r="J65" s="1">
-        <v>0.8177816209178088</v>
+        <v>0.81778162091780882</v>
       </c>
       <c r="K65" s="1"/>
     </row>
@@ -3105,28 +3105,28 @@
         <v>1</v>
       </c>
       <c r="C66" s="1">
-        <v>-0.06391843408346176</v>
+        <v>-0.063918434083461761</v>
       </c>
       <c r="D66" s="1">
-        <v>-0.0002450549711768</v>
+        <v>-0.00024505497117679998</v>
       </c>
       <c r="E66" s="1">
-        <v>-0.0019315717316659</v>
+        <v>-0.0019315717316658999</v>
       </c>
       <c r="F66" s="1">
-        <v>0.008882196620106697</v>
+        <v>0.0088821966201066971</v>
       </c>
       <c r="G66" s="1">
-        <v>0.9427871383679283</v>
+        <v>0.94278713836792827</v>
       </c>
       <c r="H66" s="1">
-        <v>-0.01040274649858475</v>
+        <v>-0.010402746498584747</v>
       </c>
       <c r="I66" s="1">
-        <v>0.9895972533495064</v>
+        <v>0.98959725334950643</v>
       </c>
       <c r="J66" s="1">
-        <v>0.9526978123442247</v>
+        <v>0.95269781234422468</v>
       </c>
       <c r="K66" s="1"/>
     </row>
@@ -3138,7 +3138,7 @@
         <v>1</v>
       </c>
       <c r="C67" s="1">
-        <v>-0.2506857216358185</v>
+        <v>-0.25068572163581848</v>
       </c>
       <c r="D67" s="1">
         <v>0</v>
@@ -3147,19 +3147,19 @@
         <v>0</v>
       </c>
       <c r="F67" s="1">
-        <v>0.02527328953146935</v>
+        <v>0.025273289531469345</v>
       </c>
       <c r="G67" s="1">
-        <v>0.774587566015807</v>
+        <v>0.77458756601580703</v>
       </c>
       <c r="H67" s="1">
-        <v>-0.02975428849458694</v>
+        <v>-0.029754288494586945</v>
       </c>
       <c r="I67" s="1">
-        <v>0.9702457112673686</v>
+        <v>0.97024571126736858</v>
       </c>
       <c r="J67" s="1">
-        <v>0.7983416318893433</v>
+        <v>0.79834163188934326</v>
       </c>
       <c r="K67" s="1">
         <v>1</v>
@@ -3173,7 +3173,7 @@
         <v>1</v>
       </c>
       <c r="C68" s="1">
-        <v>-0.3131513893604279</v>
+        <v>-0.31315138936042786</v>
       </c>
       <c r="D68" s="1">
         <v>0</v>
@@ -3182,19 +3182,19 @@
         <v>0</v>
       </c>
       <c r="F68" s="1">
-        <v>0.0355539508163929</v>
+        <v>0.035553950816392899</v>
       </c>
       <c r="G68" s="1">
-        <v>0.7224025594156133</v>
+        <v>0.72240255941561327</v>
       </c>
       <c r="H68" s="1">
-        <v>-0.04185454919934273</v>
+        <v>-0.041854549199342728</v>
       </c>
       <c r="I68" s="1">
-        <v>0.9581454517533063</v>
+        <v>0.95814545175330634</v>
       </c>
       <c r="J68" s="1">
-        <v>0.7539591803036708</v>
+        <v>0.75395918030367082</v>
       </c>
       <c r="K68" s="1"/>
     </row>
@@ -3206,7 +3206,7 @@
         <v>1</v>
       </c>
       <c r="C69" s="1">
-        <v>-0.1882200539112091</v>
+        <v>-0.18822005391120911</v>
       </c>
       <c r="D69" s="1">
         <v>0</v>
@@ -3215,19 +3215,19 @@
         <v>0</v>
       </c>
       <c r="F69" s="1">
-        <v>0.01499263010919094</v>
+        <v>0.014992630109190941</v>
       </c>
       <c r="G69" s="1">
-        <v>0.8267725726160008</v>
+        <v>0.82677257261600079</v>
       </c>
       <c r="H69" s="1">
-        <v>-0.01765402965247631</v>
+        <v>-0.017654029652476311</v>
       </c>
       <c r="I69" s="1">
-        <v>0.9823459707814309</v>
+        <v>0.98234597078143093</v>
       </c>
       <c r="J69" s="1">
-        <v>0.8416307464042678</v>
+        <v>0.84163074640426783</v>
       </c>
       <c r="K69" s="1"/>
     </row>
@@ -3236,10 +3236,10 @@
         <v>83</v>
       </c>
       <c r="B70" s="1">
-        <v>0.9785932898521423</v>
+        <v>0.97859328985214233</v>
       </c>
       <c r="C70" s="1">
-        <v>-0.1514832973480225</v>
+        <v>-0.15148329734802246</v>
       </c>
       <c r="D70" s="1">
         <v>0</v>
@@ -3248,22 +3248,22 @@
         <v>0</v>
       </c>
       <c r="F70" s="1">
-        <v>-0.1082840114831924</v>
+        <v>-0.10828401148319244</v>
       </c>
       <c r="G70" s="1">
-        <v>0.7188259811247045</v>
+        <v>0.71882598112470453</v>
       </c>
       <c r="H70" s="1">
-        <v>0.1117310374975204</v>
+        <v>0.11173103749752045</v>
       </c>
       <c r="I70" s="1">
         <v>1.111731071247424</v>
       </c>
       <c r="J70" s="1">
-        <v>0.6465826034545898</v>
+        <v>0.64658260345458984</v>
       </c>
       <c r="K70" s="1">
-        <v>1.00000002985398</v>
+        <v>1.0000000298539797</v>
       </c>
     </row>
     <row r="71">
@@ -3274,7 +3274,7 @@
         <v>1</v>
       </c>
       <c r="C71" s="1">
-        <v>-0.136486291885376</v>
+        <v>-0.13648629188537598</v>
       </c>
       <c r="D71" s="1">
         <v>0</v>
@@ -3283,19 +3283,19 @@
         <v>0</v>
       </c>
       <c r="F71" s="1">
-        <v>-0.3231302201747894</v>
+        <v>-0.32313022017478943</v>
       </c>
       <c r="G71" s="1">
-        <v>0.5403835085537427</v>
+        <v>0.54038350855374273</v>
       </c>
       <c r="H71" s="1">
-        <v>0.1776143759489059</v>
+        <v>0.17761437594890595</v>
       </c>
       <c r="I71" s="1">
-        <v>1.177614399221243</v>
+        <v>1.1776143992212429</v>
       </c>
       <c r="J71" s="1">
-        <v>0.458879841237589</v>
+        <v>0.45887984123758901</v>
       </c>
       <c r="K71" s="1"/>
     </row>
@@ -3307,7 +3307,7 @@
         <v>0.935779869556427</v>
       </c>
       <c r="C72" s="1">
-        <v>-0.267766535282135</v>
+        <v>-0.26776653528213501</v>
       </c>
       <c r="D72" s="1">
         <v>0</v>
@@ -3316,19 +3316,19 @@
         <v>0</v>
       </c>
       <c r="F72" s="1">
-        <v>0.1171193867921829</v>
+        <v>0.11711938679218292</v>
       </c>
       <c r="G72" s="1">
         <v>0.785132704777319</v>
       </c>
       <c r="H72" s="1">
-        <v>0.09225552529096603</v>
+        <v>0.092255525290966034</v>
       </c>
       <c r="I72" s="1">
-        <v>1.092255571496919</v>
+        <v>1.0922555714969193</v>
       </c>
       <c r="J72" s="1">
-        <v>0.7188177613974602</v>
+        <v>0.71881776139746023</v>
       </c>
       <c r="K72" s="1"/>
     </row>
@@ -3340,7 +3340,7 @@
         <v>1</v>
       </c>
       <c r="C73" s="1">
-        <v>-0.05019708350300789</v>
+        <v>-0.050197083503007889</v>
       </c>
       <c r="D73" s="1">
         <v>0</v>
@@ -3349,19 +3349,19 @@
         <v>0</v>
       </c>
       <c r="F73" s="1">
-        <v>-0.1188412085175514</v>
+        <v>-0.11884120851755142</v>
       </c>
       <c r="G73" s="1">
-        <v>0.8309617300430521</v>
+        <v>0.83096173004305207</v>
       </c>
       <c r="H73" s="1">
-        <v>0.06532321870326996</v>
+        <v>0.065323218703269959</v>
       </c>
       <c r="I73" s="1">
-        <v>1.06532324302411</v>
+        <v>1.0653232430241102</v>
       </c>
       <c r="J73" s="1">
-        <v>0.7800090118039844</v>
+        <v>0.78000901180398441</v>
       </c>
       <c r="K73" s="1"/>
     </row>
@@ -3373,7 +3373,7 @@
         <v>1</v>
       </c>
       <c r="C74" s="1">
-        <v>-0.8543289303779602</v>
+        <v>-0.85432893037796021</v>
       </c>
       <c r="D74" s="1">
         <v>0</v>
@@ -3385,19 +3385,19 @@
         <v>0</v>
       </c>
       <c r="G74" s="1">
-        <v>0.1456710892723972</v>
+        <v>0.14567108927239725</v>
       </c>
       <c r="H74" s="1">
-        <v>-0.02082010172307491</v>
+        <v>-0.020820101723074913</v>
       </c>
       <c r="I74" s="1">
-        <v>0.9791798960568693</v>
+        <v>0.97917989605686928</v>
       </c>
       <c r="J74" s="1">
-        <v>0.1487684696912766</v>
+        <v>0.14876846969127655</v>
       </c>
       <c r="K74" s="1">
-        <v>0.9999999979564791</v>
+        <v>0.99999999795647909</v>
       </c>
     </row>
     <row r="75">
@@ -3408,7 +3408,7 @@
         <v>1</v>
       </c>
       <c r="C75" s="1">
-        <v>-1.646022081375122</v>
+        <v>-1.6460220813751221</v>
       </c>
       <c r="D75" s="1">
         <v>0</v>
@@ -3423,10 +3423,10 @@
         <v>-0.6460220366516285</v>
       </c>
       <c r="H75" s="1">
-        <v>-0.03731274604797363</v>
+        <v>-0.037312746047973633</v>
       </c>
       <c r="I75" s="1">
-        <v>0.9626872703373329</v>
+        <v>0.96268727033733292</v>
       </c>
       <c r="J75" s="1">
         <v>-0.6710611603135227</v>
@@ -3441,7 +3441,7 @@
         <v>1</v>
       </c>
       <c r="C76" s="1">
-        <v>-0.06263576447963715</v>
+        <v>-0.062635764479637146</v>
       </c>
       <c r="D76" s="1">
         <v>0</v>
@@ -3453,16 +3453,16 @@
         <v>0</v>
       </c>
       <c r="G76" s="1">
-        <v>0.937364215196423</v>
+        <v>0.93736421519642299</v>
       </c>
       <c r="H76" s="1">
-        <v>-0.004327456932514906</v>
+        <v>-0.0043274569325149059</v>
       </c>
       <c r="I76" s="1">
-        <v>0.9956725217764056</v>
+        <v>0.99567252177640564</v>
       </c>
       <c r="J76" s="1">
-        <v>0.9414382688035287</v>
+        <v>0.94143826880352866</v>
       </c>
       <c r="K76" s="1"/>
     </row>
@@ -3474,7 +3474,7 @@
         <v>4.100581169128418</v>
       </c>
       <c r="C77" s="1">
-        <v>20.10259056091309</v>
+        <v>20.102590560913086</v>
       </c>
       <c r="D77" s="1">
         <v>0</v>
@@ -3486,19 +3486,19 @@
         <v>0</v>
       </c>
       <c r="G77" s="1">
-        <v>24.20317249354918</v>
+        <v>24.203172493549179</v>
       </c>
       <c r="H77" s="1">
-        <v>-0.3925851285457611</v>
+        <v>-0.39258512854576111</v>
       </c>
       <c r="I77" s="1">
-        <v>0.6074148882122614</v>
+        <v>0.60741488821226142</v>
       </c>
       <c r="J77" s="1">
-        <v>39.84619522094727</v>
+        <v>39.846195220947266</v>
       </c>
       <c r="K77" s="1">
-        <v>0.9999999934159318</v>
+        <v>0.99999999341593182</v>
       </c>
     </row>
     <row r="78">
@@ -3506,10 +3506,10 @@
         <v>91</v>
       </c>
       <c r="B78" s="1">
-        <v>7.655874252319336</v>
+        <v>7.6558742523193359</v>
       </c>
       <c r="C78" s="1">
-        <v>43.16090774536133</v>
+        <v>43.160907745361328</v>
       </c>
       <c r="D78" s="1">
         <v>0</v>
@@ -3521,16 +3521,16 @@
         <v>0</v>
       </c>
       <c r="G78" s="1">
-        <v>50.81678195422072</v>
+        <v>50.816781954220716</v>
       </c>
       <c r="H78" s="1">
-        <v>-0.8428928256034851</v>
+        <v>-0.84289282560348511</v>
       </c>
       <c r="I78" s="1">
-        <v>0.157107188576442</v>
+        <v>0.15710718857644204</v>
       </c>
       <c r="J78" s="1">
-        <v>323.4529394528329</v>
+        <v>323.45293945283288</v>
       </c>
       <c r="K78" s="1"/>
     </row>
@@ -3539,10 +3539,10 @@
         <v>92</v>
       </c>
       <c r="B79" s="1">
-        <v>0.5452880263328552</v>
+        <v>0.54528802633285523</v>
       </c>
       <c r="C79" s="1">
-        <v>-2.955724954605103</v>
+        <v>-2.9557249546051025</v>
       </c>
       <c r="D79" s="1">
         <v>0</v>
@@ -3554,16 +3554,16 @@
         <v>0</v>
       </c>
       <c r="G79" s="1">
-        <v>-2.410436967122359</v>
+        <v>-2.4104369671223593</v>
       </c>
       <c r="H79" s="1">
-        <v>0.05772258713841438</v>
+        <v>0.057722587138414383</v>
       </c>
       <c r="I79" s="1">
-        <v>1.057722587848081</v>
+        <v>1.0577225878480807</v>
       </c>
       <c r="J79" s="1">
-        <v>-2.278893345774485</v>
+        <v>-2.2788933457744851</v>
       </c>
       <c r="K79" s="1"/>
     </row>
@@ -3572,10 +3572,10 @@
         <v>93</v>
       </c>
       <c r="B80" s="1">
-        <v>0.4618790149688721</v>
+        <v>0.46187901496887207</v>
       </c>
       <c r="C80" s="1">
-        <v>14.44321823120117</v>
+        <v>14.443218231201172</v>
       </c>
       <c r="D80" s="1">
         <v>0</v>
@@ -3587,19 +3587,19 @@
         <v>0</v>
       </c>
       <c r="G80" s="1">
-        <v>14.90509715708152</v>
+        <v>14.905097157081519</v>
       </c>
       <c r="H80" s="1">
-        <v>-0.2820627391338348</v>
+        <v>-0.28206273913383484</v>
       </c>
       <c r="I80" s="1">
-        <v>0.7179372442644593</v>
+        <v>0.71793724426445926</v>
       </c>
       <c r="J80" s="1">
-        <v>20.7610034942627</v>
+        <v>20.761003494262695</v>
       </c>
       <c r="K80" s="1">
-        <v>0.9999999997025668</v>
+        <v>0.99999999970256681</v>
       </c>
     </row>
     <row r="81">
@@ -3610,7 +3610,7 @@
         <v>0</v>
       </c>
       <c r="C81" s="1">
-        <v>35.84024047851563</v>
+        <v>35.840240478515625</v>
       </c>
       <c r="D81" s="1">
         <v>0</v>
@@ -3622,16 +3622,16 @@
         <v>0</v>
       </c>
       <c r="G81" s="1">
-        <v>35.84023896823916</v>
+        <v>35.840238968239156</v>
       </c>
       <c r="H81" s="1">
-        <v>-0.6999268531799316</v>
+        <v>-0.69992685317993164</v>
       </c>
       <c r="I81" s="1">
-        <v>0.3000731286936802</v>
+        <v>0.30007312869368025</v>
       </c>
       <c r="J81" s="1">
-        <v>119.4383486594212</v>
+        <v>119.43834865942119</v>
       </c>
       <c r="K81" s="1"/>
     </row>
@@ -3640,10 +3640,10 @@
         <v>95</v>
       </c>
       <c r="B82" s="1">
-        <v>0.4206370413303375</v>
+        <v>0.42063704133033753</v>
       </c>
       <c r="C82" s="1">
-        <v>4.537993907928467</v>
+        <v>4.5379939079284668</v>
       </c>
       <c r="D82" s="1">
         <v>0</v>
@@ -3655,16 +3655,16 @@
         <v>0</v>
       </c>
       <c r="G82" s="1">
-        <v>4.958631025988771</v>
+        <v>4.9586310259887707</v>
       </c>
       <c r="H82" s="1">
-        <v>-0.08862284570932388</v>
+        <v>-0.088622845709323883</v>
       </c>
       <c r="I82" s="1">
-        <v>0.911377118023783</v>
+        <v>0.91137711802378296</v>
       </c>
       <c r="J82" s="1">
-        <v>5.440811413765791</v>
+        <v>5.4408114137657906</v>
       </c>
       <c r="K82" s="1"/>
     </row>
@@ -3676,7 +3676,7 @@
         <v>0.9649999737739563</v>
       </c>
       <c r="C83" s="1">
-        <v>2.951421499252319</v>
+        <v>2.9514214992523193</v>
       </c>
       <c r="D83" s="1">
         <v>0</v>
@@ -3688,16 +3688,16 @@
         <v>0</v>
       </c>
       <c r="G83" s="1">
-        <v>3.916421477016626</v>
+        <v>3.9164214770166264</v>
       </c>
       <c r="H83" s="1">
-        <v>-0.05763854458928108</v>
+        <v>-0.057638544589281082</v>
       </c>
       <c r="I83" s="1">
-        <v>0.9423614860759144</v>
+        <v>0.94236148607591441</v>
       </c>
       <c r="J83" s="1">
-        <v>4.155965131093153</v>
+        <v>4.1559651310931534</v>
       </c>
       <c r="K83" s="1"/>
     </row>
@@ -3706,10 +3706,10 @@
         <v>97</v>
       </c>
       <c r="B84" s="1">
-        <v>0.9437336325645447</v>
+        <v>0.94373363256454468</v>
       </c>
       <c r="C84" s="1">
-        <v>9.384907722473145</v>
+        <v>9.3849077224731445</v>
       </c>
       <c r="D84" s="1">
         <v>0</v>
@@ -3721,19 +3721,19 @@
         <v>0</v>
       </c>
       <c r="G84" s="1">
-        <v>10.32864112543979</v>
+        <v>10.328641125439791</v>
       </c>
       <c r="H84" s="1">
-        <v>-0.1832786053419113</v>
+        <v>-0.18327860534191132</v>
       </c>
       <c r="I84" s="1">
-        <v>0.8167214001775073</v>
+        <v>0.81672140017750727</v>
       </c>
       <c r="J84" s="1">
-        <v>12.64646816253662</v>
+        <v>12.646468162536621</v>
       </c>
       <c r="K84" s="1">
-        <v>1.000000004878025</v>
+        <v>1.0000000048780253</v>
       </c>
     </row>
     <row r="85">
@@ -3741,10 +3741,10 @@
         <v>98</v>
       </c>
       <c r="B85" s="1">
-        <v>0.9722129702568054</v>
+        <v>0.97221297025680542</v>
       </c>
       <c r="C85" s="1">
-        <v>10.64214420318604</v>
+        <v>10.642144203186035</v>
       </c>
       <c r="D85" s="1">
         <v>0</v>
@@ -3756,13 +3756,13 @@
         <v>0</v>
       </c>
       <c r="G85" s="1">
-        <v>11.61435708900713</v>
+        <v>11.614357089007134</v>
       </c>
       <c r="H85" s="1">
-        <v>-0.2078312784433365</v>
+        <v>-0.20783127844333649</v>
       </c>
       <c r="I85" s="1">
-        <v>0.7921687051968413</v>
+        <v>0.79216870519684135</v>
       </c>
       <c r="J85" s="1">
         <v>14.66146922090434</v>
@@ -3774,10 +3774,10 @@
         <v>99</v>
       </c>
       <c r="B86" s="1">
-        <v>0.9152542948722839</v>
+        <v>0.91525429487228394</v>
       </c>
       <c r="C86" s="1">
-        <v>8.127671241760254</v>
+        <v>8.1276712417602539</v>
       </c>
       <c r="D86" s="1">
         <v>0</v>
@@ -3792,7 +3792,7 @@
         <v>9.04292516187245</v>
       </c>
       <c r="H86" s="1">
-        <v>-0.1587259322404861</v>
+        <v>-0.15872593224048615</v>
       </c>
       <c r="I86" s="1">
         <v>0.8412740951581732</v>
@@ -3810,7 +3810,7 @@
         <v>1</v>
       </c>
       <c r="C87" s="1">
-        <v>7.494669914245605</v>
+        <v>7.4946699142456055</v>
       </c>
       <c r="D87" s="1">
         <v>0</v>
@@ -3822,19 +3822,19 @@
         <v>0</v>
       </c>
       <c r="G87" s="1">
-        <v>8.494670037265186</v>
+        <v>8.4946700372651858</v>
       </c>
       <c r="H87" s="1">
-        <v>0.1116973981261253</v>
+        <v>0.11169739812612534</v>
       </c>
       <c r="I87" s="1">
         <v>1.111697405491312</v>
       </c>
       <c r="J87" s="1">
-        <v>7.641170978546143</v>
+        <v>7.6411709785461426</v>
       </c>
       <c r="K87" s="1">
-        <v>0.9999999795636463</v>
+        <v>0.99999997956364628</v>
       </c>
     </row>
     <row r="88">
@@ -3845,7 +3845,7 @@
         <v>1</v>
       </c>
       <c r="C88" s="1">
-        <v>7.494669914245605</v>
+        <v>7.4946699142456055</v>
       </c>
       <c r="D88" s="1">
         <v>0</v>
@@ -3857,16 +3857,16 @@
         <v>0</v>
       </c>
       <c r="G88" s="1">
-        <v>8.494670037265186</v>
+        <v>8.4946700372651858</v>
       </c>
       <c r="H88" s="1">
-        <v>0.1116973981261253</v>
+        <v>0.11169739812612534</v>
       </c>
       <c r="I88" s="1">
         <v>1.111697405491312</v>
       </c>
       <c r="J88" s="1">
-        <v>7.641171055455496</v>
+        <v>7.6411710554554961</v>
       </c>
       <c r="K88" s="1"/>
     </row>
@@ -3875,10 +3875,10 @@
         <v>102</v>
       </c>
       <c r="B89" s="1">
-        <v>0.6666666865348816</v>
+        <v>0.66666668653488159</v>
       </c>
       <c r="C89" s="1">
-        <v>-0.01755868829786777</v>
+        <v>-0.017558688297867775</v>
       </c>
       <c r="D89" s="1">
         <v>0</v>
@@ -3890,19 +3890,19 @@
         <v>0</v>
       </c>
       <c r="G89" s="1">
-        <v>0.6491079607657513</v>
+        <v>0.64910796076575128</v>
       </c>
       <c r="H89" s="1">
-        <v>0.0003429050848353654</v>
+        <v>0.00034290508483536542</v>
       </c>
       <c r="I89" s="1">
-        <v>1.000342884571283</v>
+        <v>1.0003428845712827</v>
       </c>
       <c r="J89" s="1">
-        <v>0.6488854885101318</v>
+        <v>0.64888548851013184</v>
       </c>
       <c r="K89" s="1">
-        <v>0.9999999795201635</v>
+        <v>0.99999997952016351</v>
       </c>
     </row>
     <row r="90">
@@ -3913,7 +3913,7 @@
         <v>0.75</v>
       </c>
       <c r="C90" s="1">
-        <v>0.1003562957048416</v>
+        <v>0.10035629570484161</v>
       </c>
       <c r="D90" s="1">
         <v>0</v>
@@ -3925,16 +3925,16 @@
         <v>0</v>
       </c>
       <c r="G90" s="1">
-        <v>0.850356264448755</v>
+        <v>0.85035626444875501</v>
       </c>
       <c r="H90" s="1">
-        <v>-0.001959865912795067</v>
+        <v>-0.0019598659127950668</v>
       </c>
       <c r="I90" s="1">
-        <v>0.9980400961333243</v>
+        <v>0.99804009613332434</v>
       </c>
       <c r="J90" s="1">
-        <v>0.8520261538021006</v>
+        <v>0.85202615380210056</v>
       </c>
       <c r="K90" s="1"/>
     </row>
@@ -3946,7 +3946,7 @@
         <v>0.75</v>
       </c>
       <c r="C91" s="1">
-        <v>-0.07549013942480087</v>
+        <v>-0.075490139424800873</v>
       </c>
       <c r="D91" s="1">
         <v>0</v>
@@ -3958,16 +3958,16 @@
         <v>0</v>
       </c>
       <c r="G91" s="1">
-        <v>0.6745098344780365</v>
+        <v>0.67450983447803648</v>
       </c>
       <c r="H91" s="1">
         <v>0.001474253018386662</v>
       </c>
       <c r="I91" s="1">
-        <v>1.001474221591202</v>
+        <v>1.0014742215912018</v>
       </c>
       <c r="J91" s="1">
-        <v>0.67351692129063</v>
+        <v>0.67351692129063001</v>
       </c>
       <c r="K91" s="1"/>
     </row>
@@ -3979,7 +3979,7 @@
         <v>0.5</v>
       </c>
       <c r="C92" s="1">
-        <v>-0.07754222303628922</v>
+        <v>-0.077542223036289215</v>
       </c>
       <c r="D92" s="1">
         <v>0</v>
@@ -3994,13 +3994,13 @@
         <v>0.4224577833704623</v>
       </c>
       <c r="H92" s="1">
-        <v>0.001514328178018332</v>
+        <v>0.0015143281780183315</v>
       </c>
       <c r="I92" s="1">
-        <v>1.001514335989322</v>
+        <v>1.0015143359893219</v>
       </c>
       <c r="J92" s="1">
-        <v>0.4218190076661733</v>
+        <v>0.42181900766617331</v>
       </c>
       <c r="K92" s="1"/>
     </row>
@@ -4017,7 +4017,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5BF7382-BA68-4FFF-972D-6F46E493258F}">
   <dimension ref="E1:AL129"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="28.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultColWidth="9.109375" defaultRowHeight="28.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="4" width="9.109375" style="25"/>
     <col min="5" max="5" width="9.109375" style="25" customWidth="true"/>
@@ -4039,7 +4039,7 @@
     <col min="28" max="16384" width="9.109375" style="25"/>
   </cols>
   <sheetData>
-    <row r="1" s="2" customFormat="true" ht="19.8" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" s="2" customFormat="true" ht="19.8" x14ac:dyDescent="0.3">
       <c r="F1" s="3"/>
       <c r="K1" s="6"/>
       <c r="L1" s="6"/>
@@ -4053,7 +4053,7 @@
       <c r="T1" s="6"/>
       <c r="V1" s="3"/>
     </row>
-    <row r="2" s="2" customFormat="true" ht="19.8" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" s="2" customFormat="true" ht="19.8" x14ac:dyDescent="0.3">
       <c r="F2" s="3"/>
       <c r="K2" s="6"/>
       <c r="L2" s="6"/>
@@ -4067,7 +4067,7 @@
       <c r="T2" s="6"/>
       <c r="V2" s="3"/>
     </row>
-    <row r="3" s="2" customFormat="true" ht="19.8" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" s="2" customFormat="true" ht="19.8" x14ac:dyDescent="0.3">
       <c r="F3" s="3"/>
       <c r="K3" s="6"/>
       <c r="L3" s="6"/>
@@ -4081,7 +4081,7 @@
       <c r="T3" s="6"/>
       <c r="V3" s="3"/>
     </row>
-    <row r="4" s="2" customFormat="true" ht="19.8" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" s="2" customFormat="true" ht="19.8" x14ac:dyDescent="0.3">
       <c r="F4" s="3"/>
       <c r="K4" s="6"/>
       <c r="L4" s="6"/>
@@ -4095,7 +4095,7 @@
       <c r="T4" s="6"/>
       <c r="V4" s="3"/>
     </row>
-    <row r="5" s="2" customFormat="true" ht="19.8" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" s="2" customFormat="true" ht="19.8" x14ac:dyDescent="0.3">
       <c r="F5" s="3"/>
       <c r="K5" s="6"/>
       <c r="L5" s="6"/>
@@ -4109,7 +4109,7 @@
       <c r="T5" s="6"/>
       <c r="V5" s="3"/>
     </row>
-    <row r="6" s="2" customFormat="true" ht="20.4" thickBot="true" x14ac:dyDescent="0.35">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" s="2" customFormat="true" ht="20.4" thickBot="true" x14ac:dyDescent="0.35">
       <c r="F6" s="3"/>
       <c r="K6" s="6"/>
       <c r="L6" s="6"/>
@@ -4123,7 +4123,7 @@
       <c r="T6" s="6"/>
       <c r="V6" s="3"/>
     </row>
-    <row r="7" s="2" customFormat="true" ht="10.2" customHeight="true" thickTop="true" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" s="2" customFormat="true" ht="10.2" customHeight="true" thickTop="true" x14ac:dyDescent="0.3">
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
@@ -4142,7 +4142,7 @@
       <c r="U7" s="4"/>
       <c r="V7" s="4"/>
     </row>
-    <row r="8" s="10" customFormat="true" ht="31.8" thickBot="true" x14ac:dyDescent="0.35">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" s="10" customFormat="true" ht="31.8" thickBot="true" x14ac:dyDescent="0.35">
       <c r="J8" s="44" t="s">
         <v>12</v>
       </c>
@@ -4159,7 +4159,7 @@
       <c r="S8" s="44"/>
       <c r="T8" s="35"/>
     </row>
-    <row r="9" s="2" customFormat="true" ht="10.2" customHeight="true" thickTop="true" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" s="2" customFormat="true" ht="10.2" customHeight="true" thickTop="true" x14ac:dyDescent="0.3">
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
@@ -4178,7 +4178,7 @@
       <c r="U9" s="3"/>
       <c r="V9" s="3"/>
     </row>
-    <row r="10" s="11" customFormat="true" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" s="11" customFormat="true" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
       <c r="F10" s="8"/>
       <c r="K10" s="13"/>
       <c r="L10" s="13"/>
@@ -4194,7 +4194,7 @@
       <c r="T10" s="8"/>
       <c r="V10" s="8"/>
     </row>
-    <row r="11" s="16" customFormat="true" ht="40.05" customHeight="true" thickTop="true" thickBot="true" x14ac:dyDescent="0.75">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" s="16" customFormat="true" ht="40.05" customHeight="true" thickTop="true" thickBot="true" x14ac:dyDescent="0.75">
       <c r="E11" s="39"/>
       <c r="F11" s="40" t="s">
         <v>0</v>
@@ -4250,7 +4250,7 @@
       <c r="AK11" s="15"/>
       <c r="AL11" s="15"/>
     </row>
-    <row r="12" s="16" customFormat="true" ht="10.2" customHeight="true" thickTop="true" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" s="16" customFormat="true" ht="10.2" customHeight="true" thickTop="true" x14ac:dyDescent="0.3">
       <c r="F12" s="17"/>
       <c r="G12" s="17"/>
       <c r="H12" s="17"/>
@@ -4269,7 +4269,7 @@
       <c r="U12" s="17"/>
       <c r="V12" s="17"/>
     </row>
-    <row r="13" s="23" customFormat="true" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" s="23" customFormat="true" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
       <c r="F13" s="19"/>
       <c r="G13" s="20" t="str">
         <f>data_export!A2</f>
@@ -4318,7 +4318,7 @@
       <c r="U13" s="21"/>
       <c r="V13" s="19"/>
     </row>
-    <row r="14" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="14" x14ac:dyDescent="0.3">
       <c r="H14" s="26" t="str">
         <f>data_export!A3</f>
         <v>PTC (Shrimali)</v>
@@ -4361,7 +4361,7 @@
         <v>7.5466899999999999</v>
       </c>
     </row>
-    <row r="15" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="15" x14ac:dyDescent="0.3">
       <c r="H15" s="26" t="str">
         <f>data_export!A4</f>
         <v>PTC (Metcalf)</v>
@@ -4404,7 +4404,7 @@
         <v>5.2980609999999997</v>
       </c>
     </row>
-    <row r="16" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="16" x14ac:dyDescent="0.3">
       <c r="H16" s="26" t="str">
         <f>data_export!A5</f>
         <v>PTC (Hitaj)</v>
@@ -4447,8 +4447,8 @@
         <v>4.6260130000000004</v>
       </c>
     </row>
-    <row r="17" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
-    <row r="18" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="17" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="18" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
       <c r="G18" s="20"/>
       <c r="H18" s="20" t="str">
         <f>data_export!A6</f>
@@ -4495,7 +4495,7 @@
       </c>
       <c r="U18" s="21"/>
     </row>
-    <row r="19" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="19" x14ac:dyDescent="0.3">
       <c r="H19" s="26" t="str">
         <f>data_export!A7</f>
         <v>CSI</v>
@@ -4538,7 +4538,7 @@
         <v>5.0632710000000003</v>
       </c>
     </row>
-    <row r="20" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="20" x14ac:dyDescent="0.3">
       <c r="H20" s="26" t="str">
         <f>data_export!A8</f>
         <v>NE Solar</v>
@@ -4581,7 +4581,7 @@
         <v>4.6760539999999997</v>
       </c>
     </row>
-    <row r="21" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="21" x14ac:dyDescent="0.3">
       <c r="H21" s="26" t="str">
         <f>data_export!A9</f>
         <v>CSI (TPO)</v>
@@ -4624,7 +4624,7 @@
         <v>3.8154659999999998</v>
       </c>
     </row>
-    <row r="22" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="22" x14ac:dyDescent="0.3">
       <c r="H22" s="26" t="str">
         <f>data_export!A10</f>
         <v>CSI (HO)</v>
@@ -4667,7 +4667,7 @@
         <v>2.7115860000000001</v>
       </c>
     </row>
-    <row r="23" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="23" x14ac:dyDescent="0.3">
       <c r="H23" s="26" t="str">
         <f>data_export!A11</f>
         <v>CT Solar</v>
@@ -4710,8 +4710,8 @@
         <v>1.633623</v>
       </c>
     </row>
-    <row r="24" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
-    <row r="25" s="23" customFormat="true" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="24" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="25" s="23" customFormat="true" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
       <c r="F25" s="19"/>
       <c r="G25" s="20" t="str">
         <f>data_export!A12</f>
@@ -4760,7 +4760,7 @@
       <c r="U25" s="21"/>
       <c r="V25" s="19"/>
     </row>
-    <row r="26" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="26" x14ac:dyDescent="0.3">
       <c r="H26" s="26" t="str">
         <f>data_export!A13</f>
         <v>BEV (State - Rebate)</v>
@@ -4803,7 +4803,7 @@
         <v>1.561256</v>
       </c>
     </row>
-    <row r="27" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="27" x14ac:dyDescent="0.3">
       <c r="H27" s="26" t="str">
         <f>data_export!A14</f>
         <v>ITC (EV)</v>
@@ -4846,7 +4846,7 @@
         <v>1.473692</v>
       </c>
     </row>
-    <row r="28" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="28" x14ac:dyDescent="0.3">
       <c r="H28" s="26" t="str">
         <f>data_export!A15</f>
         <v>EFMP</v>
@@ -4889,8 +4889,8 @@
         <v>1.2961830000000001</v>
       </c>
     </row>
-    <row r="29" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
-    <row r="30" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="29" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="30" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
       <c r="G30" s="20" t="str">
         <f>data_export!A16</f>
         <v>Appliance Rebates</v>
@@ -4938,7 +4938,7 @@
       <c r="U30" s="22"/>
       <c r="V30" s="19"/>
     </row>
-    <row r="31" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="31" x14ac:dyDescent="0.3">
       <c r="H31" s="26" t="str">
         <f>data_export!A17</f>
         <v>C4A (CW)</v>
@@ -4981,7 +4981,7 @@
         <v>1.405106</v>
       </c>
     </row>
-    <row r="32" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="32" x14ac:dyDescent="0.3">
       <c r="H32" s="26" t="str">
         <f>data_export!A18</f>
         <v>ES (WH)</v>
@@ -5024,7 +5024,7 @@
         <v>1.340039</v>
       </c>
     </row>
-    <row r="33" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="33" x14ac:dyDescent="0.3">
       <c r="H33" s="26" t="str">
         <f>data_export!A19</f>
         <v>ES (CW)</v>
@@ -5066,7 +5066,7 @@
         <v>1.3096449999999999</v>
       </c>
     </row>
-    <row r="34" s="23" customFormat="true" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="34" s="23" customFormat="true" x14ac:dyDescent="0.3">
       <c r="F34" s="19"/>
       <c r="G34" s="24"/>
       <c r="H34" s="26" t="str">
@@ -5115,7 +5115,7 @@
       <c r="U34" s="27"/>
       <c r="V34" s="24"/>
     </row>
-    <row r="35" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="35" x14ac:dyDescent="0.3">
       <c r="H35" s="26" t="str">
         <f>data_export!A21</f>
         <v>ES (DW)</v>
@@ -5158,7 +5158,7 @@
         <v>1.0533790000000001</v>
       </c>
     </row>
-    <row r="36" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="36" x14ac:dyDescent="0.3">
       <c r="H36" s="26" t="str">
         <f>data_export!A22</f>
         <v>C4A (Fridge)</v>
@@ -5201,7 +5201,7 @@
         <v>1.041846</v>
       </c>
     </row>
-    <row r="37" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="37" x14ac:dyDescent="0.3">
       <c r="H37" s="26" t="str">
         <f>data_export!A23</f>
         <v>ES (Fridge)</v>
@@ -5244,7 +5244,7 @@
         <v>1.0114190000000001</v>
       </c>
     </row>
-    <row r="38" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="38" x14ac:dyDescent="0.3">
       <c r="H38" s="26" t="str">
         <f>data_export!A24</f>
         <v>CA ESA</v>
@@ -5287,8 +5287,8 @@
         <v>0.95832660000000003</v>
       </c>
     </row>
-    <row r="39" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
-    <row r="40" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="39" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="40" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
       <c r="G40" s="20" t="str">
         <f>data_export!A25</f>
         <v>Vehicle Retirement</v>
@@ -5336,7 +5336,7 @@
       <c r="U40" s="22"/>
       <c r="V40" s="19"/>
     </row>
-    <row r="41" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="41" x14ac:dyDescent="0.3">
       <c r="H41" s="26" t="str">
         <f>data_export!A26</f>
         <v>C4C (TX)</v>
@@ -5379,7 +5379,7 @@
         <v>1.0671250000000001</v>
       </c>
     </row>
-    <row r="42" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="42" x14ac:dyDescent="0.3">
       <c r="H42" s="26" t="str">
         <f>data_export!A27</f>
         <v>C4C (US)</v>
@@ -5422,7 +5422,7 @@
         <v>1.044287</v>
       </c>
     </row>
-    <row r="43" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="43" x14ac:dyDescent="0.3">
       <c r="H43" s="26" t="str">
         <f>data_export!A28</f>
         <v>BAAQMD</v>
@@ -5466,8 +5466,8 @@
       </c>
       <c r="AA43" s="38"/>
     </row>
-    <row r="44" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
-    <row r="45" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="44" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="45" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
       <c r="G45" s="20" t="str">
         <f>data_export!A29</f>
         <v>Hybrid Vehicles</v>
@@ -5515,7 +5515,7 @@
       <c r="U45" s="22"/>
       <c r="V45" s="19"/>
     </row>
-    <row r="46" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="46" x14ac:dyDescent="0.3">
       <c r="H46" s="26" t="str">
         <f>data_export!A30</f>
         <v>HY (S-STW)</v>
@@ -5558,7 +5558,7 @@
         <v>1.0272870000000001</v>
       </c>
     </row>
-    <row r="47" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="47" x14ac:dyDescent="0.3">
       <c r="H47" s="26" t="str">
         <f>data_export!A31</f>
         <v>HY (F-ITC)</v>
@@ -5601,7 +5601,7 @@
         <v>1.0075080000000001</v>
       </c>
     </row>
-    <row r="48" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="48" x14ac:dyDescent="0.3">
       <c r="H48" s="26" t="str">
         <f>data_export!A32</f>
         <v>HY (S-ITC)</v>
@@ -5644,8 +5644,8 @@
         <v>1.001606</v>
       </c>
     </row>
-    <row r="49" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
-    <row r="50" s="23" customFormat="true" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="49" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="50" s="23" customFormat="true" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
       <c r="F50" s="19"/>
       <c r="G50" s="20" t="str">
         <f>data_export!A33</f>
@@ -5694,7 +5694,7 @@
       <c r="U50" s="21"/>
       <c r="V50" s="19"/>
     </row>
-    <row r="51" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="51" x14ac:dyDescent="0.3">
       <c r="H51" s="26" t="str">
         <f>data_export!A34</f>
         <v>EPP</v>
@@ -5737,7 +5737,7 @@
         <v>1.2101489999999999</v>
       </c>
     </row>
-    <row r="52" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="52" x14ac:dyDescent="0.3">
       <c r="H52" s="26" t="str">
         <f>data_export!A35</f>
         <v>IHWAP</v>
@@ -5780,7 +5780,7 @@
         <v>0.98018269999999996</v>
       </c>
     </row>
-    <row r="53" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="53" x14ac:dyDescent="0.3">
       <c r="H53" s="26" t="str">
         <f>data_export!A36</f>
         <v>WI RF</v>
@@ -5823,7 +5823,7 @@
         <v>0.9198132</v>
       </c>
     </row>
-    <row r="54" s="23" customFormat="true" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="54" s="23" customFormat="true" x14ac:dyDescent="0.3">
       <c r="F54" s="19"/>
       <c r="G54" s="37"/>
       <c r="H54" s="26" t="str">
@@ -5872,7 +5872,7 @@
       <c r="U54" s="25"/>
       <c r="V54" s="19"/>
     </row>
-    <row r="55" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="55" x14ac:dyDescent="0.3">
       <c r="H55" s="26" t="str">
         <f>data_export!A38</f>
         <v>LEEP+</v>
@@ -5915,8 +5915,8 @@
         <v>0.8591472</v>
       </c>
     </row>
-    <row r="56" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
-    <row r="57" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="56" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="57" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
       <c r="F57" s="37"/>
       <c r="G57" s="21" t="str">
         <f>data_export!A39</f>
@@ -5965,7 +5965,7 @@
       <c r="U57" s="21"/>
       <c r="V57" s="19"/>
     </row>
-    <row r="58" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="58" x14ac:dyDescent="0.3">
       <c r="H58" s="26" t="str">
         <f>data_export!A40</f>
         <v>CA 20/20</v>
@@ -6008,7 +6008,7 @@
         <v>2.572498</v>
       </c>
     </row>
-    <row r="59" s="23" customFormat="true" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="59" s="23" customFormat="true" x14ac:dyDescent="0.3">
       <c r="F59" s="19"/>
       <c r="G59" s="37"/>
       <c r="H59" s="26" t="str">
@@ -6057,8 +6057,8 @@
       <c r="U59" s="25"/>
       <c r="V59" s="19"/>
     </row>
-    <row r="60" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
-    <row r="61" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="60" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="61" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
       <c r="F61" s="19" t="s">
         <v>1</v>
       </c>
@@ -6079,7 +6079,7 @@
       <c r="U61" s="24"/>
       <c r="W61" s="24"/>
     </row>
-    <row r="62" ht="10.2" customHeight="true" thickTop="true" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="62" ht="10.2" customHeight="true" thickTop="true" x14ac:dyDescent="0.3">
       <c r="F62" s="30"/>
       <c r="G62" s="30"/>
       <c r="H62" s="30"/>
@@ -6098,7 +6098,7 @@
       <c r="U62" s="30"/>
       <c r="V62" s="30"/>
     </row>
-    <row r="63" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="63" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
       <c r="F63" s="19"/>
       <c r="G63" s="20" t="str">
         <f>data_export!A42</f>
@@ -6147,7 +6147,7 @@
       <c r="U63" s="21"/>
       <c r="V63" s="28"/>
     </row>
-    <row r="64" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="64" x14ac:dyDescent="0.3">
       <c r="H64" s="26" t="str">
         <f>data_export!A43</f>
         <v>HER (17 RCTs)</v>
@@ -6190,7 +6190,7 @@
         <v>3.0060020000000001</v>
       </c>
     </row>
-    <row r="65" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="65" x14ac:dyDescent="0.3">
       <c r="H65" s="26" t="str">
         <f>data_export!A44</f>
         <v>Opower Elec. (166 RCTs)</v>
@@ -6233,7 +6233,7 @@
         <v>2.5476939999999999</v>
       </c>
     </row>
-    <row r="66" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="66" x14ac:dyDescent="0.3">
       <c r="H66" s="26" t="str">
         <f>data_export!A45</f>
         <v>PER</v>
@@ -6276,7 +6276,7 @@
         <v>1.5998129999999999</v>
       </c>
     </row>
-    <row r="67" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="67" x14ac:dyDescent="0.3">
       <c r="H67" s="26" t="str">
         <f>data_export!A46</f>
         <v>Opower Nat. Gas (52 RCTs)</v>
@@ -6319,8 +6319,8 @@
         <v>0.4509785</v>
       </c>
     </row>
-    <row r="68" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
-    <row r="69" s="23" customFormat="true" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="68" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="69" s="23" customFormat="true" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
       <c r="F69" s="19"/>
       <c r="G69" s="20" t="str">
         <f>data_export!A47</f>
@@ -6369,7 +6369,7 @@
       <c r="U69" s="21"/>
       <c r="V69" s="19"/>
     </row>
-    <row r="70" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="70" x14ac:dyDescent="0.3">
       <c r="H70" s="26" t="str">
         <f>data_export!A48</f>
         <v>Audit Nudge</v>
@@ -6412,7 +6412,7 @@
         <v>2.1168469999999999</v>
       </c>
     </row>
-    <row r="71" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="71" x14ac:dyDescent="0.3">
       <c r="H71" s="26" t="str">
         <f>data_export!A49</f>
         <v>Solarize</v>
@@ -6455,7 +6455,7 @@
         <v>1.8085340000000001</v>
       </c>
     </row>
-    <row r="72" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="72" x14ac:dyDescent="0.3">
       <c r="F72" s="19"/>
       <c r="G72" s="19"/>
       <c r="H72" s="25" t="str">
@@ -6502,7 +6502,7 @@
       <c r="U72" s="27"/>
       <c r="V72" s="19"/>
     </row>
-    <row r="73" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="73" x14ac:dyDescent="0.3">
       <c r="H73" s="26" t="str">
         <f>data_export!A51</f>
         <v>IHWAP + Nudge (H)</v>
@@ -6545,7 +6545,7 @@
         <v>1.0694269999999999</v>
       </c>
     </row>
-    <row r="74" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="74" x14ac:dyDescent="0.3">
       <c r="H74" s="26" t="str">
         <f>data_export!A52</f>
         <v>IHWAP + Nudge (L)</v>
@@ -6588,7 +6588,7 @@
         <v>1.0624659999999999</v>
       </c>
     </row>
-    <row r="75" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="75" x14ac:dyDescent="0.3">
       <c r="H75" s="26" t="str">
         <f>data_export!A53</f>
         <v>WAP + Nudge</v>
@@ -6631,8 +6631,8 @@
         <v>0.27975709999999998</v>
       </c>
     </row>
-    <row r="76" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
-    <row r="77" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="76" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="77" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
       <c r="F77" s="19" t="s">
         <v>2</v>
       </c>
@@ -6653,7 +6653,7 @@
       <c r="U77" s="24"/>
       <c r="W77" s="24"/>
     </row>
-    <row r="78" ht="10.2" customHeight="true" thickTop="true" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="78" ht="10.2" customHeight="true" thickTop="true" x14ac:dyDescent="0.3">
       <c r="F78" s="30"/>
       <c r="G78" s="30"/>
       <c r="H78" s="30"/>
@@ -6672,7 +6672,7 @@
       <c r="U78" s="30"/>
       <c r="V78" s="30"/>
     </row>
-    <row r="79" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="79" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
       <c r="F79" s="19"/>
       <c r="G79" s="20" t="str">
         <f>data_export!A54</f>
@@ -6720,7 +6720,7 @@
       </c>
       <c r="U79" s="21"/>
     </row>
-    <row r="80" s="23" customFormat="true" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="80" s="23" customFormat="true" x14ac:dyDescent="0.3">
       <c r="F80" s="25"/>
       <c r="G80" s="26"/>
       <c r="H80" s="26" t="str">
@@ -6769,7 +6769,7 @@
       <c r="U80" s="19"/>
       <c r="V80" s="19"/>
     </row>
-    <row r="81" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="81" x14ac:dyDescent="0.3">
       <c r="H81" s="26" t="str">
         <f>data_export!A56</f>
         <v>Gas (Su)</v>
@@ -6812,7 +6812,7 @@
         <v>0.52256800000000003</v>
       </c>
     </row>
-    <row r="82" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="82" x14ac:dyDescent="0.3">
       <c r="H82" s="26" t="str">
         <f>data_export!A57</f>
         <v>Gas (Coglianese)</v>
@@ -6855,7 +6855,7 @@
         <v>0.56079049999999997</v>
       </c>
     </row>
-    <row r="83" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="83" x14ac:dyDescent="0.3">
       <c r="H83" s="26" t="str">
         <f>data_export!A58</f>
         <v>Gas (Manzan)</v>
@@ -6898,7 +6898,7 @@
         <v>0.57773160000000001</v>
       </c>
     </row>
-    <row r="84" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="84" x14ac:dyDescent="0.3">
       <c r="H84" s="26" t="str">
         <f>data_export!A59</f>
         <v>Gas (Small)</v>
@@ -6941,7 +6941,7 @@
         <v>0.60484959999999999</v>
       </c>
     </row>
-    <row r="85" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="85" x14ac:dyDescent="0.3">
       <c r="H85" s="26" t="str">
         <f>data_export!A60</f>
         <v>Gas (Li)</v>
@@ -6984,7 +6984,7 @@
         <v>0.61893330000000002</v>
       </c>
     </row>
-    <row r="86" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="86" x14ac:dyDescent="0.3">
       <c r="H86" s="26" t="str">
         <f>data_export!A61</f>
         <v>Gas (Levin)</v>
@@ -7027,7 +7027,7 @@
         <v>0.65441349999999998</v>
       </c>
     </row>
-    <row r="87" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="87" x14ac:dyDescent="0.3">
       <c r="H87" s="26" t="str">
         <f>data_export!A62</f>
         <v>Gas (Sentenac-Chemin)</v>
@@ -7070,7 +7070,7 @@
         <v>0.67320559999999996</v>
       </c>
     </row>
-    <row r="88" s="23" customFormat="true" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="88" s="23" customFormat="true" x14ac:dyDescent="0.3">
       <c r="F88" s="25"/>
       <c r="G88" s="26"/>
       <c r="H88" s="26" t="str">
@@ -7121,7 +7121,7 @@
       <c r="W88" s="25"/>
       <c r="X88" s="24"/>
     </row>
-    <row r="89" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="89" x14ac:dyDescent="0.3">
       <c r="H89" s="26" t="str">
         <f>data_export!A64</f>
         <v>Gas (Gelman)</v>
@@ -7164,7 +7164,7 @@
         <v>0.81367109999999998</v>
       </c>
     </row>
-    <row r="90" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="90" x14ac:dyDescent="0.3">
       <c r="H90" s="26" t="str">
         <f>data_export!A65</f>
         <v>Gas (Park)</v>
@@ -7207,7 +7207,7 @@
         <v>0.81778010000000001</v>
       </c>
     </row>
-    <row r="91" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="91" x14ac:dyDescent="0.3">
       <c r="H91" s="26" t="str">
         <f>data_export!A66</f>
         <v>Gas (Hughes)</v>
@@ -7250,8 +7250,8 @@
         <v>0.9526964</v>
       </c>
     </row>
-    <row r="92" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
-    <row r="93" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="92" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="93" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
       <c r="F93" s="37"/>
       <c r="G93" s="21" t="str">
         <f>data_export!A67</f>
@@ -7299,7 +7299,7 @@
       </c>
       <c r="U93" s="21"/>
     </row>
-    <row r="94" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="94" x14ac:dyDescent="0.3">
       <c r="H94" s="26" t="str">
         <f>data_export!A68</f>
         <v>Jet Fuel</v>
@@ -7342,7 +7342,7 @@
         <v>0.75395920000000005</v>
       </c>
     </row>
-    <row r="95" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="95" x14ac:dyDescent="0.3">
       <c r="H95" s="26" t="str">
         <f>data_export!A69</f>
         <v>Diesel</v>
@@ -7385,8 +7385,8 @@
         <v>0.84163069999999995</v>
       </c>
     </row>
-    <row r="96" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
-    <row r="97" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="96" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="97" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
       <c r="F97" s="37"/>
       <c r="G97" s="21" t="str">
         <f>data_export!A70</f>
@@ -7434,7 +7434,7 @@
       </c>
       <c r="U97" s="21"/>
     </row>
-    <row r="98" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="98" x14ac:dyDescent="0.3">
       <c r="H98" s="26" t="str">
         <f>data_export!A71</f>
         <v>CPP (AJ)</v>
@@ -7477,7 +7477,7 @@
         <v>0.4588798</v>
       </c>
     </row>
-    <row r="99" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="99" x14ac:dyDescent="0.3">
       <c r="H99" s="26" t="str">
         <f>data_export!A72</f>
         <v>CARE</v>
@@ -7520,7 +7520,7 @@
         <v>0.71881779999999995</v>
       </c>
     </row>
-    <row r="100" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="100" x14ac:dyDescent="0.3">
       <c r="H100" s="26" t="str">
         <f>data_export!A73</f>
         <v>CPP (PJ)</v>
@@ -7563,8 +7563,8 @@
         <v>0.78000899999999995</v>
       </c>
     </row>
-    <row r="101" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
-    <row r="102" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="101" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="102" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
       <c r="F102" s="37"/>
       <c r="G102" s="21" t="str">
         <f>data_export!A74</f>
@@ -7612,7 +7612,7 @@
       </c>
       <c r="U102" s="21"/>
     </row>
-    <row r="103" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="103" x14ac:dyDescent="0.3">
       <c r="H103" s="26" t="str">
         <f>data_export!A75</f>
         <v>RGGI</v>
@@ -7655,7 +7655,7 @@
         <v>-0.67106120000000002</v>
       </c>
     </row>
-    <row r="104" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="104" x14ac:dyDescent="0.3">
       <c r="H104" s="26" t="str">
         <f>data_export!A76</f>
         <v>CA CT</v>
@@ -7698,8 +7698,8 @@
         <v>0.94143829999999995</v>
       </c>
     </row>
-    <row r="105" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
-    <row r="106" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="105" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="106" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
       <c r="F106" s="19" t="s">
         <v>3</v>
       </c>
@@ -7720,7 +7720,7 @@
       <c r="U106" s="24"/>
       <c r="W106" s="24"/>
     </row>
-    <row r="107" ht="10.2" customHeight="true" thickTop="true" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="107" ht="10.2" customHeight="true" thickTop="true" x14ac:dyDescent="0.3">
       <c r="F107" s="30"/>
       <c r="G107" s="30"/>
       <c r="H107" s="30"/>
@@ -7740,7 +7740,7 @@
       <c r="V107" s="30"/>
       <c r="W107" s="24"/>
     </row>
-    <row r="108" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="108" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
       <c r="F108" s="37"/>
       <c r="G108" s="21" t="str">
         <f>data_export!A77</f>
@@ -7788,7 +7788,7 @@
       </c>
       <c r="U108" s="21"/>
     </row>
-    <row r="109" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="109" x14ac:dyDescent="0.3">
       <c r="H109" s="26" t="str">
         <f>data_export!A78</f>
         <v>Cookstove (Kenya)</v>
@@ -7831,7 +7831,7 @@
         <v>323.4529</v>
       </c>
     </row>
-    <row r="110" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="110" x14ac:dyDescent="0.3">
       <c r="H110" s="26" t="str">
         <f>data_export!A79</f>
         <v>Cookstove (India)</v>
@@ -7874,8 +7874,8 @@
         <v>-2.2788930000000001</v>
       </c>
     </row>
-    <row r="111" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
-    <row r="112" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="111" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="112" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
       <c r="F112" s="37"/>
       <c r="G112" s="21" t="str">
         <f>data_export!A80</f>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="U112" s="21"/>
     </row>
-    <row r="113" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="113" x14ac:dyDescent="0.3">
       <c r="H113" s="26" t="str">
         <f>data_export!A81</f>
         <v>REDD+ (SL)</v>
@@ -7966,7 +7966,7 @@
         <v>119.4383</v>
       </c>
     </row>
-    <row r="114" s="23" customFormat="true" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="114" s="23" customFormat="true" x14ac:dyDescent="0.3">
       <c r="F114" s="19"/>
       <c r="G114" s="26"/>
       <c r="H114" s="26" t="str">
@@ -8015,7 +8015,7 @@
       <c r="U114" s="19"/>
       <c r="V114" s="19"/>
     </row>
-    <row r="115" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="115" x14ac:dyDescent="0.3">
       <c r="H115" s="26" t="str">
         <f>data_export!A83</f>
         <v>REDD+</v>
@@ -8058,8 +8058,8 @@
         <v>4.1559650000000001</v>
       </c>
     </row>
-    <row r="116" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
-    <row r="117" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="116" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="117" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
       <c r="F117" s="37"/>
       <c r="G117" s="21" t="str">
         <f>data_export!A84</f>
@@ -8107,7 +8107,7 @@
       </c>
       <c r="U117" s="21"/>
     </row>
-    <row r="118" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="118" x14ac:dyDescent="0.3">
       <c r="H118" s="26" t="str">
         <f>data_export!A85</f>
         <v>India PES (Upfront)</v>
@@ -8150,7 +8150,7 @@
         <v>14.66147</v>
       </c>
     </row>
-    <row r="119" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="119" x14ac:dyDescent="0.3">
       <c r="H119" s="26" t="str">
         <f>data_export!A86</f>
         <v>India PES (Standard)</v>
@@ -8193,8 +8193,8 @@
         <v>10.749079999999999</v>
       </c>
     </row>
-    <row r="120" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
-    <row r="121" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="120" ht="10.2" customHeight="true" x14ac:dyDescent="0.3"/>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="121" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
       <c r="F121" s="37"/>
       <c r="G121" s="20" t="str">
         <f>data_export!A87</f>
@@ -8243,7 +8243,7 @@
       <c r="U121" s="21"/>
       <c r="V121" s="25"/>
     </row>
-    <row r="122" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="122" x14ac:dyDescent="0.3">
       <c r="H122" s="26" t="str">
         <f>data_export!A88</f>
         <v>Offset (India)</v>
@@ -8286,11 +8286,11 @@
         <v>7.6411709999999999</v>
       </c>
     </row>
-    <row r="123" ht="10.2" customHeight="true" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="123" ht="10.2" customHeight="true" x14ac:dyDescent="0.3">
       <c r="H123" s="26"/>
       <c r="I123" s="26"/>
     </row>
-    <row r="124" s="23" customFormat="true" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="124" s="23" customFormat="true" ht="29.4" thickBot="true" x14ac:dyDescent="0.35">
       <c r="F124" s="19"/>
       <c r="G124" s="20" t="str">
         <f>data_export!A89</f>
@@ -8339,7 +8339,7 @@
       <c r="U124" s="21"/>
       <c r="V124" s="19"/>
     </row>
-    <row r="125" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="125" x14ac:dyDescent="0.3">
       <c r="H125" s="26" t="str">
         <f>data_export!A90</f>
         <v>Fridge (Mexico)</v>
@@ -8382,7 +8382,7 @@
         <v>0.85202619999999996</v>
       </c>
     </row>
-    <row r="126" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="126" x14ac:dyDescent="0.3">
       <c r="H126" s="26" t="str">
         <f>data_export!A91</f>
         <v>AC (Mexico)</v>
@@ -8425,7 +8425,7 @@
         <v>0.67351689999999997</v>
       </c>
     </row>
-    <row r="127" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="127" x14ac:dyDescent="0.3">
       <c r="H127" s="26" t="str">
         <f>data_export!A92</f>
         <v>WAP (Mexico)</v>
@@ -8468,8 +8468,8 @@
         <v>0.421819</v>
       </c>
     </row>
-    <row r="128" ht="10.2" customHeight="true" thickBot="true" x14ac:dyDescent="0.35"/>
-    <row r="129" ht="29.4" thickTop="true" x14ac:dyDescent="0.3">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="128" ht="10.2" customHeight="true" thickBot="true" x14ac:dyDescent="0.35"/>
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="129" ht="29.4" thickTop="true" x14ac:dyDescent="0.3">
       <c r="F129" s="32"/>
       <c r="G129" s="32"/>
       <c r="H129" s="32"/>
